--- a/research/traditional_assets/database/data/tunisia/tunisia_recreation.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_recreation.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bvmt_ecycl" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,46 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
       <c r="E2">
-        <v>0.09029999999999999</v>
+        <v>0.0756</v>
       </c>
       <c r="G2">
-        <v>0.1388888888888889</v>
+        <v>0.2218045112781955</v>
       </c>
       <c r="H2">
-        <v>0.1388888888888889</v>
+        <v>0.2218045112781955</v>
       </c>
       <c r="I2">
-        <v>0.1676245210727969</v>
+        <v>0.2067669172932331</v>
       </c>
       <c r="J2">
-        <v>0.1461863243314029</v>
+        <v>0.1683769684798315</v>
       </c>
       <c r="K2">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="L2">
-        <v>0.1513409961685824</v>
+        <v>0.1409774436090226</v>
       </c>
       <c r="M2">
-        <v>4.86</v>
+        <v>4.82</v>
       </c>
       <c r="N2">
-        <v>0.04835820895522389</v>
+        <v>0.05943279901356351</v>
       </c>
       <c r="O2">
-        <v>0.6151898734177216</v>
+        <v>0.6426666666666667</v>
       </c>
       <c r="P2">
-        <v>4.86</v>
+        <v>4.82</v>
       </c>
       <c r="Q2">
-        <v>0.04835820895522389</v>
+        <v>0.05943279901356351</v>
       </c>
       <c r="R2">
-        <v>0.6151898734177216</v>
+        <v>0.6426666666666667</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,70 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>6.39</v>
+        <v>2.77</v>
       </c>
       <c r="V2">
-        <v>0.0635820895522388</v>
+        <v>0.0341553637484587</v>
       </c>
       <c r="W2">
-        <v>0.5984848484848485</v>
+        <v>0.4518072289156626</v>
       </c>
       <c r="X2">
-        <v>0.1512959408985673</v>
+        <v>0.2916900229795031</v>
       </c>
       <c r="Y2">
-        <v>0.4471889075862812</v>
+        <v>0.1601172059361595</v>
       </c>
       <c r="Z2">
-        <v>2.354533152909337</v>
+        <v>1.790642881184786</v>
       </c>
       <c r="AA2">
-        <v>0.3442005471402448</v>
+        <v>0.3015030199638854</v>
       </c>
       <c r="AB2">
-        <v>0.1387458450438658</v>
+        <v>0.2434272406770251</v>
       </c>
       <c r="AC2">
-        <v>0.2054547020963791</v>
+        <v>0.05807577928686034</v>
       </c>
       <c r="AD2">
-        <v>19.5</v>
+        <v>33.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>19.5</v>
+        <v>33.9</v>
       </c>
       <c r="AG2">
-        <v>13.11</v>
+        <v>31.13</v>
       </c>
       <c r="AH2">
-        <v>0.1625</v>
+        <v>0.2947826086956521</v>
       </c>
       <c r="AI2">
-        <v>0.5401662049861495</v>
+        <v>0.658252427184466</v>
       </c>
       <c r="AJ2">
-        <v>0.1153947715870082</v>
+        <v>0.2773768154682349</v>
       </c>
       <c r="AK2">
-        <v>0.441265567149108</v>
+        <v>0.6388261851015801</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM2">
-        <v>-0.272</v>
+        <v>1.762</v>
       </c>
       <c r="AN2">
-        <v>2.105831533477322</v>
+        <v>2.947826086956522</v>
+      </c>
+      <c r="AO2">
+        <v>5.88235294117647</v>
       </c>
       <c r="AP2">
-        <v>1.415766738660907</v>
+        <v>2.70695652173913</v>
       </c>
       <c r="AQ2">
-        <v>-32.16911764705882</v>
+        <v>6.242905788876277</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +724,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
       <c r="E3">
-        <v>0.09029999999999999</v>
+        <v>0.0756</v>
       </c>
       <c r="G3">
-        <v>0.1388888888888889</v>
+        <v>0.2218045112781955</v>
       </c>
       <c r="H3">
-        <v>0.1388888888888889</v>
+        <v>0.2218045112781955</v>
       </c>
       <c r="I3">
-        <v>0.1676245210727969</v>
+        <v>0.2067669172932331</v>
       </c>
       <c r="J3">
-        <v>0.1461863243314029</v>
+        <v>0.1683769684798315</v>
       </c>
       <c r="K3">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="L3">
-        <v>0.1513409961685824</v>
+        <v>0.1409774436090226</v>
       </c>
       <c r="M3">
-        <v>4.86</v>
+        <v>4.82</v>
       </c>
       <c r="N3">
-        <v>0.04835820895522389</v>
+        <v>0.05943279901356351</v>
       </c>
       <c r="O3">
-        <v>0.6151898734177216</v>
+        <v>0.6426666666666667</v>
       </c>
       <c r="P3">
-        <v>4.86</v>
+        <v>4.82</v>
       </c>
       <c r="Q3">
-        <v>0.04835820895522389</v>
+        <v>0.05943279901356351</v>
       </c>
       <c r="R3">
-        <v>0.6151898734177216</v>
+        <v>0.6426666666666667</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,70 +772,8785 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>6.39</v>
+        <v>2.77</v>
       </c>
       <c r="V3">
-        <v>0.0635820895522388</v>
+        <v>0.0341553637484587</v>
       </c>
       <c r="W3">
-        <v>0.5984848484848485</v>
+        <v>0.4518072289156626</v>
       </c>
       <c r="X3">
-        <v>0.1512959408985673</v>
+        <v>0.2916900229795031</v>
       </c>
       <c r="Y3">
-        <v>0.4471889075862812</v>
+        <v>0.1601172059361595</v>
       </c>
       <c r="Z3">
-        <v>2.354533152909337</v>
+        <v>1.790642881184786</v>
       </c>
       <c r="AA3">
-        <v>0.3442005471402448</v>
+        <v>0.3015030199638854</v>
       </c>
       <c r="AB3">
-        <v>0.1387458450438658</v>
+        <v>0.2434272406770251</v>
       </c>
       <c r="AC3">
-        <v>0.2054547020963791</v>
+        <v>0.05807577928686034</v>
       </c>
       <c r="AD3">
-        <v>19.5</v>
+        <v>33.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>19.5</v>
+        <v>33.9</v>
       </c>
       <c r="AG3">
-        <v>13.11</v>
+        <v>31.13</v>
       </c>
       <c r="AH3">
-        <v>0.1625</v>
+        <v>0.2947826086956521</v>
       </c>
       <c r="AI3">
-        <v>0.5401662049861495</v>
+        <v>0.658252427184466</v>
       </c>
       <c r="AJ3">
-        <v>0.1153947715870082</v>
+        <v>0.2773768154682349</v>
       </c>
       <c r="AK3">
-        <v>0.441265567149108</v>
+        <v>0.6388261851015801</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM3">
-        <v>-0.272</v>
+        <v>1.762</v>
       </c>
       <c r="AN3">
-        <v>2.105831533477322</v>
+        <v>2.947826086956522</v>
+      </c>
+      <c r="AO3">
+        <v>5.88235294117647</v>
       </c>
       <c r="AP3">
-        <v>1.415766738660907</v>
+        <v>2.70695652173913</v>
       </c>
       <c r="AQ3">
-        <v>-32.16911764705882</v>
+        <v>6.242905788876277</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Euro-Cycles S.A (BVMT:ECYCL)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BVMT:ECYCL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.294782608695652</v>
+      </c>
+      <c r="F2">
+        <v>0.37</v>
+      </c>
+      <c r="G2">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="H2">
+        <v>88.3899058049299</v>
+      </c>
+      <c r="I2">
+        <v>112.23</v>
+      </c>
+      <c r="J2">
+        <v>128.16990580493</v>
+      </c>
+      <c r="K2">
+        <v>33.9</v>
+      </c>
+      <c r="L2">
+        <v>42.55</v>
+      </c>
+      <c r="M2">
+        <v>0.243427240677025</v>
+      </c>
+      <c r="N2">
+        <v>0.217978685331445</v>
+      </c>
+      <c r="O2">
+        <v>0.127966720183486</v>
+      </c>
+      <c r="P2">
+        <v>0.04675</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.291690022979503</v>
+      </c>
+      <c r="T2">
+        <v>0.318541564018167</v>
+      </c>
+      <c r="U2">
+        <v>1.34112266115</v>
+      </c>
+      <c r="V2">
+        <v>1.48352135979961</v>
+      </c>
+      <c r="W2">
+        <v>4.520884520884522</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="AB2">
+        <v>0.1885659159339335</v>
+      </c>
+      <c r="AC2">
+        <v>0.1505490825688073</v>
+      </c>
+      <c r="AD2">
+        <v>0.15</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>11.5</v>
+      </c>
+      <c r="AH2">
+        <v>0.92</v>
+      </c>
+      <c r="AI2">
+        <v>1.560000000000002</v>
+      </c>
+      <c r="AJ2">
+        <v>33.9</v>
+      </c>
+      <c r="AK2">
+        <v>33.9</v>
+      </c>
+      <c r="AL2">
+        <v>1.87</v>
+      </c>
+      <c r="AM2">
+        <v>33.9</v>
+      </c>
+      <c r="AN2">
+        <v>2.77</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.225393102521382</v>
+      </c>
+      <c r="C2">
+        <v>125.8469782529924</v>
+      </c>
+      <c r="D2">
+        <v>123.0769782529924</v>
+      </c>
+      <c r="E2">
+        <v>-33.9</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>2.77</v>
+      </c>
+      <c r="H2">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>11.5</v>
+      </c>
+      <c r="K2">
+        <v>0.92</v>
+      </c>
+      <c r="L2">
+        <v>10.58</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>10.58</v>
+      </c>
+      <c r="O2">
+        <v>1.587</v>
+      </c>
+      <c r="P2">
+        <v>8.993</v>
+      </c>
+      <c r="Q2">
+        <v>9.913</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.225393102521382</v>
+      </c>
+      <c r="T2">
+        <v>0.9895378048425111</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.15</v>
+      </c>
+      <c r="W2">
+        <v>0.038845</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.2251136628675999</v>
+      </c>
+      <c r="C3">
+        <v>124.8815733474274</v>
+      </c>
+      <c r="D3">
+        <v>123.2615733474274</v>
+      </c>
+      <c r="E3">
+        <v>-32.75</v>
+      </c>
+      <c r="F3">
+        <v>1.15</v>
+      </c>
+      <c r="G3">
+        <v>2.77</v>
+      </c>
+      <c r="H3">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>11.5</v>
+      </c>
+      <c r="K3">
+        <v>0.92</v>
+      </c>
+      <c r="L3">
+        <v>10.58</v>
+      </c>
+      <c r="M3">
+        <v>0.05255500000000001</v>
+      </c>
+      <c r="N3">
+        <v>10.527445</v>
+      </c>
+      <c r="O3">
+        <v>1.57911675</v>
+      </c>
+      <c r="P3">
+        <v>8.948328249999999</v>
+      </c>
+      <c r="Q3">
+        <v>9.868328249999999</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.2269951645127272</v>
+      </c>
+      <c r="T3">
+        <v>0.9980338365002497</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.15</v>
+      </c>
+      <c r="W3">
+        <v>0.038845</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>201.3129102844639</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.2248342232138179</v>
+      </c>
+      <c r="C4">
+        <v>123.9167229977756</v>
+      </c>
+      <c r="D4">
+        <v>123.4467229977756</v>
+      </c>
+      <c r="E4">
+        <v>-31.6</v>
+      </c>
+      <c r="F4">
+        <v>2.3</v>
+      </c>
+      <c r="G4">
+        <v>2.77</v>
+      </c>
+      <c r="H4">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>11.5</v>
+      </c>
+      <c r="K4">
+        <v>0.92</v>
+      </c>
+      <c r="L4">
+        <v>10.58</v>
+      </c>
+      <c r="M4">
+        <v>0.10511</v>
+      </c>
+      <c r="N4">
+        <v>10.47489</v>
+      </c>
+      <c r="O4">
+        <v>1.5712335</v>
+      </c>
+      <c r="P4">
+        <v>8.9036565</v>
+      </c>
+      <c r="Q4">
+        <v>9.8236565</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.2286299216467529</v>
+      </c>
+      <c r="T4">
+        <v>1.006703256559167</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.15</v>
+      </c>
+      <c r="W4">
+        <v>0.038845</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>100.6564551422319</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.2245547835600358</v>
+      </c>
+      <c r="C5">
+        <v>122.9524297067707</v>
+      </c>
+      <c r="D5">
+        <v>123.6324297067707</v>
+      </c>
+      <c r="E5">
+        <v>-30.45</v>
+      </c>
+      <c r="F5">
+        <v>3.45</v>
+      </c>
+      <c r="G5">
+        <v>2.77</v>
+      </c>
+      <c r="H5">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>11.5</v>
+      </c>
+      <c r="K5">
+        <v>0.92</v>
+      </c>
+      <c r="L5">
+        <v>10.58</v>
+      </c>
+      <c r="M5">
+        <v>0.157665</v>
+      </c>
+      <c r="N5">
+        <v>10.422335</v>
+      </c>
+      <c r="O5">
+        <v>1.56335025</v>
+      </c>
+      <c r="P5">
+        <v>8.858984749999999</v>
+      </c>
+      <c r="Q5">
+        <v>9.778984749999999</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.2302983851134389</v>
+      </c>
+      <c r="T5">
+        <v>1.015551427547134</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.15</v>
+      </c>
+      <c r="W5">
+        <v>0.038845</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>67.10430342815464</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.2242753439062537</v>
+      </c>
+      <c r="C6">
+        <v>121.9886959922289</v>
+      </c>
+      <c r="D6">
+        <v>123.8186959922289</v>
+      </c>
+      <c r="E6">
+        <v>-29.3</v>
+      </c>
+      <c r="F6">
+        <v>4.600000000000001</v>
+      </c>
+      <c r="G6">
+        <v>2.77</v>
+      </c>
+      <c r="H6">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>11.5</v>
+      </c>
+      <c r="K6">
+        <v>0.92</v>
+      </c>
+      <c r="L6">
+        <v>10.58</v>
+      </c>
+      <c r="M6">
+        <v>0.21022</v>
+      </c>
+      <c r="N6">
+        <v>10.36978</v>
+      </c>
+      <c r="O6">
+        <v>1.555467</v>
+      </c>
+      <c r="P6">
+        <v>8.814313</v>
+      </c>
+      <c r="Q6">
+        <v>9.734313</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.2320016082356809</v>
+      </c>
+      <c r="T6">
+        <v>1.024583935430683</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.15</v>
+      </c>
+      <c r="W6">
+        <v>0.038845</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>50.32822757111597</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.2239959042524716</v>
+      </c>
+      <c r="C7">
+        <v>121.0255243871627</v>
+      </c>
+      <c r="D7">
+        <v>124.0055243871627</v>
+      </c>
+      <c r="E7">
+        <v>-28.15</v>
+      </c>
+      <c r="F7">
+        <v>5.75</v>
+      </c>
+      <c r="G7">
+        <v>2.77</v>
+      </c>
+      <c r="H7">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>11.5</v>
+      </c>
+      <c r="K7">
+        <v>0.92</v>
+      </c>
+      <c r="L7">
+        <v>10.58</v>
+      </c>
+      <c r="M7">
+        <v>0.262775</v>
+      </c>
+      <c r="N7">
+        <v>10.317225</v>
+      </c>
+      <c r="O7">
+        <v>1.54758375</v>
+      </c>
+      <c r="P7">
+        <v>8.769641249999999</v>
+      </c>
+      <c r="Q7">
+        <v>9.689641249999999</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.2337406886868122</v>
+      </c>
+      <c r="T7">
+        <v>1.033806601374939</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.15</v>
+      </c>
+      <c r="W7">
+        <v>0.038845</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>40.26258205689278</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.2237164645986895</v>
+      </c>
+      <c r="C8">
+        <v>120.0629174398961</v>
+      </c>
+      <c r="D8">
+        <v>124.1929174398961</v>
+      </c>
+      <c r="E8">
+        <v>-27</v>
+      </c>
+      <c r="F8">
+        <v>6.899999999999999</v>
+      </c>
+      <c r="G8">
+        <v>2.77</v>
+      </c>
+      <c r="H8">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>11.5</v>
+      </c>
+      <c r="K8">
+        <v>0.92</v>
+      </c>
+      <c r="L8">
+        <v>10.58</v>
+      </c>
+      <c r="M8">
+        <v>0.31533</v>
+      </c>
+      <c r="N8">
+        <v>10.26467</v>
+      </c>
+      <c r="O8">
+        <v>1.5397005</v>
+      </c>
+      <c r="P8">
+        <v>8.7249695</v>
+      </c>
+      <c r="Q8">
+        <v>9.6449695</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.2355167708496697</v>
+      </c>
+      <c r="T8">
+        <v>1.043225494254179</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.15</v>
+      </c>
+      <c r="W8">
+        <v>0.038845</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>33.55215171407732</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.2234370249449075</v>
+      </c>
+      <c r="C9">
+        <v>119.1008777141799</v>
+      </c>
+      <c r="D9">
+        <v>124.3808777141799</v>
+      </c>
+      <c r="E9">
+        <v>-25.85</v>
+      </c>
+      <c r="F9">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="G9">
+        <v>2.77</v>
+      </c>
+      <c r="H9">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>11.5</v>
+      </c>
+      <c r="K9">
+        <v>0.92</v>
+      </c>
+      <c r="L9">
+        <v>10.58</v>
+      </c>
+      <c r="M9">
+        <v>0.3678850000000001</v>
+      </c>
+      <c r="N9">
+        <v>10.212115</v>
+      </c>
+      <c r="O9">
+        <v>1.53181725</v>
+      </c>
+      <c r="P9">
+        <v>8.680297750000001</v>
+      </c>
+      <c r="Q9">
+        <v>9.600297750000001</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.2373310483278575</v>
+      </c>
+      <c r="T9">
+        <v>1.052846943969532</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.15</v>
+      </c>
+      <c r="W9">
+        <v>0.038845</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>28.75898718349484</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.2231575852911254</v>
+      </c>
+      <c r="C10">
+        <v>118.139407789309</v>
+      </c>
+      <c r="D10">
+        <v>124.569407789309</v>
+      </c>
+      <c r="E10">
+        <v>-24.7</v>
+      </c>
+      <c r="F10">
+        <v>9.200000000000001</v>
+      </c>
+      <c r="G10">
+        <v>2.77</v>
+      </c>
+      <c r="H10">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>11.5</v>
+      </c>
+      <c r="K10">
+        <v>0.92</v>
+      </c>
+      <c r="L10">
+        <v>10.58</v>
+      </c>
+      <c r="M10">
+        <v>0.4204400000000001</v>
+      </c>
+      <c r="N10">
+        <v>10.15956</v>
+      </c>
+      <c r="O10">
+        <v>1.523934</v>
+      </c>
+      <c r="P10">
+        <v>8.635626</v>
+      </c>
+      <c r="Q10">
+        <v>9.555626</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.2391847666207885</v>
+      </c>
+      <c r="T10">
+        <v>1.062677555635218</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.15</v>
+      </c>
+      <c r="W10">
+        <v>0.038845</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>25.16411378555798</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.2228781456373433</v>
+      </c>
+      <c r="C11">
+        <v>117.1785102602404</v>
+      </c>
+      <c r="D11">
+        <v>124.7585102602404</v>
+      </c>
+      <c r="E11">
+        <v>-23.55</v>
+      </c>
+      <c r="F11">
+        <v>10.35</v>
+      </c>
+      <c r="G11">
+        <v>2.77</v>
+      </c>
+      <c r="H11">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>11.5</v>
+      </c>
+      <c r="K11">
+        <v>0.92</v>
+      </c>
+      <c r="L11">
+        <v>10.58</v>
+      </c>
+      <c r="M11">
+        <v>0.4729950000000001</v>
+      </c>
+      <c r="N11">
+        <v>10.107005</v>
+      </c>
+      <c r="O11">
+        <v>1.51605075</v>
+      </c>
+      <c r="P11">
+        <v>8.590954250000001</v>
+      </c>
+      <c r="Q11">
+        <v>9.510954250000001</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.2410792259751026</v>
+      </c>
+      <c r="T11">
+        <v>1.072724224700151</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.15</v>
+      </c>
+      <c r="W11">
+        <v>0.038845</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>22.36810114271821</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.2225987059835613</v>
+      </c>
+      <c r="C12">
+        <v>116.2181877377119</v>
+      </c>
+      <c r="D12">
+        <v>124.9481877377119</v>
+      </c>
+      <c r="E12">
+        <v>-22.4</v>
+      </c>
+      <c r="F12">
+        <v>11.5</v>
+      </c>
+      <c r="G12">
+        <v>2.77</v>
+      </c>
+      <c r="H12">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>11.5</v>
+      </c>
+      <c r="K12">
+        <v>0.92</v>
+      </c>
+      <c r="L12">
+        <v>10.58</v>
+      </c>
+      <c r="M12">
+        <v>0.5255500000000001</v>
+      </c>
+      <c r="N12">
+        <v>10.05445</v>
+      </c>
+      <c r="O12">
+        <v>1.5081675</v>
+      </c>
+      <c r="P12">
+        <v>8.546282499999998</v>
+      </c>
+      <c r="Q12">
+        <v>9.466282499999998</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.2430157844261792</v>
+      </c>
+      <c r="T12">
+        <v>1.082994153077637</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.15</v>
+      </c>
+      <c r="W12">
+        <v>0.038845</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>20.13129102844638</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.2223192663297792</v>
+      </c>
+      <c r="C13">
+        <v>115.2584428483627</v>
+      </c>
+      <c r="D13">
+        <v>125.1384428483627</v>
+      </c>
+      <c r="E13">
+        <v>-21.25</v>
+      </c>
+      <c r="F13">
+        <v>12.65</v>
+      </c>
+      <c r="G13">
+        <v>2.77</v>
+      </c>
+      <c r="H13">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>11.5</v>
+      </c>
+      <c r="K13">
+        <v>0.92</v>
+      </c>
+      <c r="L13">
+        <v>10.58</v>
+      </c>
+      <c r="M13">
+        <v>0.5781050000000001</v>
+      </c>
+      <c r="N13">
+        <v>10.001895</v>
+      </c>
+      <c r="O13">
+        <v>1.50028425</v>
+      </c>
+      <c r="P13">
+        <v>8.501610749999999</v>
+      </c>
+      <c r="Q13">
+        <v>9.421610749999999</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.2449958610446957</v>
+      </c>
+      <c r="T13">
+        <v>1.093494866362483</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.15</v>
+      </c>
+      <c r="W13">
+        <v>0.038845</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>18.30117366222399</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.2220398266759971</v>
+      </c>
+      <c r="C14">
+        <v>114.2992782348543</v>
+      </c>
+      <c r="D14">
+        <v>125.3292782348543</v>
+      </c>
+      <c r="E14">
+        <v>-20.1</v>
+      </c>
+      <c r="F14">
+        <v>13.8</v>
+      </c>
+      <c r="G14">
+        <v>2.77</v>
+      </c>
+      <c r="H14">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>11.5</v>
+      </c>
+      <c r="K14">
+        <v>0.92</v>
+      </c>
+      <c r="L14">
+        <v>10.58</v>
+      </c>
+      <c r="M14">
+        <v>0.63066</v>
+      </c>
+      <c r="N14">
+        <v>9.949339999999999</v>
+      </c>
+      <c r="O14">
+        <v>1.492401</v>
+      </c>
+      <c r="P14">
+        <v>8.456938999999998</v>
+      </c>
+      <c r="Q14">
+        <v>9.376938999999998</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.2470209394045422</v>
+      </c>
+      <c r="T14">
+        <v>1.104234232221984</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.15</v>
+      </c>
+      <c r="W14">
+        <v>0.038845</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>16.77607585703866</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.221760387022215</v>
+      </c>
+      <c r="C15">
+        <v>113.3406965559931</v>
+      </c>
+      <c r="D15">
+        <v>125.5206965559932</v>
+      </c>
+      <c r="E15">
+        <v>-18.95</v>
+      </c>
+      <c r="F15">
+        <v>14.95</v>
+      </c>
+      <c r="G15">
+        <v>2.77</v>
+      </c>
+      <c r="H15">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>11.5</v>
+      </c>
+      <c r="K15">
+        <v>0.92</v>
+      </c>
+      <c r="L15">
+        <v>10.58</v>
+      </c>
+      <c r="M15">
+        <v>0.6832150000000001</v>
+      </c>
+      <c r="N15">
+        <v>9.896784999999999</v>
+      </c>
+      <c r="O15">
+        <v>1.48451775</v>
+      </c>
+      <c r="P15">
+        <v>8.412267249999999</v>
+      </c>
+      <c r="Q15">
+        <v>9.332267249999999</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.2490925712899023</v>
+      </c>
+      <c r="T15">
+        <v>1.115220480055267</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.15</v>
+      </c>
+      <c r="W15">
+        <v>0.038845</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>15.4856084834203</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.221480947368433</v>
+      </c>
+      <c r="C16">
+        <v>112.3827004868538</v>
+      </c>
+      <c r="D16">
+        <v>125.7127004868538</v>
+      </c>
+      <c r="E16">
+        <v>-17.8</v>
+      </c>
+      <c r="F16">
+        <v>16.1</v>
+      </c>
+      <c r="G16">
+        <v>2.77</v>
+      </c>
+      <c r="H16">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>11.5</v>
+      </c>
+      <c r="K16">
+        <v>0.92</v>
+      </c>
+      <c r="L16">
+        <v>10.58</v>
+      </c>
+      <c r="M16">
+        <v>0.7357700000000001</v>
+      </c>
+      <c r="N16">
+        <v>9.84423</v>
+      </c>
+      <c r="O16">
+        <v>1.4766345</v>
+      </c>
+      <c r="P16">
+        <v>8.3675955</v>
+      </c>
+      <c r="Q16">
+        <v>9.2875955</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.2512123806609686</v>
+      </c>
+      <c r="T16">
+        <v>1.126462222024207</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.15</v>
+      </c>
+      <c r="W16">
+        <v>0.038845</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>14.37949359174742</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.2212015077146509</v>
+      </c>
+      <c r="C17">
+        <v>111.4252927189039</v>
+      </c>
+      <c r="D17">
+        <v>125.9052927189039</v>
+      </c>
+      <c r="E17">
+        <v>-16.65</v>
+      </c>
+      <c r="F17">
+        <v>17.25</v>
+      </c>
+      <c r="G17">
+        <v>2.77</v>
+      </c>
+      <c r="H17">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>11.5</v>
+      </c>
+      <c r="K17">
+        <v>0.92</v>
+      </c>
+      <c r="L17">
+        <v>10.58</v>
+      </c>
+      <c r="M17">
+        <v>0.7883250000000001</v>
+      </c>
+      <c r="N17">
+        <v>9.791675</v>
+      </c>
+      <c r="O17">
+        <v>1.46875125</v>
+      </c>
+      <c r="P17">
+        <v>8.322923749999999</v>
+      </c>
+      <c r="Q17">
+        <v>9.242923749999999</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.2533820678995893</v>
+      </c>
+      <c r="T17">
+        <v>1.137968475568888</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.15</v>
+      </c>
+      <c r="W17">
+        <v>0.038845</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>13.42086068563093</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.2211396680608688</v>
+      </c>
+      <c r="C18">
+        <v>110.3179929157062</v>
+      </c>
+      <c r="D18">
+        <v>125.9479929157062</v>
+      </c>
+      <c r="E18">
+        <v>-15.5</v>
+      </c>
+      <c r="F18">
+        <v>18.4</v>
+      </c>
+      <c r="G18">
+        <v>2.77</v>
+      </c>
+      <c r="H18">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>11.5</v>
+      </c>
+      <c r="K18">
+        <v>0.92</v>
+      </c>
+      <c r="L18">
+        <v>10.58</v>
+      </c>
+      <c r="M18">
+        <v>0.8703200000000001</v>
+      </c>
+      <c r="N18">
+        <v>9.709680000000001</v>
+      </c>
+      <c r="O18">
+        <v>1.456452</v>
+      </c>
+      <c r="P18">
+        <v>8.253228</v>
+      </c>
+      <c r="Q18">
+        <v>9.173228</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.2556034143581772</v>
+      </c>
+      <c r="T18">
+        <v>1.149748687531299</v>
+      </c>
+      <c r="U18">
+        <v>0.0473</v>
+      </c>
+      <c r="V18">
+        <v>0.15</v>
+      </c>
+      <c r="W18">
+        <v>0.040205</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>12.15644820295983</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.2208738284070867</v>
+      </c>
+      <c r="C19">
+        <v>109.3518851923952</v>
+      </c>
+      <c r="D19">
+        <v>126.1318851923952</v>
+      </c>
+      <c r="E19">
+        <v>-14.35</v>
+      </c>
+      <c r="F19">
+        <v>19.55</v>
+      </c>
+      <c r="G19">
+        <v>2.77</v>
+      </c>
+      <c r="H19">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>11.5</v>
+      </c>
+      <c r="K19">
+        <v>0.92</v>
+      </c>
+      <c r="L19">
+        <v>10.58</v>
+      </c>
+      <c r="M19">
+        <v>0.9247150000000001</v>
+      </c>
+      <c r="N19">
+        <v>9.655284999999999</v>
+      </c>
+      <c r="O19">
+        <v>1.44829275</v>
+      </c>
+      <c r="P19">
+        <v>8.206992249999999</v>
+      </c>
+      <c r="Q19">
+        <v>9.126992249999999</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.2578782872374539</v>
+      </c>
+      <c r="T19">
+        <v>1.161812760022924</v>
+      </c>
+      <c r="U19">
+        <v>0.0473</v>
+      </c>
+      <c r="V19">
+        <v>0.15</v>
+      </c>
+      <c r="W19">
+        <v>0.040205</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>11.44136301455043</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.2206079887533047</v>
+      </c>
+      <c r="C20">
+        <v>108.3863152436836</v>
+      </c>
+      <c r="D20">
+        <v>126.3163152436836</v>
+      </c>
+      <c r="E20">
+        <v>-13.2</v>
+      </c>
+      <c r="F20">
+        <v>20.7</v>
+      </c>
+      <c r="G20">
+        <v>2.77</v>
+      </c>
+      <c r="H20">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>11.5</v>
+      </c>
+      <c r="K20">
+        <v>0.92</v>
+      </c>
+      <c r="L20">
+        <v>10.58</v>
+      </c>
+      <c r="M20">
+        <v>0.97911</v>
+      </c>
+      <c r="N20">
+        <v>9.60089</v>
+      </c>
+      <c r="O20">
+        <v>1.4401335</v>
+      </c>
+      <c r="P20">
+        <v>8.1607565</v>
+      </c>
+      <c r="Q20">
+        <v>9.0807565</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.2602086448211033</v>
+      </c>
+      <c r="T20">
+        <v>1.174171078185077</v>
+      </c>
+      <c r="U20">
+        <v>0.0473</v>
+      </c>
+      <c r="V20">
+        <v>0.15</v>
+      </c>
+      <c r="W20">
+        <v>0.040205</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>10.80573173596429</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.2209558490995226</v>
+      </c>
+      <c r="C21">
+        <v>106.9950908340868</v>
+      </c>
+      <c r="D21">
+        <v>126.0750908340868</v>
+      </c>
+      <c r="E21">
+        <v>-12.05</v>
+      </c>
+      <c r="F21">
+        <v>21.85</v>
+      </c>
+      <c r="G21">
+        <v>2.77</v>
+      </c>
+      <c r="H21">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>11.5</v>
+      </c>
+      <c r="K21">
+        <v>0.92</v>
+      </c>
+      <c r="L21">
+        <v>10.58</v>
+      </c>
+      <c r="M21">
+        <v>1.116535</v>
+      </c>
+      <c r="N21">
+        <v>9.463464999999999</v>
+      </c>
+      <c r="O21">
+        <v>1.41951975</v>
+      </c>
+      <c r="P21">
+        <v>8.04394525</v>
+      </c>
+      <c r="Q21">
+        <v>8.96394525</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.2625965420981761</v>
+      </c>
+      <c r="T21">
+        <v>1.186834540005555</v>
+      </c>
+      <c r="U21">
+        <v>0.0511</v>
+      </c>
+      <c r="V21">
+        <v>0.15</v>
+      </c>
+      <c r="W21">
+        <v>0.043435</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>9.475744154907817</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.2207223094457405</v>
+      </c>
+      <c r="C22">
+        <v>106.0069375759935</v>
+      </c>
+      <c r="D22">
+        <v>126.2369375759935</v>
+      </c>
+      <c r="E22">
+        <v>-10.9</v>
+      </c>
+      <c r="F22">
+        <v>23</v>
+      </c>
+      <c r="G22">
+        <v>2.77</v>
+      </c>
+      <c r="H22">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>11.5</v>
+      </c>
+      <c r="K22">
+        <v>0.92</v>
+      </c>
+      <c r="L22">
+        <v>10.58</v>
+      </c>
+      <c r="M22">
+        <v>1.1753</v>
+      </c>
+      <c r="N22">
+        <v>9.4047</v>
+      </c>
+      <c r="O22">
+        <v>1.410705</v>
+      </c>
+      <c r="P22">
+        <v>7.993995</v>
+      </c>
+      <c r="Q22">
+        <v>8.913995</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.2650441368071756</v>
+      </c>
+      <c r="T22">
+        <v>1.199814588371545</v>
+      </c>
+      <c r="U22">
+        <v>0.0511</v>
+      </c>
+      <c r="V22">
+        <v>0.15</v>
+      </c>
+      <c r="W22">
+        <v>0.043435</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>9.001956947162427</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.2204887697919585</v>
+      </c>
+      <c r="C23">
+        <v>105.0192003879976</v>
+      </c>
+      <c r="D23">
+        <v>126.3992003879976</v>
+      </c>
+      <c r="E23">
+        <v>-9.75</v>
+      </c>
+      <c r="F23">
+        <v>24.15</v>
+      </c>
+      <c r="G23">
+        <v>2.77</v>
+      </c>
+      <c r="H23">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>11.5</v>
+      </c>
+      <c r="K23">
+        <v>0.92</v>
+      </c>
+      <c r="L23">
+        <v>10.58</v>
+      </c>
+      <c r="M23">
+        <v>1.234065</v>
+      </c>
+      <c r="N23">
+        <v>9.345935000000001</v>
+      </c>
+      <c r="O23">
+        <v>1.40189025</v>
+      </c>
+      <c r="P23">
+        <v>7.944044750000001</v>
+      </c>
+      <c r="Q23">
+        <v>8.864044750000001</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.2675536959391879</v>
+      </c>
+      <c r="T23">
+        <v>1.213123245556927</v>
+      </c>
+      <c r="U23">
+        <v>0.0511</v>
+      </c>
+      <c r="V23">
+        <v>0.15</v>
+      </c>
+      <c r="W23">
+        <v>0.043435</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>8.573292330630883</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.2202552301381764</v>
+      </c>
+      <c r="C24">
+        <v>104.0318808765923</v>
+      </c>
+      <c r="D24">
+        <v>126.5618808765923</v>
+      </c>
+      <c r="E24">
+        <v>-8.599999999999998</v>
+      </c>
+      <c r="F24">
+        <v>25.3</v>
+      </c>
+      <c r="G24">
+        <v>2.77</v>
+      </c>
+      <c r="H24">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>11.5</v>
+      </c>
+      <c r="K24">
+        <v>0.92</v>
+      </c>
+      <c r="L24">
+        <v>10.58</v>
+      </c>
+      <c r="M24">
+        <v>1.29283</v>
+      </c>
+      <c r="N24">
+        <v>9.28717</v>
+      </c>
+      <c r="O24">
+        <v>1.3930755</v>
+      </c>
+      <c r="P24">
+        <v>7.8940945</v>
+      </c>
+      <c r="Q24">
+        <v>8.814094499999999</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.2701276027412518</v>
+      </c>
+      <c r="T24">
+        <v>1.226773150362446</v>
+      </c>
+      <c r="U24">
+        <v>0.0511</v>
+      </c>
+      <c r="V24">
+        <v>0.15</v>
+      </c>
+      <c r="W24">
+        <v>0.043435</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>8.183597224693116</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.2200216904843943</v>
+      </c>
+      <c r="C25">
+        <v>103.044980656552</v>
+      </c>
+      <c r="D25">
+        <v>126.724980656552</v>
+      </c>
+      <c r="E25">
+        <v>-7.449999999999996</v>
+      </c>
+      <c r="F25">
+        <v>26.45</v>
+      </c>
+      <c r="G25">
+        <v>2.77</v>
+      </c>
+      <c r="H25">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>11.5</v>
+      </c>
+      <c r="K25">
+        <v>0.92</v>
+      </c>
+      <c r="L25">
+        <v>10.58</v>
+      </c>
+      <c r="M25">
+        <v>1.351595</v>
+      </c>
+      <c r="N25">
+        <v>9.228405</v>
+      </c>
+      <c r="O25">
+        <v>1.38426075</v>
+      </c>
+      <c r="P25">
+        <v>7.84414425</v>
+      </c>
+      <c r="Q25">
+        <v>8.764144250000001</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.2727683642654471</v>
+      </c>
+      <c r="T25">
+        <v>1.240777598149928</v>
+      </c>
+      <c r="U25">
+        <v>0.0511</v>
+      </c>
+      <c r="V25">
+        <v>0.15</v>
+      </c>
+      <c r="W25">
+        <v>0.043435</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>7.827788649706457</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.2201757508306122</v>
+      </c>
+      <c r="C26">
+        <v>101.7873406092745</v>
+      </c>
+      <c r="D26">
+        <v>126.6173406092745</v>
+      </c>
+      <c r="E26">
+        <v>-6.300000000000001</v>
+      </c>
+      <c r="F26">
+        <v>27.6</v>
+      </c>
+      <c r="G26">
+        <v>2.77</v>
+      </c>
+      <c r="H26">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>11.5</v>
+      </c>
+      <c r="K26">
+        <v>0.92</v>
+      </c>
+      <c r="L26">
+        <v>10.58</v>
+      </c>
+      <c r="M26">
+        <v>1.4628</v>
+      </c>
+      <c r="N26">
+        <v>9.1172</v>
+      </c>
+      <c r="O26">
+        <v>1.36758</v>
+      </c>
+      <c r="P26">
+        <v>7.74962</v>
+      </c>
+      <c r="Q26">
+        <v>8.66962</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.2754786195139635</v>
+      </c>
+      <c r="T26">
+        <v>1.25515058403708</v>
+      </c>
+      <c r="U26">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V26">
+        <v>0.15</v>
+      </c>
+      <c r="W26">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>7.232704402515723</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.2199583611768302</v>
+      </c>
+      <c r="C27">
+        <v>100.78928115267</v>
+      </c>
+      <c r="D27">
+        <v>126.76928115267</v>
+      </c>
+      <c r="E27">
+        <v>-5.149999999999999</v>
+      </c>
+      <c r="F27">
+        <v>28.75</v>
+      </c>
+      <c r="G27">
+        <v>2.77</v>
+      </c>
+      <c r="H27">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>11.5</v>
+      </c>
+      <c r="K27">
+        <v>0.92</v>
+      </c>
+      <c r="L27">
+        <v>10.58</v>
+      </c>
+      <c r="M27">
+        <v>1.52375</v>
+      </c>
+      <c r="N27">
+        <v>9.05625</v>
+      </c>
+      <c r="O27">
+        <v>1.3584375</v>
+      </c>
+      <c r="P27">
+        <v>7.6978125</v>
+      </c>
+      <c r="Q27">
+        <v>8.617812500000001</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.2782611482357735</v>
+      </c>
+      <c r="T27">
+        <v>1.269906849547889</v>
+      </c>
+      <c r="U27">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V27">
+        <v>0.15</v>
+      </c>
+      <c r="W27">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>6.943396226415094</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.2197409715230481</v>
+      </c>
+      <c r="C28">
+        <v>99.79158679084588</v>
+      </c>
+      <c r="D28">
+        <v>126.9215867908459</v>
+      </c>
+      <c r="E28">
+        <v>-3.999999999999996</v>
+      </c>
+      <c r="F28">
+        <v>29.9</v>
+      </c>
+      <c r="G28">
+        <v>2.77</v>
+      </c>
+      <c r="H28">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>11.5</v>
+      </c>
+      <c r="K28">
+        <v>0.92</v>
+      </c>
+      <c r="L28">
+        <v>10.58</v>
+      </c>
+      <c r="M28">
+        <v>1.5847</v>
+      </c>
+      <c r="N28">
+        <v>8.9953</v>
+      </c>
+      <c r="O28">
+        <v>1.349295</v>
+      </c>
+      <c r="P28">
+        <v>7.646005000000001</v>
+      </c>
+      <c r="Q28">
+        <v>8.566005000000001</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.2811188804365515</v>
+      </c>
+      <c r="T28">
+        <v>1.285061933045477</v>
+      </c>
+      <c r="U28">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0.15</v>
+      </c>
+      <c r="W28">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>6.676342525399129</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.219523581869266</v>
+      </c>
+      <c r="C29">
+        <v>98.79425884130298</v>
+      </c>
+      <c r="D29">
+        <v>127.074258841303</v>
+      </c>
+      <c r="E29">
+        <v>-2.849999999999998</v>
+      </c>
+      <c r="F29">
+        <v>31.05</v>
+      </c>
+      <c r="G29">
+        <v>2.77</v>
+      </c>
+      <c r="H29">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>11.5</v>
+      </c>
+      <c r="K29">
+        <v>0.92</v>
+      </c>
+      <c r="L29">
+        <v>10.58</v>
+      </c>
+      <c r="M29">
+        <v>1.64565</v>
+      </c>
+      <c r="N29">
+        <v>8.93435</v>
+      </c>
+      <c r="O29">
+        <v>1.3401525</v>
+      </c>
+      <c r="P29">
+        <v>7.5941975</v>
+      </c>
+      <c r="Q29">
+        <v>8.5141975</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.2840549066702275</v>
+      </c>
+      <c r="T29">
+        <v>1.300632224310122</v>
+      </c>
+      <c r="U29">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V29">
+        <v>0.15</v>
+      </c>
+      <c r="W29">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>6.429070580013976</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.219782192215484</v>
+      </c>
+      <c r="C30">
+        <v>97.46267899815903</v>
+      </c>
+      <c r="D30">
+        <v>126.892678998159</v>
+      </c>
+      <c r="E30">
+        <v>-1.699999999999996</v>
+      </c>
+      <c r="F30">
+        <v>32.2</v>
+      </c>
+      <c r="G30">
+        <v>2.77</v>
+      </c>
+      <c r="H30">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>11.5</v>
+      </c>
+      <c r="K30">
+        <v>0.92</v>
+      </c>
+      <c r="L30">
+        <v>10.58</v>
+      </c>
+      <c r="M30">
+        <v>1.771</v>
+      </c>
+      <c r="N30">
+        <v>8.808999999999999</v>
+      </c>
+      <c r="O30">
+        <v>1.32135</v>
+      </c>
+      <c r="P30">
+        <v>7.487649999999999</v>
+      </c>
+      <c r="Q30">
+        <v>8.40765</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2870724891881722</v>
+      </c>
+      <c r="T30">
+        <v>1.316635023665452</v>
+      </c>
+      <c r="U30">
+        <v>0.055</v>
+      </c>
+      <c r="V30">
+        <v>0.15</v>
+      </c>
+      <c r="W30">
+        <v>0.04675</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>5.974025974025973</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.2195818025617019</v>
+      </c>
+      <c r="C31">
+        <v>96.4533346374524</v>
+      </c>
+      <c r="D31">
+        <v>127.0333346374524</v>
+      </c>
+      <c r="E31">
+        <v>-0.5500000000000043</v>
+      </c>
+      <c r="F31">
+        <v>33.34999999999999</v>
+      </c>
+      <c r="G31">
+        <v>2.77</v>
+      </c>
+      <c r="H31">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>11.5</v>
+      </c>
+      <c r="K31">
+        <v>0.92</v>
+      </c>
+      <c r="L31">
+        <v>10.58</v>
+      </c>
+      <c r="M31">
+        <v>1.83425</v>
+      </c>
+      <c r="N31">
+        <v>8.745750000000001</v>
+      </c>
+      <c r="O31">
+        <v>1.3118625</v>
+      </c>
+      <c r="P31">
+        <v>7.433887500000001</v>
+      </c>
+      <c r="Q31">
+        <v>8.353887500000001</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.290175074030566</v>
+      </c>
+      <c r="T31">
+        <v>1.333088606101214</v>
+      </c>
+      <c r="U31">
+        <v>0.055</v>
+      </c>
+      <c r="V31">
+        <v>0.15</v>
+      </c>
+      <c r="W31">
+        <v>0.04675</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>5.768025078369908</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.2193814129079198</v>
+      </c>
+      <c r="C32">
+        <v>95.4443024454724</v>
+      </c>
+      <c r="D32">
+        <v>127.1743024454724</v>
+      </c>
+      <c r="E32">
+        <v>0.6000000000000014</v>
+      </c>
+      <c r="F32">
+        <v>34.5</v>
+      </c>
+      <c r="G32">
+        <v>2.77</v>
+      </c>
+      <c r="H32">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>11.5</v>
+      </c>
+      <c r="K32">
+        <v>0.92</v>
+      </c>
+      <c r="L32">
+        <v>10.58</v>
+      </c>
+      <c r="M32">
+        <v>1.8975</v>
+      </c>
+      <c r="N32">
+        <v>8.682500000000001</v>
+      </c>
+      <c r="O32">
+        <v>1.302375</v>
+      </c>
+      <c r="P32">
+        <v>7.380125</v>
+      </c>
+      <c r="Q32">
+        <v>8.300125000000001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2933663041541711</v>
+      </c>
+      <c r="T32">
+        <v>1.350012290892283</v>
+      </c>
+      <c r="U32">
+        <v>0.055</v>
+      </c>
+      <c r="V32">
+        <v>0.15</v>
+      </c>
+      <c r="W32">
+        <v>0.04675</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>5.575757575757576</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.2191810232541377</v>
+      </c>
+      <c r="C33">
+        <v>94.43558346260644</v>
+      </c>
+      <c r="D33">
+        <v>127.3155834626065</v>
+      </c>
+      <c r="E33">
+        <v>1.75</v>
+      </c>
+      <c r="F33">
+        <v>35.65</v>
+      </c>
+      <c r="G33">
+        <v>2.77</v>
+      </c>
+      <c r="H33">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>11.5</v>
+      </c>
+      <c r="K33">
+        <v>0.92</v>
+      </c>
+      <c r="L33">
+        <v>10.58</v>
+      </c>
+      <c r="M33">
+        <v>1.96075</v>
+      </c>
+      <c r="N33">
+        <v>8.619250000000001</v>
+      </c>
+      <c r="O33">
+        <v>1.2928875</v>
+      </c>
+      <c r="P33">
+        <v>7.3263625</v>
+      </c>
+      <c r="Q33">
+        <v>8.2463625</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2966500337016489</v>
+      </c>
+      <c r="T33">
+        <v>1.367426517271499</v>
+      </c>
+      <c r="U33">
+        <v>0.055</v>
+      </c>
+      <c r="V33">
+        <v>0.15</v>
+      </c>
+      <c r="W33">
+        <v>0.04675</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>5.395894428152493</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.2189806336003556</v>
+      </c>
+      <c r="C34">
+        <v>93.42717873387028</v>
+      </c>
+      <c r="D34">
+        <v>127.4571787338703</v>
+      </c>
+      <c r="E34">
+        <v>2.900000000000006</v>
+      </c>
+      <c r="F34">
+        <v>36.8</v>
+      </c>
+      <c r="G34">
+        <v>2.77</v>
+      </c>
+      <c r="H34">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>11.5</v>
+      </c>
+      <c r="K34">
+        <v>0.92</v>
+      </c>
+      <c r="L34">
+        <v>10.58</v>
+      </c>
+      <c r="M34">
+        <v>2.024</v>
+      </c>
+      <c r="N34">
+        <v>8.555999999999999</v>
+      </c>
+      <c r="O34">
+        <v>1.2834</v>
+      </c>
+      <c r="P34">
+        <v>7.272599999999999</v>
+      </c>
+      <c r="Q34">
+        <v>8.192599999999999</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.3000303435299348</v>
+      </c>
+      <c r="T34">
+        <v>1.385352926779515</v>
+      </c>
+      <c r="U34">
+        <v>0.055</v>
+      </c>
+      <c r="V34">
+        <v>0.15</v>
+      </c>
+      <c r="W34">
+        <v>0.04675</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>5.227272727272726</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2187802439465736</v>
+      </c>
+      <c r="C35">
+        <v>92.41908930893375</v>
+      </c>
+      <c r="D35">
+        <v>127.5990893089338</v>
+      </c>
+      <c r="E35">
+        <v>4.050000000000004</v>
+      </c>
+      <c r="F35">
+        <v>37.95</v>
+      </c>
+      <c r="G35">
+        <v>2.77</v>
+      </c>
+      <c r="H35">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>11.5</v>
+      </c>
+      <c r="K35">
+        <v>0.92</v>
+      </c>
+      <c r="L35">
+        <v>10.58</v>
+      </c>
+      <c r="M35">
+        <v>2.08725</v>
+      </c>
+      <c r="N35">
+        <v>8.492750000000001</v>
+      </c>
+      <c r="O35">
+        <v>1.2739125</v>
+      </c>
+      <c r="P35">
+        <v>7.218837500000001</v>
+      </c>
+      <c r="Q35">
+        <v>8.138837500000001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.3035115581292143</v>
+      </c>
+      <c r="T35">
+        <v>1.403814452989264</v>
+      </c>
+      <c r="U35">
+        <v>0.055</v>
+      </c>
+      <c r="V35">
+        <v>0.15</v>
+      </c>
+      <c r="W35">
+        <v>0.04675</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>5.068870523415979</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2185798542927915</v>
+      </c>
+      <c r="C36">
+        <v>91.41131624214668</v>
+      </c>
+      <c r="D36">
+        <v>127.7413162421467</v>
+      </c>
+      <c r="E36">
+        <v>5.200000000000003</v>
+      </c>
+      <c r="F36">
+        <v>39.1</v>
+      </c>
+      <c r="G36">
+        <v>2.77</v>
+      </c>
+      <c r="H36">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>11.5</v>
+      </c>
+      <c r="K36">
+        <v>0.92</v>
+      </c>
+      <c r="L36">
+        <v>10.58</v>
+      </c>
+      <c r="M36">
+        <v>2.1505</v>
+      </c>
+      <c r="N36">
+        <v>8.429500000000001</v>
+      </c>
+      <c r="O36">
+        <v>1.264425</v>
+      </c>
+      <c r="P36">
+        <v>7.165075000000001</v>
+      </c>
+      <c r="Q36">
+        <v>8.085075000000002</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.3070982640799871</v>
+      </c>
+      <c r="T36">
+        <v>1.422835419387186</v>
+      </c>
+      <c r="U36">
+        <v>0.055</v>
+      </c>
+      <c r="V36">
+        <v>0.15</v>
+      </c>
+      <c r="W36">
+        <v>0.04675</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>4.919786096256685</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2183794646390094</v>
+      </c>
+      <c r="C37">
+        <v>90.40386059256494</v>
+      </c>
+      <c r="D37">
+        <v>127.8838605925649</v>
+      </c>
+      <c r="E37">
+        <v>6.350000000000009</v>
+      </c>
+      <c r="F37">
+        <v>40.25000000000001</v>
+      </c>
+      <c r="G37">
+        <v>2.77</v>
+      </c>
+      <c r="H37">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>11.5</v>
+      </c>
+      <c r="K37">
+        <v>0.92</v>
+      </c>
+      <c r="L37">
+        <v>10.58</v>
+      </c>
+      <c r="M37">
+        <v>2.213750000000001</v>
+      </c>
+      <c r="N37">
+        <v>8.366249999999999</v>
+      </c>
+      <c r="O37">
+        <v>1.2549375</v>
+      </c>
+      <c r="P37">
+        <v>7.111312499999999</v>
+      </c>
+      <c r="Q37">
+        <v>8.031312499999999</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.3107953302138607</v>
+      </c>
+      <c r="T37">
+        <v>1.442441646289661</v>
+      </c>
+      <c r="U37">
+        <v>0.055</v>
+      </c>
+      <c r="V37">
+        <v>0.15</v>
+      </c>
+      <c r="W37">
+        <v>0.04675</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>4.779220779220777</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2181790749852274</v>
+      </c>
+      <c r="C38">
+        <v>89.39672342397694</v>
+      </c>
+      <c r="D38">
+        <v>128.0267234239769</v>
+      </c>
+      <c r="E38">
+        <v>7.5</v>
+      </c>
+      <c r="F38">
+        <v>41.4</v>
+      </c>
+      <c r="G38">
+        <v>2.77</v>
+      </c>
+      <c r="H38">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>11.5</v>
+      </c>
+      <c r="K38">
+        <v>0.92</v>
+      </c>
+      <c r="L38">
+        <v>10.58</v>
+      </c>
+      <c r="M38">
+        <v>2.277</v>
+      </c>
+      <c r="N38">
+        <v>8.303000000000001</v>
+      </c>
+      <c r="O38">
+        <v>1.24545</v>
+      </c>
+      <c r="P38">
+        <v>7.057550000000001</v>
+      </c>
+      <c r="Q38">
+        <v>7.977550000000001</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.3146079296644178</v>
+      </c>
+      <c r="T38">
+        <v>1.462660567782837</v>
+      </c>
+      <c r="U38">
+        <v>0.055</v>
+      </c>
+      <c r="V38">
+        <v>0.15</v>
+      </c>
+      <c r="W38">
+        <v>0.04675</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>4.646464646464647</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2179786853314453</v>
+      </c>
+      <c r="C39">
+        <v>88.38990580492994</v>
+      </c>
+      <c r="D39">
+        <v>128.1699058049299</v>
+      </c>
+      <c r="E39">
+        <v>8.649999999999999</v>
+      </c>
+      <c r="F39">
+        <v>42.55</v>
+      </c>
+      <c r="G39">
+        <v>2.77</v>
+      </c>
+      <c r="H39">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>11.5</v>
+      </c>
+      <c r="K39">
+        <v>0.92</v>
+      </c>
+      <c r="L39">
+        <v>10.58</v>
+      </c>
+      <c r="M39">
+        <v>2.34025</v>
+      </c>
+      <c r="N39">
+        <v>8.239750000000001</v>
+      </c>
+      <c r="O39">
+        <v>1.2359625</v>
+      </c>
+      <c r="P39">
+        <v>7.0037875</v>
+      </c>
+      <c r="Q39">
+        <v>7.9237875</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.3185415640181671</v>
+      </c>
+      <c r="T39">
+        <v>1.483521359799606</v>
+      </c>
+      <c r="U39">
+        <v>0.055</v>
+      </c>
+      <c r="V39">
+        <v>0.15</v>
+      </c>
+      <c r="W39">
+        <v>0.04675</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>4.520884520884522</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2190056956776632</v>
+      </c>
+      <c r="C40">
+        <v>86.5094526478283</v>
+      </c>
+      <c r="D40">
+        <v>127.4394526478283</v>
+      </c>
+      <c r="E40">
+        <v>9.800000000000004</v>
+      </c>
+      <c r="F40">
+        <v>43.7</v>
+      </c>
+      <c r="G40">
+        <v>2.77</v>
+      </c>
+      <c r="H40">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>11.5</v>
+      </c>
+      <c r="K40">
+        <v>0.92</v>
+      </c>
+      <c r="L40">
+        <v>10.58</v>
+      </c>
+      <c r="M40">
+        <v>2.569560000000001</v>
+      </c>
+      <c r="N40">
+        <v>8.010439999999999</v>
+      </c>
+      <c r="O40">
+        <v>1.201566</v>
+      </c>
+      <c r="P40">
+        <v>6.808873999999999</v>
+      </c>
+      <c r="Q40">
+        <v>7.728873999999999</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.3226020898026826</v>
+      </c>
+      <c r="T40">
+        <v>1.50505508059111</v>
+      </c>
+      <c r="U40">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V40">
+        <v>0.15</v>
+      </c>
+      <c r="W40">
+        <v>0.04998</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>4.117436448263515</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2188376060238811</v>
+      </c>
+      <c r="C41">
+        <v>85.47843475354969</v>
+      </c>
+      <c r="D41">
+        <v>127.5584347535497</v>
+      </c>
+      <c r="E41">
+        <v>10.95</v>
+      </c>
+      <c r="F41">
+        <v>44.85</v>
+      </c>
+      <c r="G41">
+        <v>2.77</v>
+      </c>
+      <c r="H41">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>11.5</v>
+      </c>
+      <c r="K41">
+        <v>0.92</v>
+      </c>
+      <c r="L41">
+        <v>10.58</v>
+      </c>
+      <c r="M41">
+        <v>2.63718</v>
+      </c>
+      <c r="N41">
+        <v>7.942819999999999</v>
+      </c>
+      <c r="O41">
+        <v>1.191423</v>
+      </c>
+      <c r="P41">
+        <v>6.751396999999999</v>
+      </c>
+      <c r="Q41">
+        <v>7.671396999999999</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.326795747580133</v>
+      </c>
+      <c r="T41">
+        <v>1.527294825015121</v>
+      </c>
+      <c r="U41">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V41">
+        <v>0.15</v>
+      </c>
+      <c r="W41">
+        <v>0.04998</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>4.011861154718297</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2200975163700991</v>
+      </c>
+      <c r="C42">
+        <v>83.44197919193411</v>
+      </c>
+      <c r="D42">
+        <v>126.6719791919341</v>
+      </c>
+      <c r="E42">
+        <v>12.1</v>
+      </c>
+      <c r="F42">
+        <v>46</v>
+      </c>
+      <c r="G42">
+        <v>2.77</v>
+      </c>
+      <c r="H42">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>11.5</v>
+      </c>
+      <c r="K42">
+        <v>0.92</v>
+      </c>
+      <c r="L42">
+        <v>10.58</v>
+      </c>
+      <c r="M42">
+        <v>2.898</v>
+      </c>
+      <c r="N42">
+        <v>7.682</v>
+      </c>
+      <c r="O42">
+        <v>1.1523</v>
+      </c>
+      <c r="P42">
+        <v>6.5297</v>
+      </c>
+      <c r="Q42">
+        <v>7.4497</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.3311291939501652</v>
+      </c>
+      <c r="T42">
+        <v>1.550275894253268</v>
+      </c>
+      <c r="U42">
+        <v>0.063</v>
+      </c>
+      <c r="V42">
+        <v>0.15</v>
+      </c>
+      <c r="W42">
+        <v>0.05355</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>3.650793650793651</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.219965126716317</v>
+      </c>
+      <c r="C43">
+        <v>82.38454700436617</v>
+      </c>
+      <c r="D43">
+        <v>126.7645470043662</v>
+      </c>
+      <c r="E43">
+        <v>13.25000000000001</v>
+      </c>
+      <c r="F43">
+        <v>47.15000000000001</v>
+      </c>
+      <c r="G43">
+        <v>2.77</v>
+      </c>
+      <c r="H43">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>11.5</v>
+      </c>
+      <c r="K43">
+        <v>0.92</v>
+      </c>
+      <c r="L43">
+        <v>10.58</v>
+      </c>
+      <c r="M43">
+        <v>2.97045</v>
+      </c>
+      <c r="N43">
+        <v>7.60955</v>
+      </c>
+      <c r="O43">
+        <v>1.1414325</v>
+      </c>
+      <c r="P43">
+        <v>6.4681175</v>
+      </c>
+      <c r="Q43">
+        <v>7.3881175</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.335609536807317</v>
+      </c>
+      <c r="T43">
+        <v>1.574035982787622</v>
+      </c>
+      <c r="U43">
+        <v>0.063</v>
+      </c>
+      <c r="V43">
+        <v>0.15</v>
+      </c>
+      <c r="W43">
+        <v>0.05355</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>3.561749903213317</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.222367437062535</v>
+      </c>
+      <c r="C44">
+        <v>79.57560472312446</v>
+      </c>
+      <c r="D44">
+        <v>125.1056047231245</v>
+      </c>
+      <c r="E44">
+        <v>14.4</v>
+      </c>
+      <c r="F44">
+        <v>48.3</v>
+      </c>
+      <c r="G44">
+        <v>2.77</v>
+      </c>
+      <c r="H44">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>11.5</v>
+      </c>
+      <c r="K44">
+        <v>0.92</v>
+      </c>
+      <c r="L44">
+        <v>10.58</v>
+      </c>
+      <c r="M44">
+        <v>3.385829999999999</v>
+      </c>
+      <c r="N44">
+        <v>7.194170000000001</v>
+      </c>
+      <c r="O44">
+        <v>1.0791255</v>
+      </c>
+      <c r="P44">
+        <v>6.115044500000001</v>
+      </c>
+      <c r="Q44">
+        <v>7.035044500000001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.3402443742457499</v>
+      </c>
+      <c r="T44">
+        <v>1.598615384719712</v>
+      </c>
+      <c r="U44">
+        <v>0.0701</v>
+      </c>
+      <c r="V44">
+        <v>0.15</v>
+      </c>
+      <c r="W44">
+        <v>0.05958499999999999</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>3.124787718225665</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2222953974087529</v>
+      </c>
+      <c r="C45">
+        <v>78.47472074770994</v>
+      </c>
+      <c r="D45">
+        <v>125.1547207477099</v>
+      </c>
+      <c r="E45">
+        <v>15.55</v>
+      </c>
+      <c r="F45">
+        <v>49.45</v>
+      </c>
+      <c r="G45">
+        <v>2.77</v>
+      </c>
+      <c r="H45">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>11.5</v>
+      </c>
+      <c r="K45">
+        <v>0.92</v>
+      </c>
+      <c r="L45">
+        <v>10.58</v>
+      </c>
+      <c r="M45">
+        <v>3.466444999999999</v>
+      </c>
+      <c r="N45">
+        <v>7.113555000000001</v>
+      </c>
+      <c r="O45">
+        <v>1.06703325</v>
+      </c>
+      <c r="P45">
+        <v>6.04652175</v>
+      </c>
+      <c r="Q45">
+        <v>6.96652175</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.3450418375592155</v>
+      </c>
+      <c r="T45">
+        <v>1.624057221807314</v>
+      </c>
+      <c r="U45">
+        <v>0.0701</v>
+      </c>
+      <c r="V45">
+        <v>0.15</v>
+      </c>
+      <c r="W45">
+        <v>0.05958499999999999</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>3.052118236406463</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2301895577549708</v>
+      </c>
+      <c r="C46">
+        <v>72.16251939640401</v>
+      </c>
+      <c r="D46">
+        <v>119.992519396404</v>
+      </c>
+      <c r="E46">
+        <v>16.7</v>
+      </c>
+      <c r="F46">
+        <v>50.6</v>
+      </c>
+      <c r="G46">
+        <v>2.77</v>
+      </c>
+      <c r="H46">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>11.5</v>
+      </c>
+      <c r="K46">
+        <v>0.92</v>
+      </c>
+      <c r="L46">
+        <v>10.58</v>
+      </c>
+      <c r="M46">
+        <v>4.624840000000001</v>
+      </c>
+      <c r="N46">
+        <v>5.955159999999999</v>
+      </c>
+      <c r="O46">
+        <v>0.893274</v>
+      </c>
+      <c r="P46">
+        <v>5.061885999999999</v>
+      </c>
+      <c r="Q46">
+        <v>5.981885999999999</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.3500106388481621</v>
+      </c>
+      <c r="T46">
+        <v>1.650407695933759</v>
+      </c>
+      <c r="U46">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V46">
+        <v>0.15</v>
+      </c>
+      <c r="W46">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>2.287646707777999</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2302985681011887</v>
+      </c>
+      <c r="C47">
+        <v>70.94421378862504</v>
+      </c>
+      <c r="D47">
+        <v>119.924213788625</v>
+      </c>
+      <c r="E47">
+        <v>17.85</v>
+      </c>
+      <c r="F47">
+        <v>51.75</v>
+      </c>
+      <c r="G47">
+        <v>2.77</v>
+      </c>
+      <c r="H47">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>11.5</v>
+      </c>
+      <c r="K47">
+        <v>0.92</v>
+      </c>
+      <c r="L47">
+        <v>10.58</v>
+      </c>
+      <c r="M47">
+        <v>4.729950000000001</v>
+      </c>
+      <c r="N47">
+        <v>5.85005</v>
+      </c>
+      <c r="O47">
+        <v>0.8775075000000001</v>
+      </c>
+      <c r="P47">
+        <v>4.972542499999999</v>
+      </c>
+      <c r="Q47">
+        <v>5.892542499999999</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.3551601238203431</v>
+      </c>
+      <c r="T47">
+        <v>1.677716369119348</v>
+      </c>
+      <c r="U47">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V47">
+        <v>0.15</v>
+      </c>
+      <c r="W47">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>2.236810114271821</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2304075784474066</v>
+      </c>
+      <c r="C48">
+        <v>69.72598590238513</v>
+      </c>
+      <c r="D48">
+        <v>119.8559859023851</v>
+      </c>
+      <c r="E48">
+        <v>19.00000000000001</v>
+      </c>
+      <c r="F48">
+        <v>52.90000000000001</v>
+      </c>
+      <c r="G48">
+        <v>2.77</v>
+      </c>
+      <c r="H48">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>11.5</v>
+      </c>
+      <c r="K48">
+        <v>0.92</v>
+      </c>
+      <c r="L48">
+        <v>10.58</v>
+      </c>
+      <c r="M48">
+        <v>4.835060000000001</v>
+      </c>
+      <c r="N48">
+        <v>5.744939999999999</v>
+      </c>
+      <c r="O48">
+        <v>0.861741</v>
+      </c>
+      <c r="P48">
+        <v>4.883198999999999</v>
+      </c>
+      <c r="Q48">
+        <v>5.803198999999998</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.3605003304581604</v>
+      </c>
+      <c r="T48">
+        <v>1.706036474645144</v>
+      </c>
+      <c r="U48">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V48">
+        <v>0.15</v>
+      </c>
+      <c r="W48">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>2.188183807439824</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2305165887936246</v>
+      </c>
+      <c r="C49">
+        <v>68.50783560510658</v>
+      </c>
+      <c r="D49">
+        <v>119.7878356051066</v>
+      </c>
+      <c r="E49">
+        <v>20.15000000000001</v>
+      </c>
+      <c r="F49">
+        <v>54.05</v>
+      </c>
+      <c r="G49">
+        <v>2.77</v>
+      </c>
+      <c r="H49">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>11.5</v>
+      </c>
+      <c r="K49">
+        <v>0.92</v>
+      </c>
+      <c r="L49">
+        <v>10.58</v>
+      </c>
+      <c r="M49">
+        <v>4.940170000000001</v>
+      </c>
+      <c r="N49">
+        <v>5.639829999999999</v>
+      </c>
+      <c r="O49">
+        <v>0.8459745</v>
+      </c>
+      <c r="P49">
+        <v>4.793855499999999</v>
+      </c>
+      <c r="Q49">
+        <v>5.713855499999999</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.3660420543275935</v>
+      </c>
+      <c r="T49">
+        <v>1.735425263398328</v>
+      </c>
+      <c r="U49">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V49">
+        <v>0.15</v>
+      </c>
+      <c r="W49">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>2.141626705153871</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2306255991398425</v>
+      </c>
+      <c r="C50">
+        <v>67.28976276451306</v>
+      </c>
+      <c r="D50">
+        <v>119.719762764513</v>
+      </c>
+      <c r="E50">
+        <v>21.3</v>
+      </c>
+      <c r="F50">
+        <v>55.2</v>
+      </c>
+      <c r="G50">
+        <v>2.77</v>
+      </c>
+      <c r="H50">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>11.5</v>
+      </c>
+      <c r="K50">
+        <v>0.92</v>
+      </c>
+      <c r="L50">
+        <v>10.58</v>
+      </c>
+      <c r="M50">
+        <v>5.04528</v>
+      </c>
+      <c r="N50">
+        <v>5.53472</v>
+      </c>
+      <c r="O50">
+        <v>0.8302080000000002</v>
+      </c>
+      <c r="P50">
+        <v>4.704512</v>
+      </c>
+      <c r="Q50">
+        <v>5.624512</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.371796921422774</v>
+      </c>
+      <c r="T50">
+        <v>1.765944390180481</v>
+      </c>
+      <c r="U50">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V50">
+        <v>0.15</v>
+      </c>
+      <c r="W50">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>2.097009482129832</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2307346094860604</v>
+      </c>
+      <c r="C51">
+        <v>66.07176724862862</v>
+      </c>
+      <c r="D51">
+        <v>119.6517672486286</v>
+      </c>
+      <c r="E51">
+        <v>22.45</v>
+      </c>
+      <c r="F51">
+        <v>56.35</v>
+      </c>
+      <c r="G51">
+        <v>2.77</v>
+      </c>
+      <c r="H51">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>11.5</v>
+      </c>
+      <c r="K51">
+        <v>0.92</v>
+      </c>
+      <c r="L51">
+        <v>10.58</v>
+      </c>
+      <c r="M51">
+        <v>5.150390000000001</v>
+      </c>
+      <c r="N51">
+        <v>5.429609999999999</v>
+      </c>
+      <c r="O51">
+        <v>0.8144415</v>
+      </c>
+      <c r="P51">
+        <v>4.615168499999999</v>
+      </c>
+      <c r="Q51">
+        <v>5.535168499999999</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.3777774695805106</v>
+      </c>
+      <c r="T51">
+        <v>1.797660345463895</v>
+      </c>
+      <c r="U51">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V51">
+        <v>0.15</v>
+      </c>
+      <c r="W51">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>2.054213370249631</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2308436198322784</v>
+      </c>
+      <c r="C52">
+        <v>64.85384892577697</v>
+      </c>
+      <c r="D52">
+        <v>119.583848925777</v>
+      </c>
+      <c r="E52">
+        <v>23.6</v>
+      </c>
+      <c r="F52">
+        <v>57.5</v>
+      </c>
+      <c r="G52">
+        <v>2.77</v>
+      </c>
+      <c r="H52">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>11.5</v>
+      </c>
+      <c r="K52">
+        <v>0.92</v>
+      </c>
+      <c r="L52">
+        <v>10.58</v>
+      </c>
+      <c r="M52">
+        <v>5.255500000000001</v>
+      </c>
+      <c r="N52">
+        <v>5.3245</v>
+      </c>
+      <c r="O52">
+        <v>0.798675</v>
+      </c>
+      <c r="P52">
+        <v>4.525824999999999</v>
+      </c>
+      <c r="Q52">
+        <v>5.445824999999999</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.3839972396645567</v>
+      </c>
+      <c r="T52">
+        <v>1.830644938958646</v>
+      </c>
+      <c r="U52">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V52">
+        <v>0.15</v>
+      </c>
+      <c r="W52">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>2.013129102844639</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2400994801784962</v>
+      </c>
+      <c r="C53">
+        <v>58.20531805854005</v>
+      </c>
+      <c r="D53">
+        <v>114.0853180585401</v>
+      </c>
+      <c r="E53">
+        <v>24.75</v>
+      </c>
+      <c r="F53">
+        <v>58.65</v>
+      </c>
+      <c r="G53">
+        <v>2.77</v>
+      </c>
+      <c r="H53">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>11.5</v>
+      </c>
+      <c r="K53">
+        <v>0.92</v>
+      </c>
+      <c r="L53">
+        <v>10.58</v>
+      </c>
+      <c r="M53">
+        <v>6.598125</v>
+      </c>
+      <c r="N53">
+        <v>3.981875</v>
+      </c>
+      <c r="O53">
+        <v>0.5972812500000002</v>
+      </c>
+      <c r="P53">
+        <v>3.384593750000001</v>
+      </c>
+      <c r="Q53">
+        <v>4.30459375</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.3904708779152985</v>
+      </c>
+      <c r="T53">
+        <v>1.864975842391957</v>
+      </c>
+      <c r="U53">
+        <v>0.1125</v>
+      </c>
+      <c r="V53">
+        <v>0.15</v>
+      </c>
+      <c r="W53">
+        <v>0.095625</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>1.603485838779957</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2403878405247142</v>
+      </c>
+      <c r="C54">
+        <v>56.89212527008555</v>
+      </c>
+      <c r="D54">
+        <v>113.9221252700856</v>
+      </c>
+      <c r="E54">
+        <v>25.90000000000001</v>
+      </c>
+      <c r="F54">
+        <v>59.8</v>
+      </c>
+      <c r="G54">
+        <v>2.77</v>
+      </c>
+      <c r="H54">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>11.5</v>
+      </c>
+      <c r="K54">
+        <v>0.92</v>
+      </c>
+      <c r="L54">
+        <v>10.58</v>
+      </c>
+      <c r="M54">
+        <v>6.727500000000001</v>
+      </c>
+      <c r="N54">
+        <v>3.852499999999999</v>
+      </c>
+      <c r="O54">
+        <v>0.5778749999999999</v>
+      </c>
+      <c r="P54">
+        <v>3.274624999999999</v>
+      </c>
+      <c r="Q54">
+        <v>4.194624999999999</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.3972142510931546</v>
+      </c>
+      <c r="T54">
+        <v>1.90073720013499</v>
+      </c>
+      <c r="U54">
+        <v>0.1125</v>
+      </c>
+      <c r="V54">
+        <v>0.15</v>
+      </c>
+      <c r="W54">
+        <v>0.095625</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>1.572649572649572</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2406762008709321</v>
+      </c>
+      <c r="C55">
+        <v>55.57939869140498</v>
+      </c>
+      <c r="D55">
+        <v>113.759398691405</v>
+      </c>
+      <c r="E55">
+        <v>27.05</v>
+      </c>
+      <c r="F55">
+        <v>60.95</v>
+      </c>
+      <c r="G55">
+        <v>2.77</v>
+      </c>
+      <c r="H55">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>11.5</v>
+      </c>
+      <c r="K55">
+        <v>0.92</v>
+      </c>
+      <c r="L55">
+        <v>10.58</v>
+      </c>
+      <c r="M55">
+        <v>6.856875</v>
+      </c>
+      <c r="N55">
+        <v>3.723125</v>
+      </c>
+      <c r="O55">
+        <v>0.5584687500000001</v>
+      </c>
+      <c r="P55">
+        <v>3.164656249999999</v>
+      </c>
+      <c r="Q55">
+        <v>4.084656249999999</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.4042445763211321</v>
+      </c>
+      <c r="T55">
+        <v>1.938020317781982</v>
+      </c>
+      <c r="U55">
+        <v>0.1125</v>
+      </c>
+      <c r="V55">
+        <v>0.15</v>
+      </c>
+      <c r="W55">
+        <v>0.095625</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>1.542976939203354</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2409645612171501</v>
+      </c>
+      <c r="C56">
+        <v>54.26713632754306</v>
+      </c>
+      <c r="D56">
+        <v>113.5971363275431</v>
+      </c>
+      <c r="E56">
+        <v>28.2</v>
+      </c>
+      <c r="F56">
+        <v>62.1</v>
+      </c>
+      <c r="G56">
+        <v>2.77</v>
+      </c>
+      <c r="H56">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>11.5</v>
+      </c>
+      <c r="K56">
+        <v>0.92</v>
+      </c>
+      <c r="L56">
+        <v>10.58</v>
+      </c>
+      <c r="M56">
+        <v>6.98625</v>
+      </c>
+      <c r="N56">
+        <v>3.59375</v>
+      </c>
+      <c r="O56">
+        <v>0.5390625000000001</v>
+      </c>
+      <c r="P56">
+        <v>3.0546875</v>
+      </c>
+      <c r="Q56">
+        <v>3.9746875</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.4115805678633697</v>
+      </c>
+      <c r="T56">
+        <v>1.97692444054406</v>
+      </c>
+      <c r="U56">
+        <v>0.1125</v>
+      </c>
+      <c r="V56">
+        <v>0.15</v>
+      </c>
+      <c r="W56">
+        <v>0.095625</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>1.51440329218107</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2852855195366665</v>
+      </c>
+      <c r="C57">
+        <v>32.69105225634267</v>
+      </c>
+      <c r="D57">
+        <v>93.17105225634268</v>
+      </c>
+      <c r="E57">
+        <v>29.35000000000001</v>
+      </c>
+      <c r="F57">
+        <v>63.25000000000001</v>
+      </c>
+      <c r="G57">
+        <v>2.77</v>
+      </c>
+      <c r="H57">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>11.5</v>
+      </c>
+      <c r="K57">
+        <v>0.92</v>
+      </c>
+      <c r="L57">
+        <v>10.58</v>
+      </c>
+      <c r="M57">
+        <v>12.43495</v>
+      </c>
+      <c r="N57">
+        <v>-1.854950000000001</v>
+      </c>
+      <c r="O57">
+        <v>-0.2782425000000001</v>
+      </c>
+      <c r="P57">
+        <v>-1.5767075</v>
+      </c>
+      <c r="Q57">
+        <v>-0.6567075000000003</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.42434559897037</v>
+      </c>
+      <c r="T57">
+        <v>2.044619766307348</v>
+      </c>
+      <c r="U57">
+        <v>0.1966</v>
+      </c>
+      <c r="V57">
+        <v>0.1276241561083881</v>
+      </c>
+      <c r="W57">
+        <v>0.1715090909090909</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.8508277073892536</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2868635195366664</v>
+      </c>
+      <c r="C58">
+        <v>30.94836567052336</v>
+      </c>
+      <c r="D58">
+        <v>92.57836567052337</v>
+      </c>
+      <c r="E58">
+        <v>30.50000000000001</v>
+      </c>
+      <c r="F58">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="G58">
+        <v>2.77</v>
+      </c>
+      <c r="H58">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>11.5</v>
+      </c>
+      <c r="K58">
+        <v>0.92</v>
+      </c>
+      <c r="L58">
+        <v>10.58</v>
+      </c>
+      <c r="M58">
+        <v>12.66104</v>
+      </c>
+      <c r="N58">
+        <v>-2.081040000000002</v>
+      </c>
+      <c r="O58">
+        <v>-0.3121560000000003</v>
+      </c>
+      <c r="P58">
+        <v>-1.768884000000001</v>
+      </c>
+      <c r="Q58">
+        <v>-0.8488840000000012</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.4331079989469692</v>
+      </c>
+      <c r="T58">
+        <v>2.091088397359787</v>
+      </c>
+      <c r="U58">
+        <v>0.1966</v>
+      </c>
+      <c r="V58">
+        <v>0.1253451533207383</v>
+      </c>
+      <c r="W58">
+        <v>0.1719571428571429</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.8356343554715884</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2884415195366665</v>
+      </c>
+      <c r="C59">
+        <v>29.21317190428113</v>
+      </c>
+      <c r="D59">
+        <v>91.99317190428114</v>
+      </c>
+      <c r="E59">
+        <v>31.65000000000001</v>
+      </c>
+      <c r="F59">
+        <v>65.55000000000001</v>
+      </c>
+      <c r="G59">
+        <v>2.77</v>
+      </c>
+      <c r="H59">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>11.5</v>
+      </c>
+      <c r="K59">
+        <v>0.92</v>
+      </c>
+      <c r="L59">
+        <v>10.58</v>
+      </c>
+      <c r="M59">
+        <v>12.88713</v>
+      </c>
+      <c r="N59">
+        <v>-2.307130000000003</v>
+      </c>
+      <c r="O59">
+        <v>-0.3460695000000004</v>
+      </c>
+      <c r="P59">
+        <v>-1.961060500000002</v>
+      </c>
+      <c r="Q59">
+        <v>-1.041060500000002</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.4422779524108524</v>
+      </c>
+      <c r="T59">
+        <v>2.139718360089085</v>
+      </c>
+      <c r="U59">
+        <v>0.1966</v>
+      </c>
+      <c r="V59">
+        <v>0.1231461155431814</v>
+      </c>
+      <c r="W59">
+        <v>0.1723894736842105</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.8209741036212095</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2900195195366665</v>
+      </c>
+      <c r="C60">
+        <v>27.48532976234614</v>
+      </c>
+      <c r="D60">
+        <v>91.41532976234613</v>
+      </c>
+      <c r="E60">
+        <v>32.79999999999999</v>
+      </c>
+      <c r="F60">
+        <v>66.69999999999999</v>
+      </c>
+      <c r="G60">
+        <v>2.77</v>
+      </c>
+      <c r="H60">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>11.5</v>
+      </c>
+      <c r="K60">
+        <v>0.92</v>
+      </c>
+      <c r="L60">
+        <v>10.58</v>
+      </c>
+      <c r="M60">
+        <v>13.11322</v>
+      </c>
+      <c r="N60">
+        <v>-2.533219999999998</v>
+      </c>
+      <c r="O60">
+        <v>-0.3799829999999998</v>
+      </c>
+      <c r="P60">
+        <v>-2.153236999999999</v>
+      </c>
+      <c r="Q60">
+        <v>-1.233236999999999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.4518845703253964</v>
+      </c>
+      <c r="T60">
+        <v>2.190664035329301</v>
+      </c>
+      <c r="U60">
+        <v>0.1966</v>
+      </c>
+      <c r="V60">
+        <v>0.1210229066545059</v>
+      </c>
+      <c r="W60">
+        <v>0.1728068965517241</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.8068193776967062</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.3027992072229954</v>
+      </c>
+      <c r="C61">
+        <v>21.91009160957115</v>
+      </c>
+      <c r="D61">
+        <v>86.99009160957115</v>
+      </c>
+      <c r="E61">
+        <v>33.95</v>
+      </c>
+      <c r="F61">
+        <v>67.84999999999999</v>
+      </c>
+      <c r="G61">
+        <v>2.77</v>
+      </c>
+      <c r="H61">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>11.5</v>
+      </c>
+      <c r="K61">
+        <v>0.92</v>
+      </c>
+      <c r="L61">
+        <v>10.58</v>
+      </c>
+      <c r="M61">
+        <v>14.50633</v>
+      </c>
+      <c r="N61">
+        <v>-3.926329999999998</v>
+      </c>
+      <c r="O61">
+        <v>-0.5889494999999998</v>
+      </c>
+      <c r="P61">
+        <v>-3.337380499999998</v>
+      </c>
+      <c r="Q61">
+        <v>-2.417380499999998</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.4645297737146227</v>
+      </c>
+      <c r="T61">
+        <v>2.257723892497002</v>
+      </c>
+      <c r="U61">
+        <v>0.2138</v>
+      </c>
+      <c r="V61">
+        <v>0.1094005168778044</v>
+      </c>
+      <c r="W61">
+        <v>0.1904101694915254</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.7293367791853627</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.3045492072229953</v>
+      </c>
+      <c r="C62">
+        <v>20.18724828142906</v>
+      </c>
+      <c r="D62">
+        <v>86.41724828142907</v>
+      </c>
+      <c r="E62">
+        <v>35.1</v>
+      </c>
+      <c r="F62">
+        <v>69</v>
+      </c>
+      <c r="G62">
+        <v>2.77</v>
+      </c>
+      <c r="H62">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>11.5</v>
+      </c>
+      <c r="K62">
+        <v>0.92</v>
+      </c>
+      <c r="L62">
+        <v>10.58</v>
+      </c>
+      <c r="M62">
+        <v>14.7522</v>
+      </c>
+      <c r="N62">
+        <v>-4.172199999999998</v>
+      </c>
+      <c r="O62">
+        <v>-0.6258299999999999</v>
+      </c>
+      <c r="P62">
+        <v>-3.546369999999999</v>
+      </c>
+      <c r="Q62">
+        <v>-2.626369999999999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.4751730180574882</v>
+      </c>
+      <c r="T62">
+        <v>2.314166989809427</v>
+      </c>
+      <c r="U62">
+        <v>0.2138</v>
+      </c>
+      <c r="V62">
+        <v>0.107577174929841</v>
+      </c>
+      <c r="W62">
+        <v>0.1908</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.7171811661989399</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.3062992072229953</v>
+      </c>
+      <c r="C63">
+        <v>18.47190012184953</v>
+      </c>
+      <c r="D63">
+        <v>85.85190012184952</v>
+      </c>
+      <c r="E63">
+        <v>36.24999999999999</v>
+      </c>
+      <c r="F63">
+        <v>70.14999999999999</v>
+      </c>
+      <c r="G63">
+        <v>2.77</v>
+      </c>
+      <c r="H63">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>11.5</v>
+      </c>
+      <c r="K63">
+        <v>0.92</v>
+      </c>
+      <c r="L63">
+        <v>10.58</v>
+      </c>
+      <c r="M63">
+        <v>14.99807</v>
+      </c>
+      <c r="N63">
+        <v>-4.418069999999997</v>
+      </c>
+      <c r="O63">
+        <v>-0.6627104999999995</v>
+      </c>
+      <c r="P63">
+        <v>-3.755359499999997</v>
+      </c>
+      <c r="Q63">
+        <v>-2.835359499999997</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.4863620698025521</v>
+      </c>
+      <c r="T63">
+        <v>2.373504604932746</v>
+      </c>
+      <c r="U63">
+        <v>0.2138</v>
+      </c>
+      <c r="V63">
+        <v>0.1058136146850895</v>
+      </c>
+      <c r="W63">
+        <v>0.1911770491803279</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.7054240979005967</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.3080492072229953</v>
+      </c>
+      <c r="C64">
+        <v>16.76390098505429</v>
+      </c>
+      <c r="D64">
+        <v>85.29390098505429</v>
+      </c>
+      <c r="E64">
+        <v>37.4</v>
+      </c>
+      <c r="F64">
+        <v>71.3</v>
+      </c>
+      <c r="G64">
+        <v>2.77</v>
+      </c>
+      <c r="H64">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>11.5</v>
+      </c>
+      <c r="K64">
+        <v>0.92</v>
+      </c>
+      <c r="L64">
+        <v>10.58</v>
+      </c>
+      <c r="M64">
+        <v>15.24394</v>
+      </c>
+      <c r="N64">
+        <v>-4.663939999999998</v>
+      </c>
+      <c r="O64">
+        <v>-0.6995909999999999</v>
+      </c>
+      <c r="P64">
+        <v>-3.964348999999999</v>
+      </c>
+      <c r="Q64">
+        <v>-3.044348999999999</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.4981400190078824</v>
+      </c>
+      <c r="T64">
+        <v>2.435965252430976</v>
+      </c>
+      <c r="U64">
+        <v>0.2138</v>
+      </c>
+      <c r="V64">
+        <v>0.1041069434804913</v>
+      </c>
+      <c r="W64">
+        <v>0.1915419354838709</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.6940462898699418</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.3097992072229953</v>
+      </c>
+      <c r="C65">
+        <v>15.06310850025922</v>
+      </c>
+      <c r="D65">
+        <v>84.74310850025923</v>
+      </c>
+      <c r="E65">
+        <v>38.55</v>
+      </c>
+      <c r="F65">
+        <v>72.45</v>
+      </c>
+      <c r="G65">
+        <v>2.77</v>
+      </c>
+      <c r="H65">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>11.5</v>
+      </c>
+      <c r="K65">
+        <v>0.92</v>
+      </c>
+      <c r="L65">
+        <v>10.58</v>
+      </c>
+      <c r="M65">
+        <v>15.48981</v>
+      </c>
+      <c r="N65">
+        <v>-4.90981</v>
+      </c>
+      <c r="O65">
+        <v>-0.7364715000000002</v>
+      </c>
+      <c r="P65">
+        <v>-4.1733385</v>
+      </c>
+      <c r="Q65">
+        <v>-3.2533385</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.5105546141162036</v>
+      </c>
+      <c r="T65">
+        <v>2.501802151145327</v>
+      </c>
+      <c r="U65">
+        <v>0.2138</v>
+      </c>
+      <c r="V65">
+        <v>0.1024544523141343</v>
+      </c>
+      <c r="W65">
+        <v>0.1918952380952381</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.6830296820942283</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.3115492072229953</v>
+      </c>
+      <c r="C66">
+        <v>13.36938395056985</v>
+      </c>
+      <c r="D66">
+        <v>84.19938395056987</v>
+      </c>
+      <c r="E66">
+        <v>39.70000000000001</v>
+      </c>
+      <c r="F66">
+        <v>73.60000000000001</v>
+      </c>
+      <c r="G66">
+        <v>2.77</v>
+      </c>
+      <c r="H66">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>11.5</v>
+      </c>
+      <c r="K66">
+        <v>0.92</v>
+      </c>
+      <c r="L66">
+        <v>10.58</v>
+      </c>
+      <c r="M66">
+        <v>15.73568</v>
+      </c>
+      <c r="N66">
+        <v>-5.15568</v>
+      </c>
+      <c r="O66">
+        <v>-0.7733520000000002</v>
+      </c>
+      <c r="P66">
+        <v>-4.382328</v>
+      </c>
+      <c r="Q66">
+        <v>-3.462328</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.5236589089527648</v>
+      </c>
+      <c r="T66">
+        <v>2.571296655343808</v>
+      </c>
+      <c r="U66">
+        <v>0.2138</v>
+      </c>
+      <c r="V66">
+        <v>0.1008536014967259</v>
+      </c>
+      <c r="W66">
+        <v>0.1922375</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.6723573433115061</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.3132992072229953</v>
+      </c>
+      <c r="C67">
+        <v>11.68259215650906</v>
+      </c>
+      <c r="D67">
+        <v>83.66259215650906</v>
+      </c>
+      <c r="E67">
+        <v>40.85</v>
+      </c>
+      <c r="F67">
+        <v>74.75</v>
+      </c>
+      <c r="G67">
+        <v>2.77</v>
+      </c>
+      <c r="H67">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>11.5</v>
+      </c>
+      <c r="K67">
+        <v>0.92</v>
+      </c>
+      <c r="L67">
+        <v>10.58</v>
+      </c>
+      <c r="M67">
+        <v>15.98155</v>
+      </c>
+      <c r="N67">
+        <v>-5.401549999999999</v>
+      </c>
+      <c r="O67">
+        <v>-0.8102324999999999</v>
+      </c>
+      <c r="P67">
+        <v>-4.591317499999999</v>
+      </c>
+      <c r="Q67">
+        <v>-3.671317499999999</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.5375120206371296</v>
+      </c>
+      <c r="T67">
+        <v>2.644762274067917</v>
+      </c>
+      <c r="U67">
+        <v>0.2138</v>
+      </c>
+      <c r="V67">
+        <v>0.09930200762754554</v>
+      </c>
+      <c r="W67">
+        <v>0.1925692307692308</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.6620133841836369</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.3150492072229952</v>
+      </c>
+      <c r="C68">
+        <v>10.00260136397186</v>
+      </c>
+      <c r="D68">
+        <v>83.13260136397187</v>
+      </c>
+      <c r="E68">
+        <v>42.00000000000001</v>
+      </c>
+      <c r="F68">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="G68">
+        <v>2.77</v>
+      </c>
+      <c r="H68">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>11.5</v>
+      </c>
+      <c r="K68">
+        <v>0.92</v>
+      </c>
+      <c r="L68">
+        <v>10.58</v>
+      </c>
+      <c r="M68">
+        <v>16.22742</v>
+      </c>
+      <c r="N68">
+        <v>-5.647420000000002</v>
+      </c>
+      <c r="O68">
+        <v>-0.8471130000000004</v>
+      </c>
+      <c r="P68">
+        <v>-4.800307000000002</v>
+      </c>
+      <c r="Q68">
+        <v>-3.880307000000002</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.5521800212441037</v>
+      </c>
+      <c r="T68">
+        <v>2.722549399775796</v>
+      </c>
+      <c r="U68">
+        <v>0.2138</v>
+      </c>
+      <c r="V68">
+        <v>0.09779743175440088</v>
+      </c>
+      <c r="W68">
+        <v>0.1928909090909091</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.6519828783626724</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.3167992072229954</v>
+      </c>
+      <c r="C69">
+        <v>8.329283136412087</v>
+      </c>
+      <c r="D69">
+        <v>82.6092831364121</v>
+      </c>
+      <c r="E69">
+        <v>43.15000000000001</v>
+      </c>
+      <c r="F69">
+        <v>77.05000000000001</v>
+      </c>
+      <c r="G69">
+        <v>2.77</v>
+      </c>
+      <c r="H69">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>11.5</v>
+      </c>
+      <c r="K69">
+        <v>0.92</v>
+      </c>
+      <c r="L69">
+        <v>10.58</v>
+      </c>
+      <c r="M69">
+        <v>16.47329</v>
+      </c>
+      <c r="N69">
+        <v>-5.893290000000002</v>
+      </c>
+      <c r="O69">
+        <v>-0.8839935000000004</v>
+      </c>
+      <c r="P69">
+        <v>-5.009296500000001</v>
+      </c>
+      <c r="Q69">
+        <v>-4.089296500000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.5677369915848345</v>
+      </c>
+      <c r="T69">
+        <v>2.8050508967387</v>
+      </c>
+      <c r="U69">
+        <v>0.2138</v>
+      </c>
+      <c r="V69">
+        <v>0.09633776859388744</v>
+      </c>
+      <c r="W69">
+        <v>0.1932029850746269</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.6422517906259162</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.3185492072229954</v>
+      </c>
+      <c r="C70">
+        <v>6.662512251075896</v>
+      </c>
+      <c r="D70">
+        <v>82.0925122510759</v>
+      </c>
+      <c r="E70">
+        <v>44.3</v>
+      </c>
+      <c r="F70">
+        <v>78.2</v>
+      </c>
+      <c r="G70">
+        <v>2.77</v>
+      </c>
+      <c r="H70">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>11.5</v>
+      </c>
+      <c r="K70">
+        <v>0.92</v>
+      </c>
+      <c r="L70">
+        <v>10.58</v>
+      </c>
+      <c r="M70">
+        <v>16.71916</v>
+      </c>
+      <c r="N70">
+        <v>-6.139159999999999</v>
+      </c>
+      <c r="O70">
+        <v>-0.920874</v>
+      </c>
+      <c r="P70">
+        <v>-5.218285999999999</v>
+      </c>
+      <c r="Q70">
+        <v>-4.298285999999999</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.5842662725718606</v>
+      </c>
+      <c r="T70">
+        <v>2.892708737261785</v>
+      </c>
+      <c r="U70">
+        <v>0.2138</v>
+      </c>
+      <c r="V70">
+        <v>0.09492103670280087</v>
+      </c>
+      <c r="W70">
+        <v>0.1935058823529412</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.6328069113520058</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.3202992072229953</v>
+      </c>
+      <c r="C71">
+        <v>5.002166599105479</v>
+      </c>
+      <c r="D71">
+        <v>81.58216659910549</v>
+      </c>
+      <c r="E71">
+        <v>45.45000000000001</v>
+      </c>
+      <c r="F71">
+        <v>79.35000000000001</v>
+      </c>
+      <c r="G71">
+        <v>2.77</v>
+      </c>
+      <c r="H71">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>11.5</v>
+      </c>
+      <c r="K71">
+        <v>0.92</v>
+      </c>
+      <c r="L71">
+        <v>10.58</v>
+      </c>
+      <c r="M71">
+        <v>16.96503</v>
+      </c>
+      <c r="N71">
+        <v>-6.385030000000002</v>
+      </c>
+      <c r="O71">
+        <v>-0.9577545000000005</v>
+      </c>
+      <c r="P71">
+        <v>-5.427275500000002</v>
+      </c>
+      <c r="Q71">
+        <v>-4.507275500000002</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.6018619587838561</v>
+      </c>
+      <c r="T71">
+        <v>2.986021922334746</v>
+      </c>
+      <c r="U71">
+        <v>0.2138</v>
+      </c>
+      <c r="V71">
+        <v>0.09354536950420955</v>
+      </c>
+      <c r="W71">
+        <v>0.1938</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.6236357966947301</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.3220492072229953</v>
+      </c>
+      <c r="C72">
+        <v>3.348127089345994</v>
+      </c>
+      <c r="D72">
+        <v>81.07812708934601</v>
+      </c>
+      <c r="E72">
+        <v>46.60000000000002</v>
+      </c>
+      <c r="F72">
+        <v>80.50000000000001</v>
+      </c>
+      <c r="G72">
+        <v>2.77</v>
+      </c>
+      <c r="H72">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>11.5</v>
+      </c>
+      <c r="K72">
+        <v>0.92</v>
+      </c>
+      <c r="L72">
+        <v>10.58</v>
+      </c>
+      <c r="M72">
+        <v>17.2109</v>
+      </c>
+      <c r="N72">
+        <v>-6.630900000000002</v>
+      </c>
+      <c r="O72">
+        <v>-0.9946350000000005</v>
+      </c>
+      <c r="P72">
+        <v>-5.636265000000002</v>
+      </c>
+      <c r="Q72">
+        <v>-4.716265000000002</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.6206306907433179</v>
+      </c>
+      <c r="T72">
+        <v>3.08555598641257</v>
+      </c>
+      <c r="U72">
+        <v>0.2138</v>
+      </c>
+      <c r="V72">
+        <v>0.09220900708272084</v>
+      </c>
+      <c r="W72">
+        <v>0.1940857142857143</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.6147267138848055</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.3237992072229954</v>
+      </c>
+      <c r="C73">
+        <v>1.700277555696829</v>
+      </c>
+      <c r="D73">
+        <v>80.58027755569682</v>
+      </c>
+      <c r="E73">
+        <v>47.74999999999999</v>
+      </c>
+      <c r="F73">
+        <v>81.64999999999999</v>
+      </c>
+      <c r="G73">
+        <v>2.77</v>
+      </c>
+      <c r="H73">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>11.5</v>
+      </c>
+      <c r="K73">
+        <v>0.92</v>
+      </c>
+      <c r="L73">
+        <v>10.58</v>
+      </c>
+      <c r="M73">
+        <v>17.45677</v>
+      </c>
+      <c r="N73">
+        <v>-6.876769999999999</v>
+      </c>
+      <c r="O73">
+        <v>-1.0315155</v>
+      </c>
+      <c r="P73">
+        <v>-5.845254499999998</v>
+      </c>
+      <c r="Q73">
+        <v>-4.925254499999999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.6406938180103288</v>
+      </c>
+      <c r="T73">
+        <v>3.191954468702658</v>
+      </c>
+      <c r="U73">
+        <v>0.2138</v>
+      </c>
+      <c r="V73">
+        <v>0.09091028867310506</v>
+      </c>
+      <c r="W73">
+        <v>0.1943633802816901</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.6060685911540338</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.3255492072229954</v>
+      </c>
+      <c r="C74">
+        <v>0.05850466785479114</v>
+      </c>
+      <c r="D74">
+        <v>80.08850466785479</v>
+      </c>
+      <c r="E74">
+        <v>48.9</v>
+      </c>
+      <c r="F74">
+        <v>82.8</v>
+      </c>
+      <c r="G74">
+        <v>2.77</v>
+      </c>
+      <c r="H74">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>11.5</v>
+      </c>
+      <c r="K74">
+        <v>0.92</v>
+      </c>
+      <c r="L74">
+        <v>10.58</v>
+      </c>
+      <c r="M74">
+        <v>17.70264</v>
+      </c>
+      <c r="N74">
+        <v>-7.122639999999999</v>
+      </c>
+      <c r="O74">
+        <v>-1.068396</v>
+      </c>
+      <c r="P74">
+        <v>-6.054243999999999</v>
+      </c>
+      <c r="Q74">
+        <v>-5.134243999999999</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.662190025796412</v>
+      </c>
+      <c r="T74">
+        <v>3.305952842584896</v>
+      </c>
+      <c r="U74">
+        <v>0.2138</v>
+      </c>
+      <c r="V74">
+        <v>0.08964764577486749</v>
+      </c>
+      <c r="W74">
+        <v>0.1946333333333333</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.5976509718324499</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.3272992072229953</v>
+      </c>
+      <c r="C75">
+        <v>-1.577302154693655</v>
+      </c>
+      <c r="D75">
+        <v>79.60269784530635</v>
+      </c>
+      <c r="E75">
+        <v>50.05</v>
+      </c>
+      <c r="F75">
+        <v>83.95</v>
+      </c>
+      <c r="G75">
+        <v>2.77</v>
+      </c>
+      <c r="H75">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>11.5</v>
+      </c>
+      <c r="K75">
+        <v>0.92</v>
+      </c>
+      <c r="L75">
+        <v>10.58</v>
+      </c>
+      <c r="M75">
+        <v>17.94851</v>
+      </c>
+      <c r="N75">
+        <v>-7.368509999999999</v>
+      </c>
+      <c r="O75">
+        <v>-1.1052765</v>
+      </c>
+      <c r="P75">
+        <v>-6.263233499999998</v>
+      </c>
+      <c r="Q75">
+        <v>-5.343233499999998</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.6852785452703529</v>
+      </c>
+      <c r="T75">
+        <v>3.428395540458411</v>
+      </c>
+      <c r="U75">
+        <v>0.2138</v>
+      </c>
+      <c r="V75">
+        <v>0.08841959583274601</v>
+      </c>
+      <c r="W75">
+        <v>0.1948958904109589</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.5894639722183068</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.3290492072229952</v>
+      </c>
+      <c r="C76">
+        <v>-3.207250825568906</v>
+      </c>
+      <c r="D76">
+        <v>79.12274917443109</v>
+      </c>
+      <c r="E76">
+        <v>51.2</v>
+      </c>
+      <c r="F76">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="G76">
+        <v>2.77</v>
+      </c>
+      <c r="H76">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>11.5</v>
+      </c>
+      <c r="K76">
+        <v>0.92</v>
+      </c>
+      <c r="L76">
+        <v>10.58</v>
+      </c>
+      <c r="M76">
+        <v>18.19438</v>
+      </c>
+      <c r="N76">
+        <v>-7.614379999999999</v>
+      </c>
+      <c r="O76">
+        <v>-1.142157</v>
+      </c>
+      <c r="P76">
+        <v>-6.472222999999999</v>
+      </c>
+      <c r="Q76">
+        <v>-5.552222999999999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.710143104703828</v>
+      </c>
+      <c r="T76">
+        <v>3.560256907399118</v>
+      </c>
+      <c r="U76">
+        <v>0.2138</v>
+      </c>
+      <c r="V76">
+        <v>0.08722473642960081</v>
+      </c>
+      <c r="W76">
+        <v>0.1951513513513513</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.5814982428640053</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.3307992072229953</v>
+      </c>
+      <c r="C77">
+        <v>-4.831446671414184</v>
+      </c>
+      <c r="D77">
+        <v>78.64855332858582</v>
+      </c>
+      <c r="E77">
+        <v>52.35</v>
+      </c>
+      <c r="F77">
+        <v>86.25</v>
+      </c>
+      <c r="G77">
+        <v>2.77</v>
+      </c>
+      <c r="H77">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>11.5</v>
+      </c>
+      <c r="K77">
+        <v>0.92</v>
+      </c>
+      <c r="L77">
+        <v>10.58</v>
+      </c>
+      <c r="M77">
+        <v>18.44025</v>
+      </c>
+      <c r="N77">
+        <v>-7.860249999999999</v>
+      </c>
+      <c r="O77">
+        <v>-1.1790375</v>
+      </c>
+      <c r="P77">
+        <v>-6.681212499999999</v>
+      </c>
+      <c r="Q77">
+        <v>-5.761212499999999</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.7369968288919813</v>
+      </c>
+      <c r="T77">
+        <v>3.702667183695084</v>
+      </c>
+      <c r="U77">
+        <v>0.2138</v>
+      </c>
+      <c r="V77">
+        <v>0.0860617399438728</v>
+      </c>
+      <c r="W77">
+        <v>0.1954</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.573744932959152</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.3325492072229953</v>
+      </c>
+      <c r="C78">
+        <v>-6.449992508954253</v>
+      </c>
+      <c r="D78">
+        <v>78.18000749104576</v>
+      </c>
+      <c r="E78">
+        <v>53.50000000000001</v>
+      </c>
+      <c r="F78">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="G78">
+        <v>2.77</v>
+      </c>
+      <c r="H78">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>11.5</v>
+      </c>
+      <c r="K78">
+        <v>0.92</v>
+      </c>
+      <c r="L78">
+        <v>10.58</v>
+      </c>
+      <c r="M78">
+        <v>18.68612</v>
+      </c>
+      <c r="N78">
+        <v>-8.106119999999999</v>
+      </c>
+      <c r="O78">
+        <v>-1.215918</v>
+      </c>
+      <c r="P78">
+        <v>-6.890201999999999</v>
+      </c>
+      <c r="Q78">
+        <v>-5.970201999999999</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.7660883634291473</v>
+      </c>
+      <c r="T78">
+        <v>3.856944983015712</v>
+      </c>
+      <c r="U78">
+        <v>0.2138</v>
+      </c>
+      <c r="V78">
+        <v>0.08492934862882184</v>
+      </c>
+      <c r="W78">
+        <v>0.1956421052631579</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.5661956575254788</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.3342992072229953</v>
+      </c>
+      <c r="C79">
+        <v>-8.062988719316621</v>
+      </c>
+      <c r="D79">
+        <v>77.71701128068338</v>
+      </c>
+      <c r="E79">
+        <v>54.65</v>
+      </c>
+      <c r="F79">
+        <v>88.55</v>
+      </c>
+      <c r="G79">
+        <v>2.77</v>
+      </c>
+      <c r="H79">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>11.5</v>
+      </c>
+      <c r="K79">
+        <v>0.92</v>
+      </c>
+      <c r="L79">
+        <v>10.58</v>
+      </c>
+      <c r="M79">
+        <v>18.93199</v>
+      </c>
+      <c r="N79">
+        <v>-8.351989999999999</v>
+      </c>
+      <c r="O79">
+        <v>-1.2527985</v>
+      </c>
+      <c r="P79">
+        <v>-7.099191499999999</v>
+      </c>
+      <c r="Q79">
+        <v>-6.179191499999999</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.7977095966217189</v>
+      </c>
+      <c r="T79">
+        <v>4.024638243146831</v>
+      </c>
+      <c r="U79">
+        <v>0.2138</v>
+      </c>
+      <c r="V79">
+        <v>0.08382637007520077</v>
+      </c>
+      <c r="W79">
+        <v>0.1958779220779221</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.558842467168005</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.3360492072229953</v>
+      </c>
+      <c r="C80">
+        <v>-9.670533319727156</v>
+      </c>
+      <c r="D80">
+        <v>77.25946668027285</v>
+      </c>
+      <c r="E80">
+        <v>55.8</v>
+      </c>
+      <c r="F80">
+        <v>89.7</v>
+      </c>
+      <c r="G80">
+        <v>2.77</v>
+      </c>
+      <c r="H80">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>11.5</v>
+      </c>
+      <c r="K80">
+        <v>0.92</v>
+      </c>
+      <c r="L80">
+        <v>10.58</v>
+      </c>
+      <c r="M80">
+        <v>19.17786</v>
+      </c>
+      <c r="N80">
+        <v>-8.597859999999999</v>
+      </c>
+      <c r="O80">
+        <v>-1.289679</v>
+      </c>
+      <c r="P80">
+        <v>-7.308180999999999</v>
+      </c>
+      <c r="Q80">
+        <v>-6.388180999999999</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.8322054873772515</v>
+      </c>
+      <c r="T80">
+        <v>4.20757634510805</v>
+      </c>
+      <c r="U80">
+        <v>0.2138</v>
+      </c>
+      <c r="V80">
+        <v>0.08275167302295461</v>
+      </c>
+      <c r="W80">
+        <v>0.1961076923076923</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.5516778201530307</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.3377992072229953</v>
+      </c>
+      <c r="C81">
+        <v>-11.27272203268801</v>
+      </c>
+      <c r="D81">
+        <v>76.807277967312</v>
+      </c>
+      <c r="E81">
+        <v>56.95000000000001</v>
+      </c>
+      <c r="F81">
+        <v>90.85000000000001</v>
+      </c>
+      <c r="G81">
+        <v>2.77</v>
+      </c>
+      <c r="H81">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>11.5</v>
+      </c>
+      <c r="K81">
+        <v>0.92</v>
+      </c>
+      <c r="L81">
+        <v>10.58</v>
+      </c>
+      <c r="M81">
+        <v>19.42373</v>
+      </c>
+      <c r="N81">
+        <v>-8.843730000000003</v>
+      </c>
+      <c r="O81">
+        <v>-1.326559500000001</v>
+      </c>
+      <c r="P81">
+        <v>-7.517170500000002</v>
+      </c>
+      <c r="Q81">
+        <v>-6.597170500000002</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.8699867010618825</v>
+      </c>
+      <c r="T81">
+        <v>4.407937123446528</v>
+      </c>
+      <c r="U81">
+        <v>0.2138</v>
+      </c>
+      <c r="V81">
+        <v>0.08170418349101846</v>
+      </c>
+      <c r="W81">
+        <v>0.1963316455696202</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.5446945566067897</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.3395492072229953</v>
+      </c>
+      <c r="C82">
+        <v>-12.86964835274021</v>
+      </c>
+      <c r="D82">
+        <v>76.36035164725979</v>
+      </c>
+      <c r="E82">
+        <v>58.1</v>
+      </c>
+      <c r="F82">
+        <v>92</v>
+      </c>
+      <c r="G82">
+        <v>2.77</v>
+      </c>
+      <c r="H82">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>11.5</v>
+      </c>
+      <c r="K82">
+        <v>0.92</v>
+      </c>
+      <c r="L82">
+        <v>10.58</v>
+      </c>
+      <c r="M82">
+        <v>19.6696</v>
+      </c>
+      <c r="N82">
+        <v>-9.089599999999999</v>
+      </c>
+      <c r="O82">
+        <v>-1.36344</v>
+      </c>
+      <c r="P82">
+        <v>-7.726159999999999</v>
+      </c>
+      <c r="Q82">
+        <v>-6.806159999999999</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.9115460361149768</v>
+      </c>
+      <c r="T82">
+        <v>4.628333979618855</v>
+      </c>
+      <c r="U82">
+        <v>0.2138</v>
+      </c>
+      <c r="V82">
+        <v>0.08068288119738075</v>
+      </c>
+      <c r="W82">
+        <v>0.19655</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.5378858746492049</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.3412992072229953</v>
+      </c>
+      <c r="C83">
+        <v>-14.46140361090922</v>
+      </c>
+      <c r="D83">
+        <v>75.91859638909079</v>
+      </c>
+      <c r="E83">
+        <v>59.25000000000001</v>
+      </c>
+      <c r="F83">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="G83">
+        <v>2.77</v>
+      </c>
+      <c r="H83">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>11.5</v>
+      </c>
+      <c r="K83">
+        <v>0.92</v>
+      </c>
+      <c r="L83">
+        <v>10.58</v>
+      </c>
+      <c r="M83">
+        <v>19.91547</v>
+      </c>
+      <c r="N83">
+        <v>-9.335469999999999</v>
+      </c>
+      <c r="O83">
+        <v>-1.4003205</v>
+      </c>
+      <c r="P83">
+        <v>-7.935149499999999</v>
+      </c>
+      <c r="Q83">
+        <v>-7.015149499999999</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.9574800380157651</v>
+      </c>
+      <c r="T83">
+        <v>4.871930504861953</v>
+      </c>
+      <c r="U83">
+        <v>0.2138</v>
+      </c>
+      <c r="V83">
+        <v>0.07968679624432666</v>
+      </c>
+      <c r="W83">
+        <v>0.196762962962963</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.5312453082955111</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.3430492072229953</v>
+      </c>
+      <c r="C84">
+        <v>-16.04807703692583</v>
+      </c>
+      <c r="D84">
+        <v>75.48192296307418</v>
+      </c>
+      <c r="E84">
+        <v>60.40000000000001</v>
+      </c>
+      <c r="F84">
+        <v>94.30000000000001</v>
+      </c>
+      <c r="G84">
+        <v>2.77</v>
+      </c>
+      <c r="H84">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>11.5</v>
+      </c>
+      <c r="K84">
+        <v>0.92</v>
+      </c>
+      <c r="L84">
+        <v>10.58</v>
+      </c>
+      <c r="M84">
+        <v>20.16134</v>
+      </c>
+      <c r="N84">
+        <v>-9.581340000000003</v>
+      </c>
+      <c r="O84">
+        <v>-1.437201000000001</v>
+      </c>
+      <c r="P84">
+        <v>-8.144139000000003</v>
+      </c>
+      <c r="Q84">
+        <v>-7.224139000000003</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>1.00851781790553</v>
+      </c>
+      <c r="T84">
+        <v>5.142593310687617</v>
+      </c>
+      <c r="U84">
+        <v>0.2138</v>
+      </c>
+      <c r="V84">
+        <v>0.07871500604622511</v>
+      </c>
+      <c r="W84">
+        <v>0.196970731707317</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.524766706974834</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.3447992072229953</v>
+      </c>
+      <c r="C85">
+        <v>-17.62975581931273</v>
+      </c>
+      <c r="D85">
+        <v>75.05024418068727</v>
+      </c>
+      <c r="E85">
+        <v>61.55</v>
+      </c>
+      <c r="F85">
+        <v>95.45</v>
+      </c>
+      <c r="G85">
+        <v>2.77</v>
+      </c>
+      <c r="H85">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>11.5</v>
+      </c>
+      <c r="K85">
+        <v>0.92</v>
+      </c>
+      <c r="L85">
+        <v>10.58</v>
+      </c>
+      <c r="M85">
+        <v>20.40721</v>
+      </c>
+      <c r="N85">
+        <v>-9.827209999999999</v>
+      </c>
+      <c r="O85">
+        <v>-1.4740815</v>
+      </c>
+      <c r="P85">
+        <v>-8.353128499999999</v>
+      </c>
+      <c r="Q85">
+        <v>-7.433128499999999</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>1.065560042488208</v>
+      </c>
+      <c r="T85">
+        <v>5.445098799551595</v>
+      </c>
+      <c r="U85">
+        <v>0.2138</v>
+      </c>
+      <c r="V85">
+        <v>0.07776663247940313</v>
+      </c>
+      <c r="W85">
+        <v>0.1971734939759036</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.5184442165293541</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3465492072229953</v>
+      </c>
+      <c r="C86">
+        <v>-19.20652516342037</v>
+      </c>
+      <c r="D86">
+        <v>74.62347483657963</v>
+      </c>
+      <c r="E86">
+        <v>62.7</v>
+      </c>
+      <c r="F86">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="G86">
+        <v>2.77</v>
+      </c>
+      <c r="H86">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>11.5</v>
+      </c>
+      <c r="K86">
+        <v>0.92</v>
+      </c>
+      <c r="L86">
+        <v>10.58</v>
+      </c>
+      <c r="M86">
+        <v>20.65308</v>
+      </c>
+      <c r="N86">
+        <v>-10.07308</v>
+      </c>
+      <c r="O86">
+        <v>-1.510962</v>
+      </c>
+      <c r="P86">
+        <v>-8.562117999999998</v>
+      </c>
+      <c r="Q86">
+        <v>-7.642117999999998</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>1.129732545143721</v>
+      </c>
+      <c r="T86">
+        <v>5.785417474523568</v>
+      </c>
+      <c r="U86">
+        <v>0.2138</v>
+      </c>
+      <c r="V86">
+        <v>0.0768408392356007</v>
+      </c>
+      <c r="W86">
+        <v>0.1973714285714286</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.5122722615706713</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3482992072229953</v>
+      </c>
+      <c r="C87">
+        <v>-20.77846834749425</v>
+      </c>
+      <c r="D87">
+        <v>74.20153165250575</v>
+      </c>
+      <c r="E87">
+        <v>63.85</v>
+      </c>
+      <c r="F87">
+        <v>97.75</v>
+      </c>
+      <c r="G87">
+        <v>2.77</v>
+      </c>
+      <c r="H87">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>11.5</v>
+      </c>
+      <c r="K87">
+        <v>0.92</v>
+      </c>
+      <c r="L87">
+        <v>10.58</v>
+      </c>
+      <c r="M87">
+        <v>20.89895</v>
+      </c>
+      <c r="N87">
+        <v>-10.31895</v>
+      </c>
+      <c r="O87">
+        <v>-1.5478425</v>
+      </c>
+      <c r="P87">
+        <v>-8.771107499999999</v>
+      </c>
+      <c r="Q87">
+        <v>-7.851107499999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>1.202461381486635</v>
+      </c>
+      <c r="T87">
+        <v>6.171111972825139</v>
+      </c>
+      <c r="U87">
+        <v>0.2138</v>
+      </c>
+      <c r="V87">
+        <v>0.07593682936224069</v>
+      </c>
+      <c r="W87">
+        <v>0.1975647058823529</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.5062455290816046</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3500492072229953</v>
+      </c>
+      <c r="C88">
+        <v>-22.34566677685072</v>
+      </c>
+      <c r="D88">
+        <v>73.78433322314928</v>
+      </c>
+      <c r="E88">
+        <v>65</v>
+      </c>
+      <c r="F88">
+        <v>98.89999999999999</v>
+      </c>
+      <c r="G88">
+        <v>2.77</v>
+      </c>
+      <c r="H88">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>11.5</v>
+      </c>
+      <c r="K88">
+        <v>0.92</v>
+      </c>
+      <c r="L88">
+        <v>10.58</v>
+      </c>
+      <c r="M88">
+        <v>21.14482</v>
+      </c>
+      <c r="N88">
+        <v>-10.56482</v>
+      </c>
+      <c r="O88">
+        <v>-1.584723</v>
+      </c>
+      <c r="P88">
+        <v>-8.980096999999995</v>
+      </c>
+      <c r="Q88">
+        <v>-8.060096999999995</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>1.285580051592824</v>
+      </c>
+      <c r="T88">
+        <v>6.611905685169791</v>
+      </c>
+      <c r="U88">
+        <v>0.2138</v>
+      </c>
+      <c r="V88">
+        <v>0.07505384297430769</v>
+      </c>
+      <c r="W88">
+        <v>0.197753488372093</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.5003589531620511</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3748100840339654</v>
+      </c>
+      <c r="C89">
+        <v>-28.93289878960573</v>
+      </c>
+      <c r="D89">
+        <v>68.34710121039427</v>
+      </c>
+      <c r="E89">
+        <v>66.15000000000001</v>
+      </c>
+      <c r="F89">
+        <v>100.05</v>
+      </c>
+      <c r="G89">
+        <v>2.77</v>
+      </c>
+      <c r="H89">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>11.5</v>
+      </c>
+      <c r="K89">
+        <v>0.92</v>
+      </c>
+      <c r="L89">
+        <v>10.58</v>
+      </c>
+      <c r="M89">
+        <v>23.89194</v>
+      </c>
+      <c r="N89">
+        <v>-13.31194</v>
+      </c>
+      <c r="O89">
+        <v>-1.996791000000001</v>
+      </c>
+      <c r="P89">
+        <v>-11.315149</v>
+      </c>
+      <c r="Q89">
+        <v>-10.395149</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>1.391185261799734</v>
+      </c>
+      <c r="T89">
+        <v>7.171949687204129</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.06642407439496333</v>
+      </c>
+      <c r="W89">
+        <v>0.2229379310344828</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.4428271626330887</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3768100840339654</v>
+      </c>
+      <c r="C90">
+        <v>-30.48730744152941</v>
+      </c>
+      <c r="D90">
+        <v>67.9426925584706</v>
+      </c>
+      <c r="E90">
+        <v>67.30000000000001</v>
+      </c>
+      <c r="F90">
+        <v>101.2</v>
+      </c>
+      <c r="G90">
+        <v>2.77</v>
+      </c>
+      <c r="H90">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>11.5</v>
+      </c>
+      <c r="K90">
+        <v>0.92</v>
+      </c>
+      <c r="L90">
+        <v>10.58</v>
+      </c>
+      <c r="M90">
+        <v>24.16656</v>
+      </c>
+      <c r="N90">
+        <v>-13.58656</v>
+      </c>
+      <c r="O90">
+        <v>-2.037984</v>
+      </c>
+      <c r="P90">
+        <v>-11.548576</v>
+      </c>
+      <c r="Q90">
+        <v>-10.628576</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.503884033616379</v>
+      </c>
+      <c r="T90">
+        <v>7.769612161137808</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.06566925536774784</v>
+      </c>
+      <c r="W90">
+        <v>0.2231181818181818</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.4377950357849856</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3788100840339654</v>
+      </c>
+      <c r="C91">
+        <v>-32.03695848571246</v>
+      </c>
+      <c r="D91">
+        <v>67.54304151428755</v>
+      </c>
+      <c r="E91">
+        <v>68.45000000000002</v>
+      </c>
+      <c r="F91">
+        <v>102.35</v>
+      </c>
+      <c r="G91">
+        <v>2.77</v>
+      </c>
+      <c r="H91">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>11.5</v>
+      </c>
+      <c r="K91">
+        <v>0.92</v>
+      </c>
+      <c r="L91">
+        <v>10.58</v>
+      </c>
+      <c r="M91">
+        <v>24.44118</v>
+      </c>
+      <c r="N91">
+        <v>-13.86118</v>
+      </c>
+      <c r="O91">
+        <v>-2.079177</v>
+      </c>
+      <c r="P91">
+        <v>-11.782003</v>
+      </c>
+      <c r="Q91">
+        <v>-10.862003</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.637073491217868</v>
+      </c>
+      <c r="T91">
+        <v>8.475940539423062</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.06493139856586302</v>
+      </c>
+      <c r="W91">
+        <v>0.2232943820224719</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.4328759904390868</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3808100840339654</v>
+      </c>
+      <c r="C92">
+        <v>-33.58193538649635</v>
+      </c>
+      <c r="D92">
+        <v>67.14806461350365</v>
+      </c>
+      <c r="E92">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="F92">
+        <v>103.5</v>
+      </c>
+      <c r="G92">
+        <v>2.77</v>
+      </c>
+      <c r="H92">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>11.5</v>
+      </c>
+      <c r="K92">
+        <v>0.92</v>
+      </c>
+      <c r="L92">
+        <v>10.58</v>
+      </c>
+      <c r="M92">
+        <v>24.7158</v>
+      </c>
+      <c r="N92">
+        <v>-14.1358</v>
+      </c>
+      <c r="O92">
+        <v>-2.120370000000001</v>
+      </c>
+      <c r="P92">
+        <v>-12.01543</v>
+      </c>
+      <c r="Q92">
+        <v>-11.09543</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.796900840339655</v>
+      </c>
+      <c r="T92">
+        <v>9.32353459336537</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.06420993858179788</v>
+      </c>
+      <c r="W92">
+        <v>0.2234666666666667</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.4280662572119859</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3828100840339654</v>
+      </c>
+      <c r="C93">
+        <v>-35.12231966724828</v>
+      </c>
+      <c r="D93">
+        <v>66.75768033275173</v>
+      </c>
+      <c r="E93">
+        <v>70.75</v>
+      </c>
+      <c r="F93">
+        <v>104.65</v>
+      </c>
+      <c r="G93">
+        <v>2.77</v>
+      </c>
+      <c r="H93">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>11.5</v>
+      </c>
+      <c r="K93">
+        <v>0.92</v>
+      </c>
+      <c r="L93">
+        <v>10.58</v>
+      </c>
+      <c r="M93">
+        <v>24.99042</v>
+      </c>
+      <c r="N93">
+        <v>-14.41042</v>
+      </c>
+      <c r="O93">
+        <v>-2.161563000000001</v>
+      </c>
+      <c r="P93">
+        <v>-12.248857</v>
+      </c>
+      <c r="Q93">
+        <v>-11.328857</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.992245378155172</v>
+      </c>
+      <c r="T93">
+        <v>10.35948288151708</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.06350433486111878</v>
+      </c>
+      <c r="W93">
+        <v>0.2236351648351648</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.4233622324074585</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3848100840339655</v>
+      </c>
+      <c r="C94">
+        <v>-36.65819096645701</v>
+      </c>
+      <c r="D94">
+        <v>66.371809033543</v>
+      </c>
+      <c r="E94">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="F94">
+        <v>105.8</v>
+      </c>
+      <c r="G94">
+        <v>2.77</v>
+      </c>
+      <c r="H94">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>11.5</v>
+      </c>
+      <c r="K94">
+        <v>0.92</v>
+      </c>
+      <c r="L94">
+        <v>10.58</v>
+      </c>
+      <c r="M94">
+        <v>25.26504</v>
+      </c>
+      <c r="N94">
+        <v>-14.68504</v>
+      </c>
+      <c r="O94">
+        <v>-2.202756000000001</v>
+      </c>
+      <c r="P94">
+        <v>-12.482284</v>
+      </c>
+      <c r="Q94">
+        <v>-11.562284</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>2.23642605042457</v>
+      </c>
+      <c r="T94">
+        <v>11.65441824170672</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.0628140703517588</v>
+      </c>
+      <c r="W94">
+        <v>0.2238</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.4187604690117253</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3868100840339655</v>
+      </c>
+      <c r="C95">
+        <v>-38.18962709189448</v>
+      </c>
+      <c r="D95">
+        <v>65.99037290810553</v>
+      </c>
+      <c r="E95">
+        <v>73.05000000000001</v>
+      </c>
+      <c r="F95">
+        <v>106.95</v>
+      </c>
+      <c r="G95">
+        <v>2.77</v>
+      </c>
+      <c r="H95">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>11.5</v>
+      </c>
+      <c r="K95">
+        <v>0.92</v>
+      </c>
+      <c r="L95">
+        <v>10.58</v>
+      </c>
+      <c r="M95">
+        <v>25.53966</v>
+      </c>
+      <c r="N95">
+        <v>-14.95966</v>
+      </c>
+      <c r="O95">
+        <v>-2.243949000000001</v>
+      </c>
+      <c r="P95">
+        <v>-12.715711</v>
+      </c>
+      <c r="Q95">
+        <v>-11.795711</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>2.550372629056652</v>
+      </c>
+      <c r="T95">
+        <v>13.31933513337911</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.06213865024044957</v>
+      </c>
+      <c r="W95">
+        <v>0.2239612903225807</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.4142576682696637</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3888100840339654</v>
+      </c>
+      <c r="C96">
+        <v>-39.71670407292055</v>
+      </c>
+      <c r="D96">
+        <v>65.61329592707946</v>
+      </c>
+      <c r="E96">
+        <v>74.20000000000002</v>
+      </c>
+      <c r="F96">
+        <v>108.1</v>
+      </c>
+      <c r="G96">
+        <v>2.77</v>
+      </c>
+      <c r="H96">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>11.5</v>
+      </c>
+      <c r="K96">
+        <v>0.92</v>
+      </c>
+      <c r="L96">
+        <v>10.58</v>
+      </c>
+      <c r="M96">
+        <v>25.81428</v>
+      </c>
+      <c r="N96">
+        <v>-15.23428</v>
+      </c>
+      <c r="O96">
+        <v>-2.285142000000001</v>
+      </c>
+      <c r="P96">
+        <v>-12.949138</v>
+      </c>
+      <c r="Q96">
+        <v>-12.029138</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.96896806723276</v>
+      </c>
+      <c r="T96">
+        <v>15.53922432227563</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.06147760076980648</v>
+      </c>
+      <c r="W96">
+        <v>0.2241191489361702</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.4098506717987098</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3908100840339656</v>
+      </c>
+      <c r="C97">
+        <v>-41.23949621100461</v>
+      </c>
+      <c r="D97">
+        <v>65.24050378899541</v>
+      </c>
+      <c r="E97">
+        <v>75.35000000000002</v>
+      </c>
+      <c r="F97">
+        <v>109.25</v>
+      </c>
+      <c r="G97">
+        <v>2.77</v>
+      </c>
+      <c r="H97">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>11.5</v>
+      </c>
+      <c r="K97">
+        <v>0.92</v>
+      </c>
+      <c r="L97">
+        <v>10.58</v>
+      </c>
+      <c r="M97">
+        <v>26.08890000000001</v>
+      </c>
+      <c r="N97">
+        <v>-15.50890000000001</v>
+      </c>
+      <c r="O97">
+        <v>-2.326335000000001</v>
+      </c>
+      <c r="P97">
+        <v>-13.182565</v>
+      </c>
+      <c r="Q97">
+        <v>-12.262565</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>3.555001680679315</v>
+      </c>
+      <c r="T97">
+        <v>18.64706918673076</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.0608304681301243</v>
+      </c>
+      <c r="W97">
+        <v>0.2242736842105263</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.4055364542008286</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3928100840339654</v>
+      </c>
+      <c r="C98">
+        <v>-42.75807612853446</v>
+      </c>
+      <c r="D98">
+        <v>64.87192387146554</v>
+      </c>
+      <c r="E98">
+        <v>76.5</v>
+      </c>
+      <c r="F98">
+        <v>110.4</v>
+      </c>
+      <c r="G98">
+        <v>2.77</v>
+      </c>
+      <c r="H98">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>11.5</v>
+      </c>
+      <c r="K98">
+        <v>0.92</v>
+      </c>
+      <c r="L98">
+        <v>10.58</v>
+      </c>
+      <c r="M98">
+        <v>26.36352</v>
+      </c>
+      <c r="N98">
+        <v>-15.78352</v>
+      </c>
+      <c r="O98">
+        <v>-2.367528</v>
+      </c>
+      <c r="P98">
+        <v>-13.415992</v>
+      </c>
+      <c r="Q98">
+        <v>-12.495992</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>4.434052100849133</v>
+      </c>
+      <c r="T98">
+        <v>23.3088364834134</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.06019681742043553</v>
+      </c>
+      <c r="W98">
+        <v>0.224425</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.4013121161362367</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3948100840339655</v>
+      </c>
+      <c r="C99">
+        <v>-44.27251481598061</v>
+      </c>
+      <c r="D99">
+        <v>64.50748518401939</v>
+      </c>
+      <c r="E99">
+        <v>77.65000000000001</v>
+      </c>
+      <c r="F99">
+        <v>111.55</v>
+      </c>
+      <c r="G99">
+        <v>2.77</v>
+      </c>
+      <c r="H99">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>11.5</v>
+      </c>
+      <c r="K99">
+        <v>0.92</v>
+      </c>
+      <c r="L99">
+        <v>10.58</v>
+      </c>
+      <c r="M99">
+        <v>26.63814</v>
+      </c>
+      <c r="N99">
+        <v>-16.05814</v>
+      </c>
+      <c r="O99">
+        <v>-2.408721000000001</v>
+      </c>
+      <c r="P99">
+        <v>-13.649419</v>
+      </c>
+      <c r="Q99">
+        <v>-12.729419</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>5.89913613446551</v>
+      </c>
+      <c r="T99">
+        <v>31.0784486445512</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.05957623167383309</v>
+      </c>
+      <c r="W99">
+        <v>0.2245731958762887</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3971748778255538</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3968100840339654</v>
+      </c>
+      <c r="C100">
+        <v>-45.78288167747884</v>
+      </c>
+      <c r="D100">
+        <v>64.14711832252117</v>
+      </c>
+      <c r="E100">
+        <v>78.80000000000001</v>
+      </c>
+      <c r="F100">
+        <v>112.7</v>
+      </c>
+      <c r="G100">
+        <v>2.77</v>
+      </c>
+      <c r="H100">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>11.5</v>
+      </c>
+      <c r="K100">
+        <v>0.92</v>
+      </c>
+      <c r="L100">
+        <v>10.58</v>
+      </c>
+      <c r="M100">
+        <v>26.91276</v>
+      </c>
+      <c r="N100">
+        <v>-16.33276</v>
+      </c>
+      <c r="O100">
+        <v>-2.449914000000001</v>
+      </c>
+      <c r="P100">
+        <v>-13.882846</v>
+      </c>
+      <c r="Q100">
+        <v>-12.962846</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>8.829304201698264</v>
+      </c>
+      <c r="T100">
+        <v>46.6176729668268</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.05896831094246745</v>
+      </c>
+      <c r="W100">
+        <v>0.2247183673469388</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.393122072949783</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3988100840339655</v>
+      </c>
+      <c r="C101">
+        <v>-47.28924457489407</v>
+      </c>
+      <c r="D101">
+        <v>63.79075542510592</v>
+      </c>
+      <c r="E101">
+        <v>79.94999999999999</v>
+      </c>
+      <c r="F101">
+        <v>113.85</v>
+      </c>
+      <c r="G101">
+        <v>2.77</v>
+      </c>
+      <c r="H101">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>11.5</v>
+      </c>
+      <c r="K101">
+        <v>0.92</v>
+      </c>
+      <c r="L101">
+        <v>10.58</v>
+      </c>
+      <c r="M101">
+        <v>27.18738</v>
+      </c>
+      <c r="N101">
+        <v>-16.60738</v>
+      </c>
+      <c r="O101">
+        <v>-2.491107</v>
+      </c>
+      <c r="P101">
+        <v>-14.116273</v>
+      </c>
+      <c r="Q101">
+        <v>-13.196273</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>17.61980840339653</v>
+      </c>
+      <c r="T101">
+        <v>93.2353459336536</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.05837267143799808</v>
+      </c>
+      <c r="W101">
+        <v>0.2248606060606061</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3891511429199872</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/tunisia/tunisia_recreation.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_recreation.xlsx
@@ -1139,7 +1139,7 @@
         <v>3.27247191011236</v>
       </c>
       <c r="H2">
-        <v>4.02471910112359</v>
+        <v>4.0247191011236</v>
       </c>
       <c r="I2">
         <v>0.390284757118928</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1924586036777757</v>
+        <v>0.192208165772259</v>
       </c>
       <c r="C2">
-        <v>68.51212942866226</v>
+        <v>68.02936333448191</v>
       </c>
       <c r="D2">
-        <v>66.78212942866226</v>
+        <v>66.8963633344819</v>
       </c>
       <c r="E2">
-        <v>-23.3</v>
+        <v>-22.703</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.5970000000000001</v>
       </c>
       <c r="G2">
         <v>1.73</v>
@@ -1451,28 +1451,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0300291</v>
       </c>
       <c r="N2">
-        <v>7.253333333333334</v>
+        <v>7.223304233333334</v>
       </c>
       <c r="O2">
-        <v>1.088</v>
+        <v>1.083495635</v>
       </c>
       <c r="P2">
-        <v>6.165333333333334</v>
+        <v>6.139808598333333</v>
       </c>
       <c r="Q2">
-        <v>8.405333333333335</v>
+        <v>8.379808598333334</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1924586036777757</v>
+        <v>0.1937177937093525</v>
       </c>
       <c r="T2">
-        <v>0.8969457633378592</v>
+        <v>0.904646812821063</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>241.5434806015942</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.192208165772259</v>
+        <v>0.1919577278667424</v>
       </c>
       <c r="C3">
-        <v>68.02936333448191</v>
+        <v>67.54698871464274</v>
       </c>
       <c r="D3">
-        <v>66.8963633344819</v>
+        <v>67.01098871464274</v>
       </c>
       <c r="E3">
-        <v>-22.703</v>
+        <v>-22.106</v>
       </c>
       <c r="F3">
-        <v>0.5970000000000001</v>
+        <v>1.194</v>
       </c>
       <c r="G3">
         <v>1.73</v>
@@ -1533,28 +1533,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M3">
-        <v>0.0300291</v>
+        <v>0.06005820000000001</v>
       </c>
       <c r="N3">
-        <v>7.223304233333334</v>
+        <v>7.193275133333334</v>
       </c>
       <c r="O3">
-        <v>1.083495635</v>
+        <v>1.07899127</v>
       </c>
       <c r="P3">
-        <v>6.139808598333333</v>
+        <v>6.114283863333334</v>
       </c>
       <c r="Q3">
-        <v>8.379808598333334</v>
+        <v>8.354283863333334</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1937177937093525</v>
+        <v>0.1950026814966759</v>
       </c>
       <c r="T3">
-        <v>0.904646812821063</v>
+        <v>0.9125050265794344</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>241.5434806015942</v>
+        <v>120.7717403007971</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1919577278667424</v>
+        <v>0.1917072899612257</v>
       </c>
       <c r="C4">
-        <v>67.54698871464274</v>
+        <v>67.06500758494565</v>
       </c>
       <c r="D4">
-        <v>67.01098871464274</v>
+        <v>67.12600758494564</v>
       </c>
       <c r="E4">
-        <v>-22.106</v>
+        <v>-21.509</v>
       </c>
       <c r="F4">
-        <v>1.194</v>
+        <v>1.791</v>
       </c>
       <c r="G4">
         <v>1.73</v>
@@ -1615,28 +1615,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M4">
-        <v>0.06005820000000001</v>
+        <v>0.0900873</v>
       </c>
       <c r="N4">
-        <v>7.193275133333334</v>
+        <v>7.163246033333333</v>
       </c>
       <c r="O4">
-        <v>1.07899127</v>
+        <v>1.074486905</v>
       </c>
       <c r="P4">
-        <v>6.114283863333334</v>
+        <v>6.088759128333334</v>
       </c>
       <c r="Q4">
-        <v>8.354283863333334</v>
+        <v>8.328759128333335</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1950026814966759</v>
+        <v>0.1963140618156966</v>
       </c>
       <c r="T4">
-        <v>0.9125050265794344</v>
+        <v>0.9205252653637513</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>120.7717403007971</v>
+        <v>80.51449353386475</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1917072899612257</v>
+        <v>0.1914568520557091</v>
       </c>
       <c r="C5">
-        <v>67.06500758494565</v>
+        <v>66.58342197505506</v>
       </c>
       <c r="D5">
-        <v>67.12600758494564</v>
+        <v>67.24142197505506</v>
       </c>
       <c r="E5">
-        <v>-21.509</v>
+        <v>-20.912</v>
       </c>
       <c r="F5">
-        <v>1.791</v>
+        <v>2.388</v>
       </c>
       <c r="G5">
         <v>1.73</v>
@@ -1697,28 +1697,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M5">
-        <v>0.0900873</v>
+        <v>0.1201164</v>
       </c>
       <c r="N5">
-        <v>7.163246033333333</v>
+        <v>7.133216933333334</v>
       </c>
       <c r="O5">
-        <v>1.074486905</v>
+        <v>1.06998254</v>
       </c>
       <c r="P5">
-        <v>6.088759128333334</v>
+        <v>6.063234393333334</v>
       </c>
       <c r="Q5">
-        <v>8.328759128333335</v>
+        <v>8.303234393333334</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1963140618156966</v>
+        <v>0.1976527625580303</v>
       </c>
       <c r="T5">
-        <v>0.9205252653637513</v>
+        <v>0.9287125924560751</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>80.51449353386475</v>
+        <v>60.38587015039856</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1914568520557091</v>
+        <v>0.1912064141501924</v>
       </c>
       <c r="C6">
-        <v>66.58342197505506</v>
+        <v>66.10223392861855</v>
       </c>
       <c r="D6">
-        <v>67.24142197505506</v>
+        <v>67.35723392861854</v>
       </c>
       <c r="E6">
-        <v>-20.912</v>
+        <v>-20.315</v>
       </c>
       <c r="F6">
-        <v>2.388</v>
+        <v>2.985</v>
       </c>
       <c r="G6">
         <v>1.73</v>
@@ -1779,28 +1779,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M6">
-        <v>0.1201164</v>
+        <v>0.1501455</v>
       </c>
       <c r="N6">
-        <v>7.133216933333334</v>
+        <v>7.103187833333334</v>
       </c>
       <c r="O6">
-        <v>1.06998254</v>
+        <v>1.065478175</v>
       </c>
       <c r="P6">
-        <v>6.063234393333334</v>
+        <v>6.037709658333334</v>
       </c>
       <c r="Q6">
-        <v>8.303234393333334</v>
+        <v>8.277709658333334</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1976527625580303</v>
+        <v>0.1990196464738867</v>
       </c>
       <c r="T6">
-        <v>0.9287125924560751</v>
+        <v>0.9370722843292898</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>60.38587015039856</v>
+        <v>48.30869612031885</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1912064141501924</v>
+        <v>0.1909559762446757</v>
       </c>
       <c r="C7">
-        <v>66.10223392861855</v>
+        <v>65.62144550338726</v>
       </c>
       <c r="D7">
-        <v>67.35723392861854</v>
+        <v>67.47344550338725</v>
       </c>
       <c r="E7">
-        <v>-20.315</v>
+        <v>-19.718</v>
       </c>
       <c r="F7">
-        <v>2.985</v>
+        <v>3.582</v>
       </c>
       <c r="G7">
         <v>1.73</v>
@@ -1861,28 +1861,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M7">
-        <v>0.1501455</v>
+        <v>0.1801746</v>
       </c>
       <c r="N7">
-        <v>7.103187833333334</v>
+        <v>7.073158733333334</v>
       </c>
       <c r="O7">
-        <v>1.065478175</v>
+        <v>1.06097381</v>
       </c>
       <c r="P7">
-        <v>6.037709658333334</v>
+        <v>6.012184923333334</v>
       </c>
       <c r="Q7">
-        <v>8.277709658333334</v>
+        <v>8.252184923333335</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1990196464738867</v>
+        <v>0.2004156130262508</v>
       </c>
       <c r="T7">
-        <v>0.9370722843292898</v>
+        <v>0.9456098419870409</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>48.30869612031885</v>
+        <v>40.25724676693237</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1909559762446757</v>
+        <v>0.1907055383391591</v>
       </c>
       <c r="C8">
-        <v>65.62144550338726</v>
+        <v>65.14105877133777</v>
       </c>
       <c r="D8">
-        <v>67.47344550338725</v>
+        <v>67.59005877133777</v>
       </c>
       <c r="E8">
-        <v>-19.718</v>
+        <v>-19.121</v>
       </c>
       <c r="F8">
-        <v>3.582</v>
+        <v>4.178999999999999</v>
       </c>
       <c r="G8">
         <v>1.73</v>
@@ -1943,28 +1943,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M8">
-        <v>0.1801746</v>
+        <v>0.2102037</v>
       </c>
       <c r="N8">
-        <v>7.073158733333334</v>
+        <v>7.043129633333334</v>
       </c>
       <c r="O8">
-        <v>1.06097381</v>
+        <v>1.056469445</v>
       </c>
       <c r="P8">
-        <v>6.012184923333334</v>
+        <v>5.986660188333333</v>
       </c>
       <c r="Q8">
-        <v>8.252184923333335</v>
+        <v>8.226660188333334</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2004156130262508</v>
+        <v>0.2018416003646872</v>
       </c>
       <c r="T8">
-        <v>0.9456098419870409</v>
+        <v>0.9543310030352814</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>40.25724676693238</v>
+        <v>34.50621151451347</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.190705538339159</v>
+        <v>0.1904551004336424</v>
       </c>
       <c r="C9">
-        <v>65.14105877133778</v>
+        <v>64.66107581879547</v>
       </c>
       <c r="D9">
-        <v>67.59005877133778</v>
+        <v>67.70707581879546</v>
       </c>
       <c r="E9">
-        <v>-19.121</v>
+        <v>-18.524</v>
       </c>
       <c r="F9">
-        <v>4.179</v>
+        <v>4.776000000000001</v>
       </c>
       <c r="G9">
         <v>1.73</v>
@@ -2025,28 +2025,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M9">
-        <v>0.2102037</v>
+        <v>0.2402328</v>
       </c>
       <c r="N9">
-        <v>7.043129633333334</v>
+        <v>7.013100533333334</v>
       </c>
       <c r="O9">
-        <v>1.056469445</v>
+        <v>1.05196508</v>
       </c>
       <c r="P9">
-        <v>5.986660188333333</v>
+        <v>5.961135453333334</v>
       </c>
       <c r="Q9">
-        <v>8.226660188333334</v>
+        <v>8.201135453333334</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2018416003646872</v>
+        <v>0.2032985874278722</v>
       </c>
       <c r="T9">
-        <v>0.9543310030352814</v>
+        <v>0.9632417545410923</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>34.50621151451347</v>
+        <v>30.19293507519928</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1904551004336424</v>
+        <v>0.1902046625281257</v>
       </c>
       <c r="C10">
-        <v>64.66107581879547</v>
+        <v>64.18149874655873</v>
       </c>
       <c r="D10">
-        <v>67.70707581879546</v>
+        <v>67.82449874655873</v>
       </c>
       <c r="E10">
-        <v>-18.524</v>
+        <v>-17.927</v>
       </c>
       <c r="F10">
-        <v>4.776000000000001</v>
+        <v>5.373</v>
       </c>
       <c r="G10">
         <v>1.73</v>
@@ -2107,28 +2107,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M10">
-        <v>0.2402328</v>
+        <v>0.2702619</v>
       </c>
       <c r="N10">
-        <v>7.013100533333334</v>
+        <v>6.983071433333333</v>
       </c>
       <c r="O10">
-        <v>1.05196508</v>
+        <v>1.047460715</v>
       </c>
       <c r="P10">
-        <v>5.961135453333334</v>
+        <v>5.935610718333334</v>
       </c>
       <c r="Q10">
-        <v>8.201135453333334</v>
+        <v>8.175610718333335</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2032985874278722</v>
+        <v>0.2047875961847536</v>
       </c>
       <c r="T10">
-        <v>0.9632417545410923</v>
+        <v>0.9723483467393386</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>30.19293507519928</v>
+        <v>26.83816451128825</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1902046625281257</v>
+        <v>0.1899542246226091</v>
       </c>
       <c r="C11">
-        <v>64.18149874655873</v>
+        <v>63.70232967002471</v>
       </c>
       <c r="D11">
-        <v>67.82449874655873</v>
+        <v>67.94232967002471</v>
       </c>
       <c r="E11">
-        <v>-17.927</v>
+        <v>-17.33</v>
       </c>
       <c r="F11">
-        <v>5.373</v>
+        <v>5.97</v>
       </c>
       <c r="G11">
         <v>1.73</v>
@@ -2189,28 +2189,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M11">
-        <v>0.2702619</v>
+        <v>0.300291</v>
       </c>
       <c r="N11">
-        <v>6.983071433333333</v>
+        <v>6.953042333333334</v>
       </c>
       <c r="O11">
-        <v>1.047460715</v>
+        <v>1.04295635</v>
       </c>
       <c r="P11">
-        <v>5.935610718333334</v>
+        <v>5.910085983333334</v>
       </c>
       <c r="Q11">
-        <v>8.175610718333335</v>
+        <v>8.150085983333334</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2047875961847536</v>
+        <v>0.2063096940251212</v>
       </c>
       <c r="T11">
-        <v>0.9723483467393386</v>
+        <v>0.9816573076531016</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>26.83816451128825</v>
+        <v>24.15434806015943</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1899542246226091</v>
+        <v>0.1897037867170924</v>
       </c>
       <c r="C12">
-        <v>63.70232967002471</v>
+        <v>63.22357071931645</v>
       </c>
       <c r="D12">
-        <v>67.94232967002471</v>
+        <v>68.06057071931644</v>
       </c>
       <c r="E12">
-        <v>-17.33</v>
+        <v>-16.733</v>
       </c>
       <c r="F12">
-        <v>5.970000000000001</v>
+        <v>6.567</v>
       </c>
       <c r="G12">
         <v>1.73</v>
@@ -2271,28 +2271,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M12">
-        <v>0.300291</v>
+        <v>0.3303201</v>
       </c>
       <c r="N12">
-        <v>6.953042333333334</v>
+        <v>6.923013233333334</v>
       </c>
       <c r="O12">
-        <v>1.04295635</v>
+        <v>1.038451985</v>
       </c>
       <c r="P12">
-        <v>5.910085983333334</v>
+        <v>5.884561248333334</v>
       </c>
       <c r="Q12">
-        <v>8.150085983333334</v>
+        <v>8.124561248333334</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2063096940251212</v>
+        <v>0.2078659963113398</v>
       </c>
       <c r="T12">
-        <v>0.9816573076531016</v>
+        <v>0.991175458699758</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.15434806015942</v>
+        <v>21.95849823650857</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1897037867170924</v>
+        <v>0.1894533488115758</v>
       </c>
       <c r="C13">
-        <v>63.22357071931645</v>
+        <v>62.74522403941113</v>
       </c>
       <c r="D13">
-        <v>68.06057071931644</v>
+        <v>68.17922403941112</v>
       </c>
       <c r="E13">
-        <v>-16.733</v>
+        <v>-16.136</v>
       </c>
       <c r="F13">
-        <v>6.567</v>
+        <v>7.164</v>
       </c>
       <c r="G13">
         <v>1.73</v>
@@ -2353,28 +2353,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M13">
-        <v>0.3303201</v>
+        <v>0.3603492</v>
       </c>
       <c r="N13">
-        <v>6.923013233333334</v>
+        <v>6.892984133333334</v>
       </c>
       <c r="O13">
-        <v>1.038451985</v>
+        <v>1.03394762</v>
       </c>
       <c r="P13">
-        <v>5.884561248333334</v>
+        <v>5.859036513333334</v>
       </c>
       <c r="Q13">
-        <v>8.124561248333334</v>
+        <v>8.099036513333335</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2078659963113398</v>
+        <v>0.2094576691040634</v>
       </c>
       <c r="T13">
-        <v>0.991175458699758</v>
+        <v>1.000909931361111</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>21.95849823650857</v>
+        <v>20.12862338346619</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1894533488115758</v>
+        <v>0.1892029109060591</v>
       </c>
       <c r="C14">
-        <v>62.74522403941113</v>
+        <v>62.26729179026989</v>
       </c>
       <c r="D14">
-        <v>68.17922403941112</v>
+        <v>68.29829179026989</v>
       </c>
       <c r="E14">
-        <v>-16.136</v>
+        <v>-15.539</v>
       </c>
       <c r="F14">
-        <v>7.164</v>
+        <v>7.761000000000001</v>
       </c>
       <c r="G14">
         <v>1.73</v>
@@ -2435,28 +2435,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M14">
-        <v>0.3603492</v>
+        <v>0.3903783</v>
       </c>
       <c r="N14">
-        <v>6.892984133333334</v>
+        <v>6.862955033333334</v>
       </c>
       <c r="O14">
-        <v>1.03394762</v>
+        <v>1.029443255</v>
       </c>
       <c r="P14">
-        <v>5.859036513333334</v>
+        <v>5.833511778333333</v>
       </c>
       <c r="Q14">
-        <v>8.099036513333335</v>
+        <v>8.073511778333334</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2094576691040634</v>
+        <v>0.21108593207593</v>
       </c>
       <c r="T14">
-        <v>1.000909931361111</v>
+        <v>1.010868185003185</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.12862338346619</v>
+        <v>18.58026773858417</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1892029109060591</v>
+        <v>0.1889524730005424</v>
       </c>
       <c r="C15">
-        <v>62.26729179026989</v>
+        <v>61.78977614696875</v>
       </c>
       <c r="D15">
-        <v>68.29829179026989</v>
+        <v>68.41777614696875</v>
       </c>
       <c r="E15">
-        <v>-15.539</v>
+        <v>-14.942</v>
       </c>
       <c r="F15">
-        <v>7.761000000000001</v>
+        <v>8.358000000000001</v>
       </c>
       <c r="G15">
         <v>1.73</v>
@@ -2517,28 +2517,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M15">
-        <v>0.3903783</v>
+        <v>0.4204074</v>
       </c>
       <c r="N15">
-        <v>6.862955033333334</v>
+        <v>6.832925933333334</v>
       </c>
       <c r="O15">
-        <v>1.029443255</v>
+        <v>1.02493889</v>
       </c>
       <c r="P15">
-        <v>5.833511778333333</v>
+        <v>5.807987043333334</v>
       </c>
       <c r="Q15">
-        <v>8.073511778333334</v>
+        <v>8.047987043333334</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.21108593207593</v>
+        <v>0.2127520616285377</v>
       </c>
       <c r="T15">
-        <v>1.010868185003185</v>
+        <v>1.021058025939261</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.58026773858417</v>
+        <v>17.25310575725673</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1889524730005424</v>
+        <v>0.1887020350950258</v>
       </c>
       <c r="C16">
-        <v>61.78977614696875</v>
+        <v>61.3126792998312</v>
       </c>
       <c r="D16">
-        <v>68.41777614696875</v>
+        <v>68.5376792998312</v>
       </c>
       <c r="E16">
-        <v>-14.942</v>
+        <v>-14.345</v>
       </c>
       <c r="F16">
-        <v>8.358000000000001</v>
+        <v>8.955000000000002</v>
       </c>
       <c r="G16">
         <v>1.73</v>
@@ -2599,28 +2599,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M16">
-        <v>0.4204074</v>
+        <v>0.4504365000000001</v>
       </c>
       <c r="N16">
-        <v>6.832925933333334</v>
+        <v>6.802896833333334</v>
       </c>
       <c r="O16">
-        <v>1.02493889</v>
+        <v>1.020434525</v>
       </c>
       <c r="P16">
-        <v>5.807987043333334</v>
+        <v>5.782462308333334</v>
       </c>
       <c r="Q16">
-        <v>8.047987043333334</v>
+        <v>8.022462308333335</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2127520616285377</v>
+        <v>0.2144573942294421</v>
       </c>
       <c r="T16">
-        <v>1.021058025939261</v>
+        <v>1.031487627838538</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.25310575725673</v>
+        <v>16.10289870677295</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1887020350950258</v>
+        <v>0.1884515971895091</v>
       </c>
       <c r="C17">
-        <v>61.3126792998312</v>
+        <v>60.83600345456197</v>
       </c>
       <c r="D17">
-        <v>68.5376792998312</v>
+        <v>68.65800345456196</v>
       </c>
       <c r="E17">
-        <v>-14.345</v>
+        <v>-13.748</v>
       </c>
       <c r="F17">
-        <v>8.955</v>
+        <v>9.552000000000001</v>
       </c>
       <c r="G17">
         <v>1.73</v>
@@ -2681,28 +2681,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M17">
-        <v>0.4504365</v>
+        <v>0.4804656</v>
       </c>
       <c r="N17">
-        <v>6.802896833333334</v>
+        <v>6.772867733333333</v>
       </c>
       <c r="O17">
-        <v>1.020434525</v>
+        <v>1.01593016</v>
       </c>
       <c r="P17">
-        <v>5.782462308333334</v>
+        <v>5.756937573333333</v>
       </c>
       <c r="Q17">
-        <v>8.022462308333335</v>
+        <v>7.996937573333334</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2144573942294421</v>
+        <v>0.2162033299875108</v>
       </c>
       <c r="T17">
-        <v>1.031487627838538</v>
+        <v>1.04216555359256</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.10289870677295</v>
+        <v>15.09646753759964</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1884515971895091</v>
+        <v>0.1882011592839924</v>
       </c>
       <c r="C18">
-        <v>60.83600345456197</v>
+        <v>60.3597508323823</v>
       </c>
       <c r="D18">
-        <v>68.65800345456196</v>
+        <v>68.7787508323823</v>
       </c>
       <c r="E18">
-        <v>-13.748</v>
+        <v>-13.151</v>
       </c>
       <c r="F18">
-        <v>9.552000000000001</v>
+        <v>10.149</v>
       </c>
       <c r="G18">
         <v>1.73</v>
@@ -2763,28 +2763,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M18">
-        <v>0.4804656</v>
+        <v>0.5104947</v>
       </c>
       <c r="N18">
-        <v>6.772867733333333</v>
+        <v>6.742838633333334</v>
       </c>
       <c r="O18">
-        <v>1.01593016</v>
+        <v>1.011425795</v>
       </c>
       <c r="P18">
-        <v>5.756937573333333</v>
+        <v>5.731412838333334</v>
       </c>
       <c r="Q18">
-        <v>7.996937573333334</v>
+        <v>7.971412838333334</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2162033299875108</v>
+        <v>0.2179913364867379</v>
       </c>
       <c r="T18">
-        <v>1.04216555359256</v>
+        <v>1.053100778762342</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.09646753759964</v>
+        <v>14.2084400353879</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1882011592839924</v>
+        <v>0.1879507213784758</v>
       </c>
       <c r="C19">
-        <v>60.3597508323823</v>
+        <v>59.88392367016659</v>
       </c>
       <c r="D19">
-        <v>68.7787508323823</v>
+        <v>68.89992367016659</v>
       </c>
       <c r="E19">
-        <v>-13.151</v>
+        <v>-12.554</v>
       </c>
       <c r="F19">
-        <v>10.149</v>
+        <v>10.746</v>
       </c>
       <c r="G19">
         <v>1.73</v>
@@ -2845,28 +2845,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M19">
-        <v>0.5104947</v>
+        <v>0.5405238000000001</v>
       </c>
       <c r="N19">
-        <v>6.742838633333334</v>
+        <v>6.712809533333334</v>
       </c>
       <c r="O19">
-        <v>1.011425795</v>
+        <v>1.00692143</v>
       </c>
       <c r="P19">
-        <v>5.731412838333334</v>
+        <v>5.705888103333334</v>
       </c>
       <c r="Q19">
-        <v>7.971412838333334</v>
+        <v>7.945888103333334</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2179913364867379</v>
+        <v>0.2198229529005802</v>
       </c>
       <c r="T19">
-        <v>1.053100778762342</v>
+        <v>1.064302716741143</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.2084400353879</v>
+        <v>13.41908225564412</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1879507213784758</v>
+        <v>0.1879425334729591</v>
       </c>
       <c r="C20">
-        <v>59.88392367016657</v>
+        <v>59.29089254599377</v>
       </c>
       <c r="D20">
-        <v>68.89992367016657</v>
+        <v>68.90389254599377</v>
       </c>
       <c r="E20">
-        <v>-12.554</v>
+        <v>-11.957</v>
       </c>
       <c r="F20">
-        <v>10.746</v>
+        <v>11.343</v>
       </c>
       <c r="G20">
         <v>1.73</v>
@@ -2927,45 +2927,45 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M20">
-        <v>0.5405238</v>
+        <v>0.5875674</v>
       </c>
       <c r="N20">
-        <v>6.712809533333334</v>
+        <v>6.665765933333334</v>
       </c>
       <c r="O20">
-        <v>1.00692143</v>
+        <v>0.99986489</v>
       </c>
       <c r="P20">
-        <v>5.705888103333334</v>
+        <v>5.665901043333333</v>
       </c>
       <c r="Q20">
-        <v>7.945888103333334</v>
+        <v>7.905901043333333</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2198229529005802</v>
+        <v>0.2216997944110606</v>
       </c>
       <c r="T20">
-        <v>1.064302716741143</v>
+        <v>1.075781245781148</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.15</v>
       </c>
       <c r="W20">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>13.41908225564413</v>
+        <v>12.34468306671428</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1879425334729591</v>
+        <v>0.1877048455674424</v>
       </c>
       <c r="C21">
-        <v>59.29089254599377</v>
+        <v>58.80930524973701</v>
       </c>
       <c r="D21">
-        <v>68.90389254599377</v>
+        <v>69.019305249737</v>
       </c>
       <c r="E21">
-        <v>-11.957</v>
+        <v>-11.36</v>
       </c>
       <c r="F21">
-        <v>11.343</v>
+        <v>11.94</v>
       </c>
       <c r="G21">
         <v>1.73</v>
@@ -3009,28 +3009,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M21">
-        <v>0.5875674</v>
+        <v>0.618492</v>
       </c>
       <c r="N21">
-        <v>6.665765933333334</v>
+        <v>6.634841333333334</v>
       </c>
       <c r="O21">
-        <v>0.99986489</v>
+        <v>0.9952262000000001</v>
       </c>
       <c r="P21">
-        <v>5.665901043333333</v>
+        <v>5.639615133333334</v>
       </c>
       <c r="Q21">
-        <v>7.905901043333333</v>
+        <v>7.879615133333334</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2216997944110606</v>
+        <v>0.223623556959303</v>
       </c>
       <c r="T21">
-        <v>1.075781245781148</v>
+        <v>1.087546738047154</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.34468306671428</v>
+        <v>11.72744891337856</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1877048455674424</v>
+        <v>0.1874671576619258</v>
       </c>
       <c r="C22">
-        <v>58.80930524973701</v>
+        <v>58.32810523030957</v>
       </c>
       <c r="D22">
-        <v>69.019305249737</v>
+        <v>69.13510523030958</v>
       </c>
       <c r="E22">
-        <v>-11.36</v>
+        <v>-10.763</v>
       </c>
       <c r="F22">
-        <v>11.94</v>
+        <v>12.537</v>
       </c>
       <c r="G22">
         <v>1.73</v>
@@ -3091,28 +3091,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M22">
-        <v>0.618492</v>
+        <v>0.6494166000000001</v>
       </c>
       <c r="N22">
-        <v>6.634841333333334</v>
+        <v>6.603916733333334</v>
       </c>
       <c r="O22">
-        <v>0.9952262000000001</v>
+        <v>0.99058751</v>
       </c>
       <c r="P22">
-        <v>5.639615133333334</v>
+        <v>5.613329223333333</v>
       </c>
       <c r="Q22">
-        <v>7.879615133333334</v>
+        <v>7.853329223333334</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.223623556959303</v>
+        <v>0.2255960223568681</v>
       </c>
       <c r="T22">
-        <v>1.087546738047154</v>
+        <v>1.099610090876857</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.72744891337856</v>
+        <v>11.16899896512244</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1874671576619258</v>
+        <v>0.1872294697564091</v>
       </c>
       <c r="C23">
-        <v>58.3281052303096</v>
+        <v>57.84729444029652</v>
       </c>
       <c r="D23">
-        <v>69.13510523030959</v>
+        <v>69.25129444029652</v>
       </c>
       <c r="E23">
-        <v>-10.763</v>
+        <v>-10.166</v>
       </c>
       <c r="F23">
-        <v>12.537</v>
+        <v>13.134</v>
       </c>
       <c r="G23">
         <v>1.73</v>
@@ -3173,28 +3173,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M23">
-        <v>0.6494166</v>
+        <v>0.6803412</v>
       </c>
       <c r="N23">
-        <v>6.603916733333334</v>
+        <v>6.572992133333334</v>
       </c>
       <c r="O23">
-        <v>0.99058751</v>
+        <v>0.9859488200000001</v>
       </c>
       <c r="P23">
-        <v>5.613329223333333</v>
+        <v>5.587043313333334</v>
       </c>
       <c r="Q23">
-        <v>7.853329223333334</v>
+        <v>7.827043313333334</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2255960223568681</v>
+        <v>0.2276190637902681</v>
       </c>
       <c r="T23">
-        <v>1.099610090876856</v>
+        <v>1.111982760445782</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.16899896512244</v>
+        <v>10.66131719398051</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1872294697564091</v>
+        <v>0.1869917818508925</v>
       </c>
       <c r="C24">
-        <v>57.84729444029652</v>
+        <v>57.36687484543096</v>
       </c>
       <c r="D24">
-        <v>69.25129444029652</v>
+        <v>69.36787484543096</v>
       </c>
       <c r="E24">
-        <v>-10.166</v>
+        <v>-9.568999999999999</v>
       </c>
       <c r="F24">
-        <v>13.134</v>
+        <v>13.731</v>
       </c>
       <c r="G24">
         <v>1.73</v>
@@ -3255,28 +3255,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M24">
-        <v>0.6803412</v>
+        <v>0.7112658000000001</v>
       </c>
       <c r="N24">
-        <v>6.572992133333334</v>
+        <v>6.542067533333334</v>
       </c>
       <c r="O24">
-        <v>0.9859488200000001</v>
+        <v>0.9813101300000001</v>
       </c>
       <c r="P24">
-        <v>5.587043313333334</v>
+        <v>5.560757403333334</v>
       </c>
       <c r="Q24">
-        <v>7.827043313333334</v>
+        <v>7.800757403333335</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2276190637902681</v>
+        <v>0.2296946517544058</v>
       </c>
       <c r="T24">
-        <v>1.111982760445782</v>
+        <v>1.124676798055459</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.66131719398051</v>
+        <v>10.19778166380745</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1869917818508925</v>
+        <v>0.1871008939453758</v>
       </c>
       <c r="C25">
-        <v>57.36687484543096</v>
+        <v>56.71630919624852</v>
       </c>
       <c r="D25">
-        <v>69.36787484543096</v>
+        <v>69.31430919624852</v>
       </c>
       <c r="E25">
-        <v>-9.568999999999999</v>
+        <v>-8.972</v>
       </c>
       <c r="F25">
-        <v>13.731</v>
+        <v>14.328</v>
       </c>
       <c r="G25">
         <v>1.73</v>
@@ -3337,45 +3337,45 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M25">
-        <v>0.7112658000000001</v>
+        <v>0.766548</v>
       </c>
       <c r="N25">
-        <v>6.542067533333334</v>
+        <v>6.486785333333334</v>
       </c>
       <c r="O25">
-        <v>0.9813101300000001</v>
+        <v>0.9730178</v>
       </c>
       <c r="P25">
-        <v>5.560757403333334</v>
+        <v>5.513767533333334</v>
       </c>
       <c r="Q25">
-        <v>7.800757403333335</v>
+        <v>7.753767533333334</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2296946517544058</v>
+        <v>0.2318248604544418</v>
       </c>
       <c r="T25">
-        <v>1.124676798055459</v>
+        <v>1.137704889286443</v>
       </c>
       <c r="U25">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.15</v>
       </c>
       <c r="W25">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>10.19778166380745</v>
+        <v>9.462334169984572</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1871008939453758</v>
+        <v>0.1868776560398591</v>
       </c>
       <c r="C26">
-        <v>56.71630919624852</v>
+        <v>56.22899049973527</v>
       </c>
       <c r="D26">
-        <v>69.31430919624852</v>
+        <v>69.42399049973527</v>
       </c>
       <c r="E26">
-        <v>-8.972000000000001</v>
+        <v>-8.375</v>
       </c>
       <c r="F26">
-        <v>14.328</v>
+        <v>14.925</v>
       </c>
       <c r="G26">
         <v>1.73</v>
@@ -3419,28 +3419,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M26">
-        <v>0.766548</v>
+        <v>0.7984875</v>
       </c>
       <c r="N26">
-        <v>6.486785333333334</v>
+        <v>6.454845833333334</v>
       </c>
       <c r="O26">
-        <v>0.9730178</v>
+        <v>0.968226875</v>
       </c>
       <c r="P26">
-        <v>5.513767533333334</v>
+        <v>5.486618958333334</v>
       </c>
       <c r="Q26">
-        <v>7.753767533333334</v>
+        <v>7.726618958333334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2318248604544418</v>
+        <v>0.2340118747198121</v>
       </c>
       <c r="T26">
-        <v>1.137704889286443</v>
+        <v>1.151080396283586</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.462334169984572</v>
+        <v>9.083840803185188</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1868776560398591</v>
+        <v>0.1866544181343424</v>
       </c>
       <c r="C27">
-        <v>56.22899049973527</v>
+        <v>55.74201946749535</v>
       </c>
       <c r="D27">
-        <v>69.42399049973527</v>
+        <v>69.53401946749536</v>
       </c>
       <c r="E27">
-        <v>-8.375</v>
+        <v>-7.777999999999999</v>
       </c>
       <c r="F27">
-        <v>14.925</v>
+        <v>15.522</v>
       </c>
       <c r="G27">
         <v>1.73</v>
@@ -3501,28 +3501,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M27">
-        <v>0.7984875</v>
+        <v>0.8304270000000001</v>
       </c>
       <c r="N27">
-        <v>6.454845833333334</v>
+        <v>6.422906333333334</v>
       </c>
       <c r="O27">
-        <v>0.968226875</v>
+        <v>0.96343595</v>
       </c>
       <c r="P27">
-        <v>5.486618958333334</v>
+        <v>5.459470383333334</v>
       </c>
       <c r="Q27">
-        <v>7.726618958333334</v>
+        <v>7.699470383333334</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2340118747198121</v>
+        <v>0.2362579974788412</v>
       </c>
       <c r="T27">
-        <v>1.151080396283586</v>
+        <v>1.164817403469842</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.083840803185188</v>
+        <v>8.734462310754989</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1866544181343424</v>
+        <v>0.1864311802288258</v>
       </c>
       <c r="C28">
-        <v>55.74201946749535</v>
+        <v>55.25539775517538</v>
       </c>
       <c r="D28">
-        <v>69.53401946749536</v>
+        <v>69.64439775517538</v>
       </c>
       <c r="E28">
-        <v>-7.777999999999999</v>
+        <v>-7.180999999999997</v>
       </c>
       <c r="F28">
-        <v>15.522</v>
+        <v>16.119</v>
       </c>
       <c r="G28">
         <v>1.73</v>
@@ -3583,28 +3583,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M28">
-        <v>0.8304270000000001</v>
+        <v>0.8623665000000001</v>
       </c>
       <c r="N28">
-        <v>6.422906333333334</v>
+        <v>6.390966833333334</v>
       </c>
       <c r="O28">
-        <v>0.96343595</v>
+        <v>0.958645025</v>
       </c>
       <c r="P28">
-        <v>5.459470383333334</v>
+        <v>5.432321808333334</v>
       </c>
       <c r="Q28">
-        <v>7.699470383333334</v>
+        <v>7.672321808333334</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2362579974788412</v>
+        <v>0.2385656578477066</v>
       </c>
       <c r="T28">
-        <v>1.164817403469842</v>
+        <v>1.178930767017364</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.734462310754989</v>
+        <v>8.410963706652952</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1864311802288258</v>
+        <v>0.1862079423233091</v>
       </c>
       <c r="C29">
-        <v>55.25539775517538</v>
+        <v>54.76912702895131</v>
       </c>
       <c r="D29">
-        <v>69.64439775517538</v>
+        <v>69.75512702895131</v>
       </c>
       <c r="E29">
-        <v>-7.180999999999997</v>
+        <v>-6.584</v>
       </c>
       <c r="F29">
-        <v>16.119</v>
+        <v>16.716</v>
       </c>
       <c r="G29">
         <v>1.73</v>
@@ -3665,28 +3665,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M29">
-        <v>0.8623665000000001</v>
+        <v>0.894306</v>
       </c>
       <c r="N29">
-        <v>6.390966833333334</v>
+        <v>6.359027333333334</v>
       </c>
       <c r="O29">
-        <v>0.958645025</v>
+        <v>0.9538541</v>
       </c>
       <c r="P29">
-        <v>5.432321808333334</v>
+        <v>5.405173233333334</v>
       </c>
       <c r="Q29">
-        <v>7.672321808333334</v>
+        <v>7.645173233333334</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2385656578477066</v>
+        <v>0.2409374198934849</v>
       </c>
       <c r="T29">
-        <v>1.178930767017364</v>
+        <v>1.193436168441207</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.410963706652952</v>
+        <v>8.110572145701061</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1862079423233091</v>
+        <v>0.1859847044177925</v>
       </c>
       <c r="C30">
-        <v>54.76912702895131</v>
+        <v>54.28320896561242</v>
       </c>
       <c r="D30">
-        <v>69.75512702895131</v>
+        <v>69.86620896561242</v>
       </c>
       <c r="E30">
-        <v>-6.584</v>
+        <v>-5.986999999999998</v>
       </c>
       <c r="F30">
-        <v>16.716</v>
+        <v>17.313</v>
       </c>
       <c r="G30">
         <v>1.73</v>
@@ -3747,28 +3747,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M30">
-        <v>0.894306</v>
+        <v>0.9262455000000001</v>
       </c>
       <c r="N30">
-        <v>6.359027333333334</v>
+        <v>6.327087833333334</v>
       </c>
       <c r="O30">
-        <v>0.9538541</v>
+        <v>0.949063175</v>
       </c>
       <c r="P30">
-        <v>5.405173233333334</v>
+        <v>5.378024658333334</v>
       </c>
       <c r="Q30">
-        <v>7.645173233333334</v>
+        <v>7.618024658333334</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2409374198934849</v>
+        <v>0.2433759921377359</v>
       </c>
       <c r="T30">
-        <v>1.193436168441207</v>
+        <v>1.20835017272206</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.110572145701061</v>
+        <v>7.830897244125162</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1859847044177925</v>
+        <v>0.1859654665122758</v>
       </c>
       <c r="C31">
-        <v>54.28320896561242</v>
+        <v>53.69579820011026</v>
       </c>
       <c r="D31">
-        <v>69.86620896561242</v>
+        <v>69.87579820011025</v>
       </c>
       <c r="E31">
-        <v>-5.987000000000002</v>
+        <v>-5.390000000000001</v>
       </c>
       <c r="F31">
-        <v>17.313</v>
+        <v>17.91</v>
       </c>
       <c r="G31">
         <v>1.73</v>
@@ -3829,45 +3829,45 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M31">
-        <v>0.9262454999999999</v>
+        <v>0.9725130000000001</v>
       </c>
       <c r="N31">
-        <v>6.327087833333334</v>
+        <v>6.280820333333334</v>
       </c>
       <c r="O31">
-        <v>0.949063175</v>
+        <v>0.94212305</v>
       </c>
       <c r="P31">
-        <v>5.378024658333334</v>
+        <v>5.338697283333333</v>
       </c>
       <c r="Q31">
-        <v>7.618024658333334</v>
+        <v>7.578697283333334</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2433759921377359</v>
+        <v>0.2458842378746798</v>
       </c>
       <c r="T31">
-        <v>1.20835017272206</v>
+        <v>1.223690291410937</v>
       </c>
       <c r="U31">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V31">
         <v>0.15</v>
       </c>
       <c r="W31">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y31">
-        <v>7.830897244125163</v>
+        <v>7.458340745402204</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1859654665122758</v>
+        <v>0.1857490286067591</v>
       </c>
       <c r="C32">
-        <v>53.69579820011026</v>
+        <v>53.2068644836658</v>
       </c>
       <c r="D32">
-        <v>69.87579820011025</v>
+        <v>69.9838644836658</v>
       </c>
       <c r="E32">
-        <v>-5.390000000000001</v>
+        <v>-4.792999999999999</v>
       </c>
       <c r="F32">
-        <v>17.91</v>
+        <v>18.507</v>
       </c>
       <c r="G32">
         <v>1.73</v>
@@ -3911,28 +3911,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M32">
-        <v>0.9725130000000001</v>
+        <v>1.0049301</v>
       </c>
       <c r="N32">
-        <v>6.280820333333334</v>
+        <v>6.248403233333334</v>
       </c>
       <c r="O32">
-        <v>0.94212305</v>
+        <v>0.937260485</v>
       </c>
       <c r="P32">
-        <v>5.338697283333333</v>
+        <v>5.311142748333333</v>
       </c>
       <c r="Q32">
-        <v>7.578697283333334</v>
+        <v>7.551142748333334</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2458842378746798</v>
+        <v>0.2484651863866075</v>
       </c>
       <c r="T32">
-        <v>1.223690291410937</v>
+        <v>1.23947505122123</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.458340745402204</v>
+        <v>7.217749108453745</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1857490286067591</v>
+        <v>0.1855325907012425</v>
       </c>
       <c r="C33">
-        <v>53.2068644836658</v>
+        <v>52.71826554438323</v>
       </c>
       <c r="D33">
-        <v>69.9838644836658</v>
+        <v>70.09226554438322</v>
       </c>
       <c r="E33">
-        <v>-4.792999999999999</v>
+        <v>-4.195999999999998</v>
       </c>
       <c r="F33">
-        <v>18.507</v>
+        <v>19.104</v>
       </c>
       <c r="G33">
         <v>1.73</v>
@@ -3993,28 +3993,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M33">
-        <v>1.0049301</v>
+        <v>1.0373472</v>
       </c>
       <c r="N33">
-        <v>6.248403233333334</v>
+        <v>6.215986133333334</v>
       </c>
       <c r="O33">
-        <v>0.937260485</v>
+        <v>0.93239792</v>
       </c>
       <c r="P33">
-        <v>5.311142748333333</v>
+        <v>5.283588213333334</v>
       </c>
       <c r="Q33">
-        <v>7.551142748333334</v>
+        <v>7.523588213333334</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2484651863866075</v>
+        <v>0.251122045148886</v>
       </c>
       <c r="T33">
-        <v>1.23947505122123</v>
+        <v>1.255724068673003</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.217749108453745</v>
+        <v>6.992194448814566</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1855325907012425</v>
+        <v>0.1853161527957258</v>
       </c>
       <c r="C34">
-        <v>52.71826554438323</v>
+        <v>52.23000294032872</v>
       </c>
       <c r="D34">
-        <v>70.09226554438322</v>
+        <v>70.20100294032872</v>
       </c>
       <c r="E34">
-        <v>-4.195999999999998</v>
+        <v>-3.599</v>
       </c>
       <c r="F34">
-        <v>19.104</v>
+        <v>19.701</v>
       </c>
       <c r="G34">
         <v>1.73</v>
@@ -4075,28 +4075,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M34">
-        <v>1.0373472</v>
+        <v>1.0697643</v>
       </c>
       <c r="N34">
-        <v>6.215986133333334</v>
+        <v>6.183569033333334</v>
       </c>
       <c r="O34">
-        <v>0.93239792</v>
+        <v>0.9275353550000001</v>
       </c>
       <c r="P34">
-        <v>5.283588213333334</v>
+        <v>5.256033678333334</v>
       </c>
       <c r="Q34">
-        <v>7.523588213333334</v>
+        <v>7.496033678333334</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.251122045148886</v>
+        <v>0.253858213127949</v>
       </c>
       <c r="T34">
-        <v>1.255724068673003</v>
+        <v>1.272458131421844</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.992194448814566</v>
+        <v>6.780309768547458</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1853161527957258</v>
+        <v>0.1850997148902092</v>
       </c>
       <c r="C35">
-        <v>52.23000294032872</v>
+        <v>51.74207823925197</v>
       </c>
       <c r="D35">
-        <v>70.20100294032872</v>
+        <v>70.31007823925196</v>
       </c>
       <c r="E35">
-        <v>-3.599</v>
+        <v>-3.001999999999999</v>
       </c>
       <c r="F35">
-        <v>19.701</v>
+        <v>20.298</v>
       </c>
       <c r="G35">
         <v>1.73</v>
@@ -4157,28 +4157,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M35">
-        <v>1.0697643</v>
+        <v>1.1021814</v>
       </c>
       <c r="N35">
-        <v>6.183569033333334</v>
+        <v>6.151151933333334</v>
       </c>
       <c r="O35">
-        <v>0.9275353550000001</v>
+        <v>0.92267279</v>
       </c>
       <c r="P35">
-        <v>5.256033678333334</v>
+        <v>5.228479143333334</v>
       </c>
       <c r="Q35">
-        <v>7.496033678333334</v>
+        <v>7.468479143333334</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.253858213127949</v>
+        <v>0.2566772952881957</v>
       </c>
       <c r="T35">
-        <v>1.272458131421844</v>
+        <v>1.289699286981255</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.780309768547458</v>
+        <v>6.580888893001944</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1850997148902092</v>
+        <v>0.1848832769846925</v>
       </c>
       <c r="C36">
-        <v>51.74207823925197</v>
+        <v>51.2544930186614</v>
       </c>
       <c r="D36">
-        <v>70.31007823925196</v>
+        <v>70.4194930186614</v>
       </c>
       <c r="E36">
-        <v>-3.001999999999999</v>
+        <v>-2.404999999999998</v>
       </c>
       <c r="F36">
-        <v>20.298</v>
+        <v>20.895</v>
       </c>
       <c r="G36">
         <v>1.73</v>
@@ -4239,28 +4239,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M36">
-        <v>1.1021814</v>
+        <v>1.1345985</v>
       </c>
       <c r="N36">
-        <v>6.151151933333334</v>
+        <v>6.118734833333334</v>
       </c>
       <c r="O36">
-        <v>0.92267279</v>
+        <v>0.917810225</v>
       </c>
       <c r="P36">
-        <v>5.228479143333334</v>
+        <v>5.200924608333334</v>
       </c>
       <c r="Q36">
-        <v>7.468479143333334</v>
+        <v>7.440924608333334</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2566772952881957</v>
+        <v>0.2595831184379884</v>
       </c>
       <c r="T36">
-        <v>1.289699286981255</v>
+        <v>1.307470939634803</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.580888893001944</v>
+        <v>6.39286349605903</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1848832769846925</v>
+        <v>0.1846668390791758</v>
       </c>
       <c r="C37">
-        <v>51.2544930186614</v>
+        <v>50.76724886590014</v>
       </c>
       <c r="D37">
-        <v>70.4194930186614</v>
+        <v>70.52924886590014</v>
       </c>
       <c r="E37">
-        <v>-2.404999999999998</v>
+        <v>-1.807999999999996</v>
       </c>
       <c r="F37">
-        <v>20.895</v>
+        <v>21.492</v>
       </c>
       <c r="G37">
         <v>1.73</v>
@@ -4321,28 +4321,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M37">
-        <v>1.1345985</v>
+        <v>1.1670156</v>
       </c>
       <c r="N37">
-        <v>6.118734833333334</v>
+        <v>6.086317733333334</v>
       </c>
       <c r="O37">
-        <v>0.917810225</v>
+        <v>0.91294766</v>
       </c>
       <c r="P37">
-        <v>5.200924608333334</v>
+        <v>5.173370073333333</v>
       </c>
       <c r="Q37">
-        <v>7.440924608333334</v>
+        <v>7.413370073333334</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2595831184379884</v>
+        <v>0.2625797485612122</v>
       </c>
       <c r="T37">
-        <v>1.307470939634803</v>
+        <v>1.325797956433773</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.39286349605903</v>
+        <v>6.215283954501835</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1846668390791758</v>
+        <v>0.1847649011736592</v>
       </c>
       <c r="C38">
-        <v>50.76724886590016</v>
+        <v>50.12047913406343</v>
       </c>
       <c r="D38">
-        <v>70.52924886590016</v>
+        <v>70.47947913406342</v>
       </c>
       <c r="E38">
-        <v>-1.808</v>
+        <v>-1.210999999999999</v>
       </c>
       <c r="F38">
-        <v>21.492</v>
+        <v>22.089</v>
       </c>
       <c r="G38">
         <v>1.73</v>
@@ -4403,45 +4403,45 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M38">
-        <v>1.1670156</v>
+        <v>1.2215217</v>
       </c>
       <c r="N38">
-        <v>6.086317733333334</v>
+        <v>6.031811633333334</v>
       </c>
       <c r="O38">
-        <v>0.91294766</v>
+        <v>0.904771745</v>
       </c>
       <c r="P38">
-        <v>5.173370073333333</v>
+        <v>5.127039888333334</v>
       </c>
       <c r="Q38">
-        <v>7.413370073333334</v>
+        <v>7.367039888333334</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2625797485612122</v>
+        <v>0.265671509799459</v>
       </c>
       <c r="T38">
-        <v>1.325797956433773</v>
+        <v>1.344706783289854</v>
       </c>
       <c r="U38">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V38">
         <v>0.15</v>
       </c>
       <c r="W38">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>6.215283954501837</v>
+        <v>5.937948816900537</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1847649011736592</v>
+        <v>0.1845569632681425</v>
       </c>
       <c r="C39">
-        <v>50.12047913406343</v>
+        <v>49.62909801565228</v>
       </c>
       <c r="D39">
-        <v>70.47947913406342</v>
+        <v>70.58509801565228</v>
       </c>
       <c r="E39">
-        <v>-1.210999999999999</v>
+        <v>-0.6140000000000008</v>
       </c>
       <c r="F39">
-        <v>22.089</v>
+        <v>22.686</v>
       </c>
       <c r="G39">
         <v>1.73</v>
@@ -4485,28 +4485,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M39">
-        <v>1.2215217</v>
+        <v>1.2545358</v>
       </c>
       <c r="N39">
-        <v>6.031811633333334</v>
+        <v>5.998797533333334</v>
       </c>
       <c r="O39">
-        <v>0.904771745</v>
+        <v>0.89981963</v>
       </c>
       <c r="P39">
-        <v>5.127039888333334</v>
+        <v>5.098977903333334</v>
       </c>
       <c r="Q39">
-        <v>7.367039888333334</v>
+        <v>7.338977903333334</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.265671509799459</v>
+        <v>0.2688630052711976</v>
       </c>
       <c r="T39">
-        <v>1.344706783289854</v>
+        <v>1.364225572302583</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.937948816900537</v>
+        <v>5.781687005929471</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1845569632681425</v>
+        <v>0.1843490253626258</v>
       </c>
       <c r="C40">
-        <v>49.62909801565228</v>
+        <v>49.13803392825542</v>
       </c>
       <c r="D40">
-        <v>70.58509801565228</v>
+        <v>70.69103392825542</v>
       </c>
       <c r="E40">
-        <v>-0.6140000000000008</v>
+        <v>-0.01699999999999946</v>
       </c>
       <c r="F40">
-        <v>22.686</v>
+        <v>23.283</v>
       </c>
       <c r="G40">
         <v>1.73</v>
@@ -4567,28 +4567,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M40">
-        <v>1.2545358</v>
+        <v>1.2875499</v>
       </c>
       <c r="N40">
-        <v>5.998797533333334</v>
+        <v>5.965783433333334</v>
       </c>
       <c r="O40">
-        <v>0.89981963</v>
+        <v>0.8948675150000001</v>
       </c>
       <c r="P40">
-        <v>5.098977903333334</v>
+        <v>5.070915918333334</v>
       </c>
       <c r="Q40">
-        <v>7.338977903333334</v>
+        <v>7.310915918333334</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2688630052711976</v>
+        <v>0.2721591399387308</v>
       </c>
       <c r="T40">
-        <v>1.364225572302583</v>
+        <v>1.38438432161081</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.781687005929471</v>
+        <v>5.633438621162048</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1843490253626258</v>
+        <v>0.1841410874571092</v>
       </c>
       <c r="C41">
-        <v>49.13803392825542</v>
+        <v>48.64728830144301</v>
       </c>
       <c r="D41">
-        <v>70.69103392825542</v>
+        <v>70.797288301443</v>
       </c>
       <c r="E41">
-        <v>-0.01699999999999946</v>
+        <v>0.5800000000000018</v>
       </c>
       <c r="F41">
-        <v>23.283</v>
+        <v>23.88</v>
       </c>
       <c r="G41">
         <v>1.73</v>
@@ -4649,28 +4649,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M41">
-        <v>1.2875499</v>
+        <v>1.320564</v>
       </c>
       <c r="N41">
-        <v>5.965783433333334</v>
+        <v>5.932769333333334</v>
       </c>
       <c r="O41">
-        <v>0.8948675150000001</v>
+        <v>0.8899154</v>
       </c>
       <c r="P41">
-        <v>5.070915918333334</v>
+        <v>5.042853933333333</v>
       </c>
       <c r="Q41">
-        <v>7.310915918333334</v>
+        <v>7.282853933333334</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2721591399387308</v>
+        <v>0.2755651457618487</v>
       </c>
       <c r="T41">
-        <v>1.38438432161081</v>
+        <v>1.405215029229313</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.633438621162048</v>
+        <v>5.492602655632997</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1841410874571092</v>
+        <v>0.1839331495515925</v>
       </c>
       <c r="C42">
-        <v>48.64728830144301</v>
+        <v>48.1568625733933</v>
       </c>
       <c r="D42">
-        <v>70.797288301443</v>
+        <v>70.9038625733933</v>
       </c>
       <c r="E42">
-        <v>0.5800000000000018</v>
+        <v>1.177000000000003</v>
       </c>
       <c r="F42">
-        <v>23.88</v>
+        <v>24.477</v>
       </c>
       <c r="G42">
         <v>1.73</v>
@@ -4731,28 +4731,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M42">
-        <v>1.320564</v>
+        <v>1.3535781</v>
       </c>
       <c r="N42">
-        <v>5.932769333333334</v>
+        <v>5.899755233333334</v>
       </c>
       <c r="O42">
-        <v>0.8899154</v>
+        <v>0.8849632850000001</v>
       </c>
       <c r="P42">
-        <v>5.042853933333333</v>
+        <v>5.014791948333333</v>
       </c>
       <c r="Q42">
-        <v>7.282853933333334</v>
+        <v>7.254791948333334</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2755651457618487</v>
+        <v>0.2790866094094788</v>
       </c>
       <c r="T42">
-        <v>1.405215029229313</v>
+        <v>1.426751862529798</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.492602655632997</v>
+        <v>5.358636737202923</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1839331495515925</v>
+        <v>0.1837252116460758</v>
       </c>
       <c r="C43">
-        <v>48.1568625733933</v>
+        <v>47.6667581909573</v>
       </c>
       <c r="D43">
-        <v>70.9038625733933</v>
+        <v>71.0107581909573</v>
       </c>
       <c r="E43">
-        <v>1.177000000000003</v>
+        <v>1.774000000000004</v>
       </c>
       <c r="F43">
-        <v>24.477</v>
+        <v>25.07400000000001</v>
       </c>
       <c r="G43">
         <v>1.73</v>
@@ -4813,28 +4813,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M43">
-        <v>1.3535781</v>
+        <v>1.3865922</v>
       </c>
       <c r="N43">
-        <v>5.899755233333334</v>
+        <v>5.866741133333333</v>
       </c>
       <c r="O43">
-        <v>0.8849632850000001</v>
+        <v>0.88001117</v>
       </c>
       <c r="P43">
-        <v>5.014791948333333</v>
+        <v>4.986729963333334</v>
       </c>
       <c r="Q43">
-        <v>7.254791948333334</v>
+        <v>7.226729963333334</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2790866094094788</v>
+        <v>0.2827295028380618</v>
       </c>
       <c r="T43">
-        <v>1.426751862529798</v>
+        <v>1.449031345254438</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.358636737202923</v>
+        <v>5.2310501482219</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1837252116460759</v>
+        <v>0.1835172737405592</v>
       </c>
       <c r="C44">
-        <v>47.6667581909573</v>
+        <v>47.1769766097244</v>
       </c>
       <c r="D44">
-        <v>71.01075819095729</v>
+        <v>71.11797660972439</v>
       </c>
       <c r="E44">
-        <v>1.774000000000001</v>
+        <v>2.370999999999999</v>
       </c>
       <c r="F44">
-        <v>25.074</v>
+        <v>25.671</v>
       </c>
       <c r="G44">
         <v>1.73</v>
@@ -4895,28 +4895,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M44">
-        <v>1.3865922</v>
+        <v>1.4196063</v>
       </c>
       <c r="N44">
-        <v>5.866741133333334</v>
+        <v>5.833727033333334</v>
       </c>
       <c r="O44">
-        <v>0.8800111700000001</v>
+        <v>0.875059055</v>
       </c>
       <c r="P44">
-        <v>4.986729963333334</v>
+        <v>4.958667978333334</v>
       </c>
       <c r="Q44">
-        <v>7.226729963333334</v>
+        <v>7.198667978333334</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2827295028380618</v>
+        <v>0.2865002170887003</v>
       </c>
       <c r="T44">
-        <v>1.449031345254438</v>
+        <v>1.47209256421503</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.231050148221902</v>
+        <v>5.109397819193486</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1835172737405592</v>
+        <v>0.1833093358350425</v>
       </c>
       <c r="C45">
-        <v>47.1769766097244</v>
+        <v>46.68751929408839</v>
       </c>
       <c r="D45">
-        <v>71.11797660972439</v>
+        <v>71.22551929408839</v>
       </c>
       <c r="E45">
-        <v>2.370999999999999</v>
+        <v>2.968</v>
       </c>
       <c r="F45">
-        <v>25.671</v>
+        <v>26.268</v>
       </c>
       <c r="G45">
         <v>1.73</v>
@@ -4977,28 +4977,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M45">
-        <v>1.4196063</v>
+        <v>1.4526204</v>
       </c>
       <c r="N45">
-        <v>5.833727033333334</v>
+        <v>5.800712933333334</v>
       </c>
       <c r="O45">
-        <v>0.875059055</v>
+        <v>0.8701069400000001</v>
       </c>
       <c r="P45">
-        <v>4.958667978333334</v>
+        <v>4.930605993333334</v>
       </c>
       <c r="Q45">
-        <v>7.198667978333334</v>
+        <v>7.170605993333334</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2865002170887003</v>
+        <v>0.290405599705433</v>
       </c>
       <c r="T45">
-        <v>1.47209256421503</v>
+        <v>1.495977398138501</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.109397819193486</v>
+        <v>4.993275141484544</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1833093358350425</v>
+        <v>0.1831013979295259</v>
       </c>
       <c r="C46">
-        <v>46.68751929408839</v>
+        <v>46.19838771731411</v>
       </c>
       <c r="D46">
-        <v>71.22551929408839</v>
+        <v>71.33338771731411</v>
       </c>
       <c r="E46">
-        <v>2.968</v>
+        <v>3.565000000000001</v>
       </c>
       <c r="F46">
-        <v>26.268</v>
+        <v>26.865</v>
       </c>
       <c r="G46">
         <v>1.73</v>
@@ -5059,28 +5059,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M46">
-        <v>1.4526204</v>
+        <v>1.4856345</v>
       </c>
       <c r="N46">
-        <v>5.800712933333334</v>
+        <v>5.767698833333334</v>
       </c>
       <c r="O46">
-        <v>0.8701069400000001</v>
+        <v>0.8651548250000001</v>
       </c>
       <c r="P46">
-        <v>4.930605993333334</v>
+        <v>4.902544008333334</v>
       </c>
       <c r="Q46">
-        <v>7.170605993333334</v>
+        <v>7.142544008333334</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.290405599705433</v>
+        <v>0.2944529962355015</v>
       </c>
       <c r="T46">
-        <v>1.495977398138501</v>
+        <v>1.52073077147737</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.993275141484544</v>
+        <v>4.882313471673775</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1831013979295259</v>
+        <v>0.1828934600240092</v>
       </c>
       <c r="C47">
-        <v>46.19838771731411</v>
+        <v>45.70958336160488</v>
       </c>
       <c r="D47">
-        <v>71.33338771731411</v>
+        <v>71.44158336160488</v>
       </c>
       <c r="E47">
-        <v>3.565000000000001</v>
+        <v>4.162000000000003</v>
       </c>
       <c r="F47">
-        <v>26.865</v>
+        <v>27.462</v>
       </c>
       <c r="G47">
         <v>1.73</v>
@@ -5141,28 +5141,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M47">
-        <v>1.4856345</v>
+        <v>1.5186486</v>
       </c>
       <c r="N47">
-        <v>5.767698833333334</v>
+        <v>5.734684733333333</v>
       </c>
       <c r="O47">
-        <v>0.8651548250000001</v>
+        <v>0.8602027099999999</v>
       </c>
       <c r="P47">
-        <v>4.902544008333334</v>
+        <v>4.874482023333333</v>
       </c>
       <c r="Q47">
-        <v>7.142544008333334</v>
+        <v>7.114482023333333</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2944529962355015</v>
+        <v>0.2986502963407577</v>
       </c>
       <c r="T47">
-        <v>1.52073077147737</v>
+        <v>1.546400936421383</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.882313471673775</v>
+        <v>4.776176222289562</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1828934600240092</v>
+        <v>0.1826855221184925</v>
       </c>
       <c r="C48">
-        <v>45.70958336160488</v>
+        <v>45.22110771817011</v>
       </c>
       <c r="D48">
-        <v>71.44158336160488</v>
+        <v>71.55010771817011</v>
       </c>
       <c r="E48">
-        <v>4.162000000000003</v>
+        <v>4.759000000000004</v>
       </c>
       <c r="F48">
-        <v>27.462</v>
+        <v>28.059</v>
       </c>
       <c r="G48">
         <v>1.73</v>
@@ -5223,28 +5223,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M48">
-        <v>1.5186486</v>
+        <v>1.5516627</v>
       </c>
       <c r="N48">
-        <v>5.734684733333333</v>
+        <v>5.701670633333333</v>
       </c>
       <c r="O48">
-        <v>0.8602027099999999</v>
+        <v>0.855250595</v>
       </c>
       <c r="P48">
-        <v>4.874482023333333</v>
+        <v>4.846420038333333</v>
       </c>
       <c r="Q48">
-        <v>7.114482023333333</v>
+        <v>7.086420038333333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2986502963407577</v>
+        <v>0.3030059851292312</v>
       </c>
       <c r="T48">
-        <v>1.546400936421383</v>
+        <v>1.573039786834981</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.776176222289562</v>
+        <v>4.674555451602551</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1826855221184925</v>
+        <v>0.1824775842129759</v>
       </c>
       <c r="C49">
-        <v>45.22110771817011</v>
+        <v>44.73296228729409</v>
       </c>
       <c r="D49">
-        <v>71.55010771817011</v>
+        <v>71.65896228729409</v>
       </c>
       <c r="E49">
-        <v>4.759000000000004</v>
+        <v>5.356000000000002</v>
       </c>
       <c r="F49">
-        <v>28.059</v>
+        <v>28.656</v>
       </c>
       <c r="G49">
         <v>1.73</v>
@@ -5305,28 +5305,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M49">
-        <v>1.5516627</v>
+        <v>1.5846768</v>
       </c>
       <c r="N49">
-        <v>5.701670633333333</v>
+        <v>5.668656533333333</v>
       </c>
       <c r="O49">
-        <v>0.855250595</v>
+        <v>0.85029848</v>
       </c>
       <c r="P49">
-        <v>4.846420038333333</v>
+        <v>4.818358053333333</v>
       </c>
       <c r="Q49">
-        <v>7.086420038333333</v>
+        <v>7.058358053333333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3030059851292312</v>
+        <v>0.3075292004095689</v>
       </c>
       <c r="T49">
-        <v>1.573039786834981</v>
+        <v>1.600703208418333</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.674555451602551</v>
+        <v>4.577168879694164</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1824775842129759</v>
+        <v>0.1833108963074592</v>
       </c>
       <c r="C50">
-        <v>44.73296228729409</v>
+        <v>43.70171102753491</v>
       </c>
       <c r="D50">
-        <v>71.65896228729409</v>
+        <v>71.22471102753491</v>
       </c>
       <c r="E50">
-        <v>5.355999999999998</v>
+        <v>5.952999999999999</v>
       </c>
       <c r="F50">
-        <v>28.656</v>
+        <v>29.253</v>
       </c>
       <c r="G50">
         <v>1.73</v>
@@ -5387,45 +5387,45 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M50">
-        <v>1.5846768</v>
+        <v>1.6908234</v>
       </c>
       <c r="N50">
-        <v>5.668656533333333</v>
+        <v>5.562509933333334</v>
       </c>
       <c r="O50">
-        <v>0.85029848</v>
+        <v>0.83437649</v>
       </c>
       <c r="P50">
-        <v>4.818358053333333</v>
+        <v>4.728133443333333</v>
       </c>
       <c r="Q50">
-        <v>7.058358053333333</v>
+        <v>6.968133443333334</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3075292004095689</v>
+        <v>0.3122297966812925</v>
       </c>
       <c r="T50">
-        <v>1.600703208418333</v>
+        <v>1.629451470063777</v>
       </c>
       <c r="U50">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V50">
         <v>0.15</v>
       </c>
       <c r="W50">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.577168879694165</v>
+        <v>4.28982313193284</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1833108963074592</v>
+        <v>0.1831242084019425</v>
       </c>
       <c r="C51">
-        <v>43.70171102753491</v>
+        <v>43.20153876299027</v>
       </c>
       <c r="D51">
-        <v>71.22471102753491</v>
+        <v>71.32153876299027</v>
       </c>
       <c r="E51">
-        <v>5.952999999999999</v>
+        <v>6.550000000000001</v>
       </c>
       <c r="F51">
-        <v>29.253</v>
+        <v>29.85</v>
       </c>
       <c r="G51">
         <v>1.73</v>
@@ -5469,28 +5469,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M51">
-        <v>1.6908234</v>
+        <v>1.72533</v>
       </c>
       <c r="N51">
-        <v>5.562509933333334</v>
+        <v>5.528003333333333</v>
       </c>
       <c r="O51">
-        <v>0.83437649</v>
+        <v>0.8292005</v>
       </c>
       <c r="P51">
-        <v>4.728133443333333</v>
+        <v>4.698802833333334</v>
       </c>
       <c r="Q51">
-        <v>6.968133443333334</v>
+        <v>6.938802833333334</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3122297966812925</v>
+        <v>0.3171184168038851</v>
       </c>
       <c r="T51">
-        <v>1.629451470063777</v>
+        <v>1.65934966217504</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.28982313193284</v>
+        <v>4.204026669294183</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1831242084019425</v>
+        <v>0.1829375204964259</v>
       </c>
       <c r="C52">
-        <v>43.20153876299027</v>
+        <v>42.7016301253081</v>
       </c>
       <c r="D52">
-        <v>71.32153876299027</v>
+        <v>71.4186301253081</v>
       </c>
       <c r="E52">
-        <v>6.550000000000001</v>
+        <v>7.147000000000002</v>
       </c>
       <c r="F52">
-        <v>29.85</v>
+        <v>30.447</v>
       </c>
       <c r="G52">
         <v>1.73</v>
@@ -5551,28 +5551,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M52">
-        <v>1.72533</v>
+        <v>1.7598366</v>
       </c>
       <c r="N52">
-        <v>5.528003333333333</v>
+        <v>5.493496733333334</v>
       </c>
       <c r="O52">
-        <v>0.8292005</v>
+        <v>0.8240245100000001</v>
       </c>
       <c r="P52">
-        <v>4.698802833333334</v>
+        <v>4.669472223333334</v>
       </c>
       <c r="Q52">
-        <v>6.938802833333334</v>
+        <v>6.909472223333334</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3171184168038851</v>
+        <v>0.3222065724416854</v>
       </c>
       <c r="T52">
-        <v>1.65934966217504</v>
+        <v>1.69046818865819</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.204026669294183</v>
+        <v>4.121594773817827</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1829375204964259</v>
+        <v>0.1827508325909092</v>
       </c>
       <c r="C53">
-        <v>42.7016301253081</v>
+        <v>42.20198619259681</v>
       </c>
       <c r="D53">
-        <v>71.4186301253081</v>
+        <v>71.51598619259681</v>
       </c>
       <c r="E53">
-        <v>7.147000000000002</v>
+        <v>7.744000000000003</v>
       </c>
       <c r="F53">
-        <v>30.447</v>
+        <v>31.044</v>
       </c>
       <c r="G53">
         <v>1.73</v>
@@ -5633,28 +5633,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M53">
-        <v>1.7598366</v>
+        <v>1.7943432</v>
       </c>
       <c r="N53">
-        <v>5.493496733333334</v>
+        <v>5.458990133333334</v>
       </c>
       <c r="O53">
-        <v>0.8240245100000001</v>
+        <v>0.8188485200000001</v>
       </c>
       <c r="P53">
-        <v>4.669472223333334</v>
+        <v>4.640141613333333</v>
       </c>
       <c r="Q53">
-        <v>6.909472223333334</v>
+        <v>6.880141613333334</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3222065724416854</v>
+        <v>0.3275067345643942</v>
       </c>
       <c r="T53">
-        <v>1.69046818865819</v>
+        <v>1.722883320411471</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.121594773817827</v>
+        <v>4.042333335859791</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1827508325909092</v>
+        <v>0.1841408946853925</v>
       </c>
       <c r="C54">
-        <v>42.20198619259681</v>
+        <v>40.88638695422989</v>
       </c>
       <c r="D54">
-        <v>71.51598619259681</v>
+        <v>70.79738695422989</v>
       </c>
       <c r="E54">
-        <v>7.744000000000003</v>
+        <v>8.341000000000001</v>
       </c>
       <c r="F54">
-        <v>31.044</v>
+        <v>31.641</v>
       </c>
       <c r="G54">
         <v>1.73</v>
@@ -5715,45 +5715,45 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M54">
-        <v>1.7943432</v>
+        <v>1.9395933</v>
       </c>
       <c r="N54">
-        <v>5.458990133333334</v>
+        <v>5.313740033333334</v>
       </c>
       <c r="O54">
-        <v>0.8188485200000001</v>
+        <v>0.797061005</v>
       </c>
       <c r="P54">
-        <v>4.640141613333333</v>
+        <v>4.516679028333334</v>
       </c>
       <c r="Q54">
-        <v>6.880141613333334</v>
+        <v>6.756679028333334</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3275067345643942</v>
+        <v>0.3330324355008352</v>
       </c>
       <c r="T54">
-        <v>1.722883320411471</v>
+        <v>1.756677819473403</v>
       </c>
       <c r="U54">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V54">
         <v>0.15</v>
       </c>
       <c r="W54">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>4.042333335859791</v>
+        <v>3.739615585047305</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1841408946853925</v>
+        <v>0.1839839567798759</v>
       </c>
       <c r="C55">
-        <v>40.88638695422989</v>
+        <v>40.36979276893923</v>
       </c>
       <c r="D55">
-        <v>70.79738695422989</v>
+        <v>70.87779276893923</v>
       </c>
       <c r="E55">
-        <v>8.341000000000001</v>
+        <v>8.938000000000006</v>
       </c>
       <c r="F55">
-        <v>31.641</v>
+        <v>32.23800000000001</v>
       </c>
       <c r="G55">
         <v>1.73</v>
@@ -5797,28 +5797,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M55">
-        <v>1.9395933</v>
+        <v>1.9761894</v>
       </c>
       <c r="N55">
-        <v>5.313740033333334</v>
+        <v>5.277143933333333</v>
       </c>
       <c r="O55">
-        <v>0.797061005</v>
+        <v>0.7915715899999999</v>
       </c>
       <c r="P55">
-        <v>4.516679028333334</v>
+        <v>4.485572343333333</v>
       </c>
       <c r="Q55">
-        <v>6.756679028333334</v>
+        <v>6.725572343333333</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3330324355008352</v>
+        <v>0.338798384304078</v>
       </c>
       <c r="T55">
-        <v>1.756677819473403</v>
+        <v>1.791941644581506</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.739615585047305</v>
+        <v>3.670363444583466</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1839839567798759</v>
+        <v>0.1838270188743592</v>
       </c>
       <c r="C56">
-        <v>40.36979276893923</v>
+        <v>39.85338142785192</v>
       </c>
       <c r="D56">
-        <v>70.87779276893923</v>
+        <v>70.95838142785192</v>
       </c>
       <c r="E56">
-        <v>8.938000000000006</v>
+        <v>9.535</v>
       </c>
       <c r="F56">
-        <v>32.23800000000001</v>
+        <v>32.835</v>
       </c>
       <c r="G56">
         <v>1.73</v>
@@ -5879,28 +5879,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M56">
-        <v>1.9761894</v>
+        <v>2.0127855</v>
       </c>
       <c r="N56">
-        <v>5.277143933333333</v>
+        <v>5.240547833333334</v>
       </c>
       <c r="O56">
-        <v>0.7915715899999999</v>
+        <v>0.7860821750000001</v>
       </c>
       <c r="P56">
-        <v>4.485572343333333</v>
+        <v>4.454465658333334</v>
       </c>
       <c r="Q56">
-        <v>6.725572343333333</v>
+        <v>6.694465658333335</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.338798384304078</v>
+        <v>0.3448205974985761</v>
       </c>
       <c r="T56">
-        <v>1.791941644581506</v>
+        <v>1.828772750805524</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.670363444583466</v>
+        <v>3.603629563772858</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1838270188743592</v>
+        <v>0.1836700809688425</v>
       </c>
       <c r="C57">
-        <v>39.85338142785192</v>
+        <v>39.33715355536418</v>
       </c>
       <c r="D57">
-        <v>70.95838142785192</v>
+        <v>71.03915355536418</v>
       </c>
       <c r="E57">
-        <v>9.535</v>
+        <v>10.132</v>
       </c>
       <c r="F57">
-        <v>32.835</v>
+        <v>33.432</v>
       </c>
       <c r="G57">
         <v>1.73</v>
@@ -5961,28 +5961,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M57">
-        <v>2.0127855</v>
+        <v>2.0493816</v>
       </c>
       <c r="N57">
-        <v>5.240547833333334</v>
+        <v>5.203951733333334</v>
       </c>
       <c r="O57">
-        <v>0.7860821750000001</v>
+        <v>0.78059276</v>
       </c>
       <c r="P57">
-        <v>4.454465658333334</v>
+        <v>4.423358973333333</v>
       </c>
       <c r="Q57">
-        <v>6.694465658333335</v>
+        <v>6.663358973333334</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3448205974985761</v>
+        <v>0.3511165476564604</v>
       </c>
       <c r="T57">
-        <v>1.828772750805524</v>
+        <v>1.867277998221544</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.603629563772858</v>
+        <v>3.539279035848342</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1836700809688425</v>
+        <v>0.1848697430633259</v>
       </c>
       <c r="C58">
-        <v>39.33715355536418</v>
+        <v>38.12734606850669</v>
       </c>
       <c r="D58">
-        <v>71.03915355536418</v>
+        <v>70.42634606850669</v>
       </c>
       <c r="E58">
-        <v>10.132</v>
+        <v>10.729</v>
       </c>
       <c r="F58">
-        <v>33.432</v>
+        <v>34.029</v>
       </c>
       <c r="G58">
         <v>1.73</v>
@@ -6043,45 +6043,45 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M58">
-        <v>2.0493816</v>
+        <v>2.1812589</v>
       </c>
       <c r="N58">
-        <v>5.203951733333334</v>
+        <v>5.072074433333333</v>
       </c>
       <c r="O58">
-        <v>0.78059276</v>
+        <v>0.760811165</v>
       </c>
       <c r="P58">
-        <v>4.423358973333333</v>
+        <v>4.311263268333334</v>
       </c>
       <c r="Q58">
-        <v>6.663358973333334</v>
+        <v>6.551263268333334</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3511165476564604</v>
+        <v>0.3577053327054091</v>
       </c>
       <c r="T58">
-        <v>1.867277998221544</v>
+        <v>1.907574187377843</v>
       </c>
       <c r="U58">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V58">
         <v>0.15</v>
       </c>
       <c r="W58">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>3.539279035848342</v>
+        <v>3.325296842723866</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1848697430633259</v>
+        <v>0.1847366051578092</v>
       </c>
       <c r="C59">
-        <v>38.12734606850669</v>
+        <v>37.59783307956548</v>
       </c>
       <c r="D59">
-        <v>70.42634606850669</v>
+        <v>70.49383307956548</v>
       </c>
       <c r="E59">
-        <v>10.729</v>
+        <v>11.326</v>
       </c>
       <c r="F59">
-        <v>34.029</v>
+        <v>34.626</v>
       </c>
       <c r="G59">
         <v>1.73</v>
@@ -6125,28 +6125,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M59">
-        <v>2.1812589</v>
+        <v>2.2195266</v>
       </c>
       <c r="N59">
-        <v>5.072074433333333</v>
+        <v>5.033806733333334</v>
       </c>
       <c r="O59">
-        <v>0.760811165</v>
+        <v>0.7550710100000001</v>
       </c>
       <c r="P59">
-        <v>4.311263268333334</v>
+        <v>4.278735723333334</v>
       </c>
       <c r="Q59">
-        <v>6.551263268333334</v>
+        <v>6.518735723333334</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3577053327054091</v>
+        <v>0.3646078694233553</v>
       </c>
       <c r="T59">
-        <v>1.907574187377843</v>
+        <v>1.949789242684442</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.325296842723866</v>
+        <v>3.267964138538971</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1847366051578092</v>
+        <v>0.1846034672522925</v>
       </c>
       <c r="C60">
-        <v>37.59783307956547</v>
+        <v>37.06844955539167</v>
       </c>
       <c r="D60">
-        <v>70.49383307956546</v>
+        <v>70.56144955539166</v>
       </c>
       <c r="E60">
-        <v>11.326</v>
+        <v>11.923</v>
       </c>
       <c r="F60">
-        <v>34.626</v>
+        <v>35.223</v>
       </c>
       <c r="G60">
         <v>1.73</v>
@@ -6207,28 +6207,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M60">
-        <v>2.2195266</v>
+        <v>2.2577943</v>
       </c>
       <c r="N60">
-        <v>5.033806733333334</v>
+        <v>4.995539033333333</v>
       </c>
       <c r="O60">
-        <v>0.7550710100000001</v>
+        <v>0.749330855</v>
       </c>
       <c r="P60">
-        <v>4.278735723333334</v>
+        <v>4.246208178333333</v>
       </c>
       <c r="Q60">
-        <v>6.518735723333334</v>
+        <v>6.486208178333333</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3646078694233553</v>
+        <v>0.371847115249494</v>
       </c>
       <c r="T60">
-        <v>1.949789242684441</v>
+        <v>1.994063568981606</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.267964138538972</v>
+        <v>3.212574915851871</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1846034672522925</v>
+        <v>0.1844703293467759</v>
       </c>
       <c r="C61">
-        <v>37.06844955539167</v>
+        <v>36.53919586888409</v>
       </c>
       <c r="D61">
-        <v>70.56144955539166</v>
+        <v>70.62919586888408</v>
       </c>
       <c r="E61">
-        <v>11.923</v>
+        <v>12.52</v>
       </c>
       <c r="F61">
-        <v>35.223</v>
+        <v>35.82</v>
       </c>
       <c r="G61">
         <v>1.73</v>
@@ -6289,28 +6289,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M61">
-        <v>2.2577943</v>
+        <v>2.296062</v>
       </c>
       <c r="N61">
-        <v>4.995539033333333</v>
+        <v>4.957271333333334</v>
       </c>
       <c r="O61">
-        <v>0.749330855</v>
+        <v>0.7435907</v>
       </c>
       <c r="P61">
-        <v>4.246208178333333</v>
+        <v>4.213680633333333</v>
       </c>
       <c r="Q61">
-        <v>6.486208178333333</v>
+        <v>6.453680633333334</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.371847115249494</v>
+        <v>0.3794483233669397</v>
       </c>
       <c r="T61">
-        <v>1.994063568981606</v>
+        <v>2.040551611593629</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.212574915851871</v>
+        <v>3.159032000587673</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1844703293467759</v>
+        <v>0.1843371914412592</v>
       </c>
       <c r="C62">
-        <v>36.53919586888409</v>
+        <v>36.01007239437506</v>
       </c>
       <c r="D62">
-        <v>70.62919586888408</v>
+        <v>70.69707239437506</v>
       </c>
       <c r="E62">
-        <v>12.52</v>
+        <v>13.117</v>
       </c>
       <c r="F62">
-        <v>35.82</v>
+        <v>36.417</v>
       </c>
       <c r="G62">
         <v>1.73</v>
@@ -6371,28 +6371,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M62">
-        <v>2.296062</v>
+        <v>2.3343297</v>
       </c>
       <c r="N62">
-        <v>4.957271333333334</v>
+        <v>4.919003633333334</v>
       </c>
       <c r="O62">
-        <v>0.7435907</v>
+        <v>0.7378505450000001</v>
       </c>
       <c r="P62">
-        <v>4.213680633333333</v>
+        <v>4.181153088333334</v>
       </c>
       <c r="Q62">
-        <v>6.453680633333334</v>
+        <v>6.421153088333334</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3794483233669397</v>
+        <v>0.3874393370288698</v>
       </c>
       <c r="T62">
-        <v>2.040551611593629</v>
+        <v>2.089423656390885</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.159032000587673</v>
+        <v>3.107244590741974</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1843371914412592</v>
+        <v>0.1842040535357425</v>
       </c>
       <c r="C63">
-        <v>36.01007239437506</v>
+        <v>35.48107950763721</v>
       </c>
       <c r="D63">
-        <v>70.69707239437506</v>
+        <v>70.76507950763721</v>
       </c>
       <c r="E63">
-        <v>13.117</v>
+        <v>13.714</v>
       </c>
       <c r="F63">
-        <v>36.417</v>
+        <v>37.014</v>
       </c>
       <c r="G63">
         <v>1.73</v>
@@ -6453,28 +6453,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M63">
-        <v>2.3343297</v>
+        <v>2.372597400000001</v>
       </c>
       <c r="N63">
-        <v>4.919003633333334</v>
+        <v>4.880735933333334</v>
       </c>
       <c r="O63">
-        <v>0.7378505450000001</v>
+        <v>0.73211039</v>
       </c>
       <c r="P63">
-        <v>4.181153088333334</v>
+        <v>4.148625543333334</v>
       </c>
       <c r="Q63">
-        <v>6.421153088333334</v>
+        <v>6.388625543333334</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3874393370288698</v>
+        <v>0.3958509303572172</v>
       </c>
       <c r="T63">
-        <v>2.089423656390885</v>
+        <v>2.140867914072206</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.107244590741974</v>
+        <v>3.057127742504199</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1842040535357425</v>
+        <v>0.1840709156302259</v>
       </c>
       <c r="C64">
-        <v>35.48107950763721</v>
+        <v>34.95221758589051</v>
       </c>
       <c r="D64">
-        <v>70.76507950763721</v>
+        <v>70.83321758589051</v>
       </c>
       <c r="E64">
-        <v>13.714</v>
+        <v>14.311</v>
       </c>
       <c r="F64">
-        <v>37.014</v>
+        <v>37.611</v>
       </c>
       <c r="G64">
         <v>1.73</v>
@@ -6535,28 +6535,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M64">
-        <v>2.372597400000001</v>
+        <v>2.410865100000001</v>
       </c>
       <c r="N64">
-        <v>4.880735933333334</v>
+        <v>4.842468233333333</v>
       </c>
       <c r="O64">
-        <v>0.73211039</v>
+        <v>0.726370235</v>
       </c>
       <c r="P64">
-        <v>4.148625543333334</v>
+        <v>4.116097998333333</v>
       </c>
       <c r="Q64">
-        <v>6.388625543333334</v>
+        <v>6.356097998333333</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3958509303572172</v>
+        <v>0.4047172044060159</v>
       </c>
       <c r="T64">
-        <v>2.140867914072206</v>
+        <v>2.195092942439004</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.057127742504199</v>
+        <v>3.008601905321593</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1840709156302259</v>
+        <v>0.1881809777247092</v>
       </c>
       <c r="C65">
-        <v>34.95221758589051</v>
+        <v>32.31049976415346</v>
       </c>
       <c r="D65">
-        <v>70.83321758589051</v>
+        <v>68.78849976415346</v>
       </c>
       <c r="E65">
-        <v>14.311</v>
+        <v>14.908</v>
       </c>
       <c r="F65">
-        <v>37.611</v>
+        <v>38.20800000000001</v>
       </c>
       <c r="G65">
         <v>1.73</v>
@@ -6617,45 +6617,45 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M65">
-        <v>2.410865100000001</v>
+        <v>2.747155200000001</v>
       </c>
       <c r="N65">
-        <v>4.842468233333333</v>
+        <v>4.506178133333333</v>
       </c>
       <c r="O65">
-        <v>0.726370235</v>
+        <v>0.67592672</v>
       </c>
       <c r="P65">
-        <v>4.116097998333333</v>
+        <v>3.830251413333333</v>
       </c>
       <c r="Q65">
-        <v>6.356097998333333</v>
+        <v>6.070251413333333</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.4047172044060159</v>
+        <v>0.4140760492353034</v>
       </c>
       <c r="T65">
-        <v>2.195092942439004</v>
+        <v>2.252330472381735</v>
       </c>
       <c r="U65">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V65">
         <v>0.15</v>
       </c>
       <c r="W65">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>3.008601905321593</v>
+        <v>2.640307083244999</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1881809777247092</v>
+        <v>0.1881141398191926</v>
       </c>
       <c r="C66">
-        <v>32.31049976415346</v>
+        <v>31.7458063167821</v>
       </c>
       <c r="D66">
-        <v>68.78849976415346</v>
+        <v>68.8208063167821</v>
       </c>
       <c r="E66">
-        <v>14.908</v>
+        <v>15.505</v>
       </c>
       <c r="F66">
-        <v>38.20800000000001</v>
+        <v>38.805</v>
       </c>
       <c r="G66">
         <v>1.73</v>
@@ -6699,28 +6699,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M66">
-        <v>2.747155200000001</v>
+        <v>2.7900795</v>
       </c>
       <c r="N66">
-        <v>4.506178133333333</v>
+        <v>4.463253833333334</v>
       </c>
       <c r="O66">
-        <v>0.67592672</v>
+        <v>0.6694880750000001</v>
       </c>
       <c r="P66">
-        <v>3.830251413333333</v>
+        <v>3.793765758333334</v>
       </c>
       <c r="Q66">
-        <v>6.070251413333333</v>
+        <v>6.033765758333334</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.4140760492353034</v>
+        <v>0.4239696851976931</v>
       </c>
       <c r="T66">
-        <v>2.252330472381735</v>
+        <v>2.312838718321194</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.640307083244999</v>
+        <v>2.599686974272</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1881141398191926</v>
+        <v>0.1880473019136759</v>
       </c>
       <c r="C67">
-        <v>31.7458063167821</v>
+        <v>31.18114322924581</v>
       </c>
       <c r="D67">
-        <v>68.8208063167821</v>
+        <v>68.8531432292458</v>
       </c>
       <c r="E67">
-        <v>15.505</v>
+        <v>16.102</v>
       </c>
       <c r="F67">
-        <v>38.805</v>
+        <v>39.402</v>
       </c>
       <c r="G67">
         <v>1.73</v>
@@ -6781,28 +6781,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M67">
-        <v>2.7900795</v>
+        <v>2.8330038</v>
       </c>
       <c r="N67">
-        <v>4.463253833333334</v>
+        <v>4.420329533333334</v>
       </c>
       <c r="O67">
-        <v>0.6694880750000001</v>
+        <v>0.6630494300000001</v>
       </c>
       <c r="P67">
-        <v>3.793765758333334</v>
+        <v>3.757280103333334</v>
       </c>
       <c r="Q67">
-        <v>6.033765758333334</v>
+        <v>5.997280103333334</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4239696851976931</v>
+        <v>0.4344452997461057</v>
       </c>
       <c r="T67">
-        <v>2.312838718321194</v>
+        <v>2.376906272845327</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.599686974272</v>
+        <v>2.560297777692121</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1880473019136759</v>
+        <v>0.1879804640081592</v>
       </c>
       <c r="C68">
-        <v>31.18114322924581</v>
+        <v>30.61651054436033</v>
       </c>
       <c r="D68">
-        <v>68.8531432292458</v>
+        <v>68.88551054436033</v>
       </c>
       <c r="E68">
-        <v>16.102</v>
+        <v>16.699</v>
       </c>
       <c r="F68">
-        <v>39.402</v>
+        <v>39.999</v>
       </c>
       <c r="G68">
         <v>1.73</v>
@@ -6863,28 +6863,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M68">
-        <v>2.8330038</v>
+        <v>2.8759281</v>
       </c>
       <c r="N68">
-        <v>4.420329533333334</v>
+        <v>4.377405233333334</v>
       </c>
       <c r="O68">
-        <v>0.6630494300000001</v>
+        <v>0.656610785</v>
       </c>
       <c r="P68">
-        <v>3.757280103333334</v>
+        <v>3.720794448333334</v>
       </c>
       <c r="Q68">
-        <v>5.997280103333334</v>
+        <v>5.960794448333334</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4344452997461057</v>
+        <v>0.445555800024725</v>
       </c>
       <c r="T68">
-        <v>2.376906272845327</v>
+        <v>2.444856709461832</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.560297777692121</v>
+        <v>2.522084378025074</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1879804640081592</v>
+        <v>0.1901678261026426</v>
       </c>
       <c r="C69">
-        <v>30.61651054436033</v>
+        <v>28.97580462530925</v>
       </c>
       <c r="D69">
-        <v>68.88551054436033</v>
+        <v>67.84180462530925</v>
       </c>
       <c r="E69">
-        <v>16.699</v>
+        <v>17.296</v>
       </c>
       <c r="F69">
-        <v>39.999</v>
+        <v>40.596</v>
       </c>
       <c r="G69">
         <v>1.73</v>
@@ -6945,45 +6945,45 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M69">
-        <v>2.8759281</v>
+        <v>3.077176800000001</v>
       </c>
       <c r="N69">
-        <v>4.377405233333334</v>
+        <v>4.176156533333334</v>
       </c>
       <c r="O69">
-        <v>0.656610785</v>
+        <v>0.62642348</v>
       </c>
       <c r="P69">
-        <v>3.720794448333334</v>
+        <v>3.549733053333334</v>
       </c>
       <c r="Q69">
-        <v>5.960794448333334</v>
+        <v>5.789733053333334</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.445555800024725</v>
+        <v>0.4573607065707581</v>
       </c>
       <c r="T69">
-        <v>2.444856709461832</v>
+        <v>2.517054048366868</v>
       </c>
       <c r="U69">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V69">
         <v>0.15</v>
       </c>
       <c r="W69">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.522084378025074</v>
+        <v>2.35713896365439</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1901678261026426</v>
+        <v>0.1901341381971259</v>
       </c>
       <c r="C70">
-        <v>28.97580462530925</v>
+        <v>28.39463905182014</v>
       </c>
       <c r="D70">
-        <v>67.84180462530925</v>
+        <v>67.85763905182014</v>
       </c>
       <c r="E70">
-        <v>17.296</v>
+        <v>17.893</v>
       </c>
       <c r="F70">
-        <v>40.596</v>
+        <v>41.193</v>
       </c>
       <c r="G70">
         <v>1.73</v>
@@ -7027,28 +7027,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M70">
-        <v>3.077176800000001</v>
+        <v>3.122429400000001</v>
       </c>
       <c r="N70">
-        <v>4.176156533333334</v>
+        <v>4.130903933333333</v>
       </c>
       <c r="O70">
-        <v>0.62642348</v>
+        <v>0.61963559</v>
       </c>
       <c r="P70">
-        <v>3.549733053333334</v>
+        <v>3.511268343333333</v>
       </c>
       <c r="Q70">
-        <v>5.789733053333334</v>
+        <v>5.751268343333333</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4573607065707581</v>
+        <v>0.4699272199907289</v>
       </c>
       <c r="T70">
-        <v>2.517054048366868</v>
+        <v>2.593909280104487</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.35713896365439</v>
+        <v>2.322977529398529</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1901341381971259</v>
+        <v>0.1901004502916092</v>
       </c>
       <c r="C71">
-        <v>28.39463905182014</v>
+        <v>27.81348087163667</v>
       </c>
       <c r="D71">
-        <v>67.85763905182014</v>
+        <v>67.87348087163667</v>
       </c>
       <c r="E71">
-        <v>17.893</v>
+        <v>18.49000000000001</v>
       </c>
       <c r="F71">
-        <v>41.193</v>
+        <v>41.79000000000001</v>
       </c>
       <c r="G71">
         <v>1.73</v>
@@ -7109,28 +7109,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M71">
-        <v>3.122429400000001</v>
+        <v>3.167682000000001</v>
       </c>
       <c r="N71">
-        <v>4.130903933333333</v>
+        <v>4.085651333333333</v>
       </c>
       <c r="O71">
-        <v>0.61963559</v>
+        <v>0.6128476999999999</v>
       </c>
       <c r="P71">
-        <v>3.511268343333333</v>
+        <v>3.472803633333333</v>
       </c>
       <c r="Q71">
-        <v>5.751268343333333</v>
+        <v>5.712803633333333</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4699272199907289</v>
+        <v>0.4833315009720309</v>
       </c>
       <c r="T71">
-        <v>2.593909280104487</v>
+        <v>2.675888193957947</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.322977529398529</v>
+        <v>2.289792136121408</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1901004502916092</v>
+        <v>0.1900667623860926</v>
       </c>
       <c r="C72">
-        <v>27.81348087163667</v>
+        <v>27.23233008993805</v>
       </c>
       <c r="D72">
-        <v>67.87348087163667</v>
+        <v>67.88933008993806</v>
       </c>
       <c r="E72">
-        <v>18.49000000000001</v>
+        <v>19.08700000000001</v>
       </c>
       <c r="F72">
-        <v>41.79000000000001</v>
+        <v>42.38700000000001</v>
       </c>
       <c r="G72">
         <v>1.73</v>
@@ -7191,28 +7191,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M72">
-        <v>3.167682000000001</v>
+        <v>3.212934600000001</v>
       </c>
       <c r="N72">
-        <v>4.085651333333333</v>
+        <v>4.040398733333333</v>
       </c>
       <c r="O72">
-        <v>0.6128476999999999</v>
+        <v>0.60605981</v>
       </c>
       <c r="P72">
-        <v>3.472803633333333</v>
+        <v>3.434338923333333</v>
       </c>
       <c r="Q72">
-        <v>5.712803633333333</v>
+        <v>5.674338923333334</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4833315009720309</v>
+        <v>0.4976602151244574</v>
       </c>
       <c r="T72">
-        <v>2.675888193957947</v>
+        <v>2.763520826008198</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.289792136121408</v>
+        <v>2.257541542654909</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1900667623860926</v>
+        <v>0.1900330744805759</v>
       </c>
       <c r="C73">
-        <v>27.23233008993806</v>
+        <v>26.6511867119084</v>
       </c>
       <c r="D73">
-        <v>67.88933008993806</v>
+        <v>67.9051867119084</v>
       </c>
       <c r="E73">
-        <v>19.087</v>
+        <v>19.684</v>
       </c>
       <c r="F73">
-        <v>42.387</v>
+        <v>42.984</v>
       </c>
       <c r="G73">
         <v>1.73</v>
@@ -7273,28 +7273,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M73">
-        <v>3.2129346</v>
+        <v>3.258187200000001</v>
       </c>
       <c r="N73">
-        <v>4.040398733333333</v>
+        <v>3.995146133333333</v>
       </c>
       <c r="O73">
-        <v>0.60605981</v>
+        <v>0.59927192</v>
       </c>
       <c r="P73">
-        <v>3.434338923333333</v>
+        <v>3.395874213333333</v>
       </c>
       <c r="Q73">
-        <v>5.674338923333334</v>
+        <v>5.635874213333333</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4976602151244572</v>
+        <v>0.5130124088591997</v>
       </c>
       <c r="T73">
-        <v>2.763520826008197</v>
+        <v>2.857412931776323</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.257541542654909</v>
+        <v>2.226186799006924</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1900330744805759</v>
+        <v>0.1899993865750592</v>
       </c>
       <c r="C74">
-        <v>26.6511867119084</v>
+        <v>26.07005074273668</v>
       </c>
       <c r="D74">
-        <v>67.9051867119084</v>
+        <v>67.92105074273668</v>
       </c>
       <c r="E74">
-        <v>19.684</v>
+        <v>20.281</v>
       </c>
       <c r="F74">
-        <v>42.984</v>
+        <v>43.581</v>
       </c>
       <c r="G74">
         <v>1.73</v>
@@ -7355,28 +7355,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M74">
-        <v>3.258187200000001</v>
+        <v>3.3034398</v>
       </c>
       <c r="N74">
-        <v>3.995146133333333</v>
+        <v>3.949893533333333</v>
       </c>
       <c r="O74">
-        <v>0.59927192</v>
+        <v>0.5924840299999999</v>
       </c>
       <c r="P74">
-        <v>3.395874213333333</v>
+        <v>3.357409503333333</v>
       </c>
       <c r="Q74">
-        <v>5.635874213333333</v>
+        <v>5.597409503333333</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.5130124088591997</v>
+        <v>0.529501802129849</v>
       </c>
       <c r="T74">
-        <v>2.857412931776323</v>
+        <v>2.958260008342087</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.226186799006924</v>
+        <v>2.195691089431487</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1899993865750592</v>
+        <v>0.1899656986695426</v>
       </c>
       <c r="C75">
-        <v>26.07005074273668</v>
+        <v>25.4889221876166</v>
       </c>
       <c r="D75">
-        <v>67.92105074273668</v>
+        <v>67.9369221876166</v>
       </c>
       <c r="E75">
-        <v>20.281</v>
+        <v>20.878</v>
       </c>
       <c r="F75">
-        <v>43.581</v>
+        <v>44.178</v>
       </c>
       <c r="G75">
         <v>1.73</v>
@@ -7437,28 +7437,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M75">
-        <v>3.3034398</v>
+        <v>3.3486924</v>
       </c>
       <c r="N75">
-        <v>3.949893533333333</v>
+        <v>3.904640933333333</v>
       </c>
       <c r="O75">
-        <v>0.5924840299999999</v>
+        <v>0.58569614</v>
       </c>
       <c r="P75">
-        <v>3.357409503333333</v>
+        <v>3.318944793333333</v>
       </c>
       <c r="Q75">
-        <v>5.597409503333333</v>
+        <v>5.558944793333334</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.529501802129849</v>
+        <v>0.5472596102674715</v>
       </c>
       <c r="T75">
-        <v>2.958260008342087</v>
+        <v>3.066864552335988</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.195691089431487</v>
+        <v>2.166019588222953</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1899656986695426</v>
+        <v>0.1899320107640259</v>
       </c>
       <c r="C76">
-        <v>25.4889221876166</v>
+        <v>24.9078010517469</v>
       </c>
       <c r="D76">
-        <v>67.9369221876166</v>
+        <v>67.9528010517469</v>
       </c>
       <c r="E76">
-        <v>20.878</v>
+        <v>21.475</v>
       </c>
       <c r="F76">
-        <v>44.178</v>
+        <v>44.77500000000001</v>
       </c>
       <c r="G76">
         <v>1.73</v>
@@ -7519,28 +7519,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M76">
-        <v>3.3486924</v>
+        <v>3.393945000000001</v>
       </c>
       <c r="N76">
-        <v>3.904640933333333</v>
+        <v>3.859388333333333</v>
       </c>
       <c r="O76">
-        <v>0.58569614</v>
+        <v>0.5789082499999999</v>
       </c>
       <c r="P76">
-        <v>3.318944793333333</v>
+        <v>3.280480083333333</v>
       </c>
       <c r="Q76">
-        <v>5.558944793333334</v>
+        <v>5.520480083333333</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.5472596102674715</v>
+        <v>0.5664380430561037</v>
       </c>
       <c r="T76">
-        <v>3.066864552335988</v>
+        <v>3.1841574598494</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.166019588222953</v>
+        <v>2.137139327046647</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1899320107640259</v>
+        <v>0.1898983228585093</v>
       </c>
       <c r="C77">
-        <v>24.9078010517469</v>
+        <v>24.32668734033108</v>
       </c>
       <c r="D77">
-        <v>67.9528010517469</v>
+        <v>67.96868734033107</v>
       </c>
       <c r="E77">
-        <v>21.475</v>
+        <v>22.072</v>
       </c>
       <c r="F77">
-        <v>44.77500000000001</v>
+        <v>45.372</v>
       </c>
       <c r="G77">
         <v>1.73</v>
@@ -7601,28 +7601,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M77">
-        <v>3.393945000000001</v>
+        <v>3.4391976</v>
       </c>
       <c r="N77">
-        <v>3.859388333333333</v>
+        <v>3.814135733333333</v>
       </c>
       <c r="O77">
-        <v>0.5789082499999999</v>
+        <v>0.57212036</v>
       </c>
       <c r="P77">
-        <v>3.280480083333333</v>
+        <v>3.242015373333333</v>
       </c>
       <c r="Q77">
-        <v>5.520480083333333</v>
+        <v>5.482015373333334</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5664380430561037</v>
+        <v>0.587214678577122</v>
       </c>
       <c r="T77">
-        <v>3.1841574598494</v>
+        <v>3.311224776322264</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.137139327046647</v>
+        <v>2.109019072743402</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1898983228585093</v>
+        <v>0.1898646349529926</v>
       </c>
       <c r="C78">
-        <v>24.32668734033108</v>
+        <v>23.74558105857748</v>
       </c>
       <c r="D78">
-        <v>67.96868734033107</v>
+        <v>67.98458105857748</v>
       </c>
       <c r="E78">
-        <v>22.072</v>
+        <v>22.669</v>
       </c>
       <c r="F78">
-        <v>45.372</v>
+        <v>45.969</v>
       </c>
       <c r="G78">
         <v>1.73</v>
@@ -7683,28 +7683,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M78">
-        <v>3.4391976</v>
+        <v>3.4844502</v>
       </c>
       <c r="N78">
-        <v>3.814135733333333</v>
+        <v>3.768883133333333</v>
       </c>
       <c r="O78">
-        <v>0.57212036</v>
+        <v>0.56533247</v>
       </c>
       <c r="P78">
-        <v>3.242015373333333</v>
+        <v>3.203550663333333</v>
       </c>
       <c r="Q78">
-        <v>5.482015373333334</v>
+        <v>5.443550663333333</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.587214678577122</v>
+        <v>0.6097979780564895</v>
       </c>
       <c r="T78">
-        <v>3.311224776322264</v>
+        <v>3.449341424662332</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.109019072743402</v>
+        <v>2.081629214655825</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1898646349529926</v>
+        <v>0.1898309470474759</v>
       </c>
       <c r="C79">
-        <v>23.74558105857748</v>
+        <v>23.16448221169935</v>
       </c>
       <c r="D79">
-        <v>67.98458105857748</v>
+        <v>68.00048221169935</v>
       </c>
       <c r="E79">
-        <v>22.669</v>
+        <v>23.266</v>
       </c>
       <c r="F79">
-        <v>45.969</v>
+        <v>46.566</v>
       </c>
       <c r="G79">
         <v>1.73</v>
@@ -7765,28 +7765,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M79">
-        <v>3.4844502</v>
+        <v>3.5297028</v>
       </c>
       <c r="N79">
-        <v>3.768883133333333</v>
+        <v>3.723630533333333</v>
       </c>
       <c r="O79">
-        <v>0.56533247</v>
+        <v>0.55854458</v>
       </c>
       <c r="P79">
-        <v>3.203550663333333</v>
+        <v>3.165085953333334</v>
       </c>
       <c r="Q79">
-        <v>5.443550663333333</v>
+        <v>5.405085953333334</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.6097979780564895</v>
+        <v>0.6344343047612543</v>
       </c>
       <c r="T79">
-        <v>3.449341424662332</v>
+        <v>3.600014131942408</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.081629214655825</v>
+        <v>2.054941660621776</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1898309470474759</v>
+        <v>0.1897972591419593</v>
       </c>
       <c r="C80">
-        <v>23.16448221169935</v>
+        <v>22.58339080491483</v>
       </c>
       <c r="D80">
-        <v>68.00048221169935</v>
+        <v>68.01639080491483</v>
       </c>
       <c r="E80">
-        <v>23.266</v>
+        <v>23.863</v>
       </c>
       <c r="F80">
-        <v>46.566</v>
+        <v>47.163</v>
       </c>
       <c r="G80">
         <v>1.73</v>
@@ -7847,28 +7847,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M80">
-        <v>3.5297028</v>
+        <v>3.574955400000001</v>
       </c>
       <c r="N80">
-        <v>3.723630533333333</v>
+        <v>3.678377933333333</v>
       </c>
       <c r="O80">
-        <v>0.55854458</v>
+        <v>0.5517566899999999</v>
       </c>
       <c r="P80">
-        <v>3.165085953333334</v>
+        <v>3.126621243333333</v>
       </c>
       <c r="Q80">
-        <v>5.405085953333334</v>
+        <v>5.366621243333333</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.6344343047612543</v>
+        <v>0.6614169482950442</v>
       </c>
       <c r="T80">
-        <v>3.600014131942408</v>
+        <v>3.765036620868205</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.054941660621776</v>
+        <v>2.02892974086707</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1897972591419593</v>
+        <v>0.1897635712364426</v>
       </c>
       <c r="C81">
-        <v>22.58339080491483</v>
+        <v>22.00230684344697</v>
       </c>
       <c r="D81">
-        <v>68.01639080491483</v>
+        <v>68.03230684344697</v>
       </c>
       <c r="E81">
-        <v>23.863</v>
+        <v>24.46</v>
       </c>
       <c r="F81">
-        <v>47.163</v>
+        <v>47.76000000000001</v>
       </c>
       <c r="G81">
         <v>1.73</v>
@@ -7929,28 +7929,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M81">
-        <v>3.574955400000001</v>
+        <v>3.620208000000001</v>
       </c>
       <c r="N81">
-        <v>3.678377933333333</v>
+        <v>3.633125333333333</v>
       </c>
       <c r="O81">
-        <v>0.5517566899999999</v>
+        <v>0.5449687999999999</v>
       </c>
       <c r="P81">
-        <v>3.126621243333333</v>
+        <v>3.088156533333333</v>
       </c>
       <c r="Q81">
-        <v>5.366621243333333</v>
+        <v>5.328156533333333</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.6614169482950442</v>
+        <v>0.6910978561822131</v>
       </c>
       <c r="T81">
-        <v>3.765036620868205</v>
+        <v>3.946561358686581</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.02892974086707</v>
+        <v>2.003568119106232</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1897635712364426</v>
+        <v>0.199506583330926</v>
       </c>
       <c r="C82">
-        <v>22.00230684344697</v>
+        <v>17.09293730125089</v>
       </c>
       <c r="D82">
-        <v>68.03230684344697</v>
+        <v>63.71993730125089</v>
       </c>
       <c r="E82">
-        <v>24.46</v>
+        <v>25.05700000000001</v>
       </c>
       <c r="F82">
-        <v>47.76000000000001</v>
+        <v>48.35700000000001</v>
       </c>
       <c r="G82">
         <v>1.73</v>
@@ -8011,45 +8011,45 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M82">
-        <v>3.620208000000001</v>
+        <v>4.352130000000001</v>
       </c>
       <c r="N82">
-        <v>3.633125333333333</v>
+        <v>2.901203333333333</v>
       </c>
       <c r="O82">
-        <v>0.5449687999999999</v>
+        <v>0.4351805</v>
       </c>
       <c r="P82">
-        <v>3.088156533333333</v>
+        <v>2.466022833333333</v>
       </c>
       <c r="Q82">
-        <v>5.328156533333333</v>
+        <v>4.706022833333334</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6910978561822131</v>
+        <v>0.7239030701627683</v>
       </c>
       <c r="T82">
-        <v>3.946561358686581</v>
+        <v>4.147193963643734</v>
       </c>
       <c r="U82">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V82">
         <v>0.15</v>
       </c>
       <c r="W82">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.003568119106232</v>
+        <v>1.666616882614566</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.199506583330926</v>
+        <v>0.1995935954254093</v>
       </c>
       <c r="C83">
-        <v>17.09293730125089</v>
+        <v>16.45988635134239</v>
       </c>
       <c r="D83">
-        <v>63.71993730125089</v>
+        <v>63.6838863513424</v>
       </c>
       <c r="E83">
-        <v>25.05700000000001</v>
+        <v>25.65400000000001</v>
       </c>
       <c r="F83">
-        <v>48.35700000000001</v>
+        <v>48.95400000000001</v>
       </c>
       <c r="G83">
         <v>1.73</v>
@@ -8093,28 +8093,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M83">
-        <v>4.352130000000001</v>
+        <v>4.405860000000001</v>
       </c>
       <c r="N83">
-        <v>2.901203333333333</v>
+        <v>2.847473333333333</v>
       </c>
       <c r="O83">
-        <v>0.4351805</v>
+        <v>0.427121</v>
       </c>
       <c r="P83">
-        <v>2.466022833333333</v>
+        <v>2.420352333333333</v>
       </c>
       <c r="Q83">
-        <v>4.706022833333334</v>
+        <v>4.660352333333334</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.7239030701627683</v>
+        <v>0.7603533079189407</v>
       </c>
       <c r="T83">
-        <v>4.147193963643734</v>
+        <v>4.370119080262794</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.666616882614566</v>
+        <v>1.64629228648512</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1995935954254093</v>
+        <v>0.1996806075198926</v>
       </c>
       <c r="C84">
-        <v>16.45988635134239</v>
+        <v>15.82687617159603</v>
       </c>
       <c r="D84">
-        <v>63.6838863513424</v>
+        <v>63.64787617159605</v>
       </c>
       <c r="E84">
-        <v>25.65400000000001</v>
+        <v>26.25100000000001</v>
       </c>
       <c r="F84">
-        <v>48.95400000000001</v>
+        <v>49.55100000000001</v>
       </c>
       <c r="G84">
         <v>1.73</v>
@@ -8175,28 +8175,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M84">
-        <v>4.405860000000001</v>
+        <v>4.45959</v>
       </c>
       <c r="N84">
-        <v>2.847473333333333</v>
+        <v>2.793743333333333</v>
       </c>
       <c r="O84">
-        <v>0.427121</v>
+        <v>0.4190615</v>
       </c>
       <c r="P84">
-        <v>2.420352333333333</v>
+        <v>2.374681833333333</v>
       </c>
       <c r="Q84">
-        <v>4.660352333333334</v>
+        <v>4.614681833333334</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.7603533079189407</v>
+        <v>0.8010918089405451</v>
       </c>
       <c r="T84">
-        <v>4.370119080262794</v>
+        <v>4.619270681189977</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.64629228648512</v>
+        <v>1.626457439659998</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1996806075198926</v>
+        <v>0.199767619614376</v>
       </c>
       <c r="C85">
-        <v>15.82687617159603</v>
+        <v>15.19390669289021</v>
       </c>
       <c r="D85">
-        <v>63.64787617159605</v>
+        <v>63.61190669289022</v>
       </c>
       <c r="E85">
-        <v>26.25100000000001</v>
+        <v>26.84800000000001</v>
       </c>
       <c r="F85">
-        <v>49.55100000000001</v>
+        <v>50.14800000000001</v>
       </c>
       <c r="G85">
         <v>1.73</v>
@@ -8257,28 +8257,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M85">
-        <v>4.45959</v>
+        <v>4.513320000000001</v>
       </c>
       <c r="N85">
-        <v>2.793743333333333</v>
+        <v>2.740013333333333</v>
       </c>
       <c r="O85">
-        <v>0.4190615</v>
+        <v>0.4110019999999999</v>
       </c>
       <c r="P85">
-        <v>2.374681833333333</v>
+        <v>2.329011333333333</v>
       </c>
       <c r="Q85">
-        <v>4.614681833333334</v>
+        <v>4.569011333333333</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.8010918089405451</v>
+        <v>0.8469226225898502</v>
       </c>
       <c r="T85">
-        <v>4.619270681189977</v>
+        <v>4.899566232233059</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.626457439659998</v>
+        <v>1.607094851092617</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.199767619614376</v>
+        <v>0.1998546317088593</v>
       </c>
       <c r="C86">
-        <v>15.1939066928902</v>
+        <v>14.56097784625943</v>
       </c>
       <c r="D86">
-        <v>63.6119066928902</v>
+        <v>63.57597784625944</v>
       </c>
       <c r="E86">
-        <v>26.848</v>
+        <v>27.445</v>
       </c>
       <c r="F86">
-        <v>50.148</v>
+        <v>50.745</v>
       </c>
       <c r="G86">
         <v>1.73</v>
@@ -8339,28 +8339,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M86">
-        <v>4.51332</v>
+        <v>4.56705</v>
       </c>
       <c r="N86">
-        <v>2.740013333333334</v>
+        <v>2.686283333333334</v>
       </c>
       <c r="O86">
-        <v>0.411002</v>
+        <v>0.4029425</v>
       </c>
       <c r="P86">
-        <v>2.329011333333334</v>
+        <v>2.283340833333334</v>
       </c>
       <c r="Q86">
-        <v>4.569011333333334</v>
+        <v>4.523340833333334</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.8469226225898497</v>
+        <v>0.8988642113923954</v>
       </c>
       <c r="T86">
-        <v>4.899566232233056</v>
+        <v>5.217234523415215</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.607094851092618</v>
+        <v>1.588187852844469</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1998546317088593</v>
+        <v>0.1999416438033426</v>
       </c>
       <c r="C87">
-        <v>14.56097784625943</v>
+        <v>13.92808956289403</v>
       </c>
       <c r="D87">
-        <v>63.57597784625944</v>
+        <v>63.54008956289402</v>
       </c>
       <c r="E87">
-        <v>27.445</v>
+        <v>28.042</v>
       </c>
       <c r="F87">
-        <v>50.745</v>
+        <v>51.342</v>
       </c>
       <c r="G87">
         <v>1.73</v>
@@ -8421,28 +8421,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M87">
-        <v>4.56705</v>
+        <v>4.62078</v>
       </c>
       <c r="N87">
-        <v>2.686283333333334</v>
+        <v>2.632553333333334</v>
       </c>
       <c r="O87">
-        <v>0.4029425</v>
+        <v>0.3948830000000001</v>
       </c>
       <c r="P87">
-        <v>2.283340833333334</v>
+        <v>2.237670333333334</v>
       </c>
       <c r="Q87">
-        <v>4.523340833333334</v>
+        <v>4.477670333333334</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.8988642113923954</v>
+        <v>0.9582260271667329</v>
       </c>
       <c r="T87">
-        <v>5.217234523415215</v>
+        <v>5.580283999051966</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.588187852844469</v>
+        <v>1.569720552229999</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1999416438033426</v>
+        <v>0.200028655897826</v>
       </c>
       <c r="C88">
-        <v>13.92808956289403</v>
+        <v>13.29524177413943</v>
       </c>
       <c r="D88">
-        <v>63.54008956289402</v>
+        <v>63.50424177413944</v>
       </c>
       <c r="E88">
-        <v>28.042</v>
+        <v>28.639</v>
       </c>
       <c r="F88">
-        <v>51.342</v>
+        <v>51.939</v>
       </c>
       <c r="G88">
         <v>1.73</v>
@@ -8503,28 +8503,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M88">
-        <v>4.62078</v>
+        <v>4.67451</v>
       </c>
       <c r="N88">
-        <v>2.632553333333334</v>
+        <v>2.578823333333334</v>
       </c>
       <c r="O88">
-        <v>0.3948830000000001</v>
+        <v>0.3868235000000001</v>
       </c>
       <c r="P88">
-        <v>2.237670333333334</v>
+        <v>2.191999833333334</v>
       </c>
       <c r="Q88">
-        <v>4.477670333333334</v>
+        <v>4.431999833333334</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.9582260271667329</v>
+        <v>1.026720429983277</v>
       </c>
       <c r="T88">
-        <v>5.580283999051966</v>
+        <v>5.999187240171296</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.569720552229999</v>
+        <v>1.551677787261838</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.200028655897826</v>
+        <v>0.2001156679923093</v>
       </c>
       <c r="C89">
-        <v>13.29524177413943</v>
+        <v>12.66243441149614</v>
       </c>
       <c r="D89">
-        <v>63.50424177413944</v>
+        <v>63.46843441149613</v>
       </c>
       <c r="E89">
-        <v>28.639</v>
+        <v>29.236</v>
       </c>
       <c r="F89">
-        <v>51.939</v>
+        <v>52.536</v>
       </c>
       <c r="G89">
         <v>1.73</v>
@@ -8585,28 +8585,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M89">
-        <v>4.67451</v>
+        <v>4.72824</v>
       </c>
       <c r="N89">
-        <v>2.578823333333334</v>
+        <v>2.525093333333334</v>
       </c>
       <c r="O89">
-        <v>0.3868235000000001</v>
+        <v>0.3787640000000002</v>
       </c>
       <c r="P89">
-        <v>2.191999833333334</v>
+        <v>2.146329333333334</v>
       </c>
       <c r="Q89">
-        <v>4.431999833333334</v>
+        <v>4.386329333333334</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.026720429983277</v>
+        <v>1.106630566602578</v>
       </c>
       <c r="T89">
-        <v>5.999187240171296</v>
+        <v>6.487907688143848</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.551677787261838</v>
+        <v>1.534045085133863</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2001156679923093</v>
+        <v>0.2002026800867927</v>
       </c>
       <c r="C90">
-        <v>12.66243441149614</v>
+        <v>12.02966740661891</v>
       </c>
       <c r="D90">
-        <v>63.46843441149613</v>
+        <v>63.43266740661891</v>
       </c>
       <c r="E90">
-        <v>29.236</v>
+        <v>29.833</v>
       </c>
       <c r="F90">
-        <v>52.536</v>
+        <v>53.133</v>
       </c>
       <c r="G90">
         <v>1.73</v>
@@ -8667,28 +8667,28 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M90">
-        <v>4.72824</v>
+        <v>4.78197</v>
       </c>
       <c r="N90">
-        <v>2.525093333333334</v>
+        <v>2.471363333333334</v>
       </c>
       <c r="O90">
-        <v>0.3787640000000002</v>
+        <v>0.3707045</v>
       </c>
       <c r="P90">
-        <v>2.146329333333334</v>
+        <v>2.100658833333334</v>
       </c>
       <c r="Q90">
-        <v>4.386329333333334</v>
+        <v>4.340658833333334</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.106630566602578</v>
+        <v>1.201069818970842</v>
       </c>
       <c r="T90">
-        <v>6.487907688143848</v>
+        <v>7.065486399384137</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.534045085133863</v>
+        <v>1.516808623503145</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2002026800867927</v>
+        <v>0.2469272460721477</v>
       </c>
       <c r="C91">
-        <v>12.02966740661891</v>
+        <v>-3.303594893738257</v>
       </c>
       <c r="D91">
-        <v>63.43266740661891</v>
+        <v>48.69640510626175</v>
       </c>
       <c r="E91">
-        <v>29.833</v>
+        <v>30.43</v>
       </c>
       <c r="F91">
-        <v>53.133</v>
+        <v>53.73</v>
       </c>
       <c r="G91">
         <v>1.73</v>
@@ -8749,45 +8749,45 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M91">
-        <v>4.78197</v>
+        <v>7.887564000000001</v>
       </c>
       <c r="N91">
-        <v>2.471363333333334</v>
+        <v>-0.6342306666666673</v>
       </c>
       <c r="O91">
-        <v>0.3707045</v>
+        <v>-0.09513460000000008</v>
       </c>
       <c r="P91">
-        <v>2.100658833333334</v>
+        <v>-0.5390960666666672</v>
       </c>
       <c r="Q91">
-        <v>4.340658833333334</v>
+        <v>1.700903933333333</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.201069818970842</v>
+        <v>1.33031701683538</v>
       </c>
       <c r="T91">
-        <v>7.065486399384137</v>
+        <v>7.855946172222233</v>
       </c>
       <c r="U91">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.15</v>
+        <v>0.1379386588812465</v>
       </c>
       <c r="W91">
-        <v>0.0765</v>
+        <v>0.126550604876233</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y91">
-        <v>1.516808623503145</v>
+        <v>0.9195910592083097</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2469272460721477</v>
+        <v>0.2479372460721477</v>
       </c>
       <c r="C92">
-        <v>-3.303594893738257</v>
+        <v>-4.143911601138967</v>
       </c>
       <c r="D92">
-        <v>48.69640510626175</v>
+        <v>48.45308839886104</v>
       </c>
       <c r="E92">
-        <v>30.43</v>
+        <v>31.027</v>
       </c>
       <c r="F92">
-        <v>53.73</v>
+        <v>54.32700000000001</v>
       </c>
       <c r="G92">
         <v>1.73</v>
@@ -8831,37 +8831,37 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M92">
-        <v>7.887564000000001</v>
+        <v>7.975203600000001</v>
       </c>
       <c r="N92">
-        <v>-0.6342306666666673</v>
+        <v>-0.7218702666666674</v>
       </c>
       <c r="O92">
-        <v>-0.09513460000000008</v>
+        <v>-0.1082805400000001</v>
       </c>
       <c r="P92">
-        <v>-0.5390960666666672</v>
+        <v>-0.6135897266666673</v>
       </c>
       <c r="Q92">
-        <v>1.700903933333333</v>
+        <v>1.626410273333333</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.33031701683538</v>
+        <v>1.473041129817089</v>
       </c>
       <c r="T92">
-        <v>7.855946172222233</v>
+        <v>8.728829080246925</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1379386588812465</v>
+        <v>0.136422849442991</v>
       </c>
       <c r="W92">
-        <v>0.126550604876233</v>
+        <v>0.1267731257017689</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.9195910592083097</v>
+        <v>0.9094856629532734</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2479372460721477</v>
+        <v>0.2489472460721477</v>
       </c>
       <c r="C93">
-        <v>-4.143911601138967</v>
+        <v>-4.981808882441371</v>
       </c>
       <c r="D93">
-        <v>48.45308839886104</v>
+        <v>48.21219111755864</v>
       </c>
       <c r="E93">
-        <v>31.027</v>
+        <v>31.62400000000001</v>
       </c>
       <c r="F93">
-        <v>54.32700000000001</v>
+        <v>54.92400000000001</v>
       </c>
       <c r="G93">
         <v>1.73</v>
@@ -8913,37 +8913,37 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M93">
-        <v>7.975203600000001</v>
+        <v>8.062843200000001</v>
       </c>
       <c r="N93">
-        <v>-0.7218702666666674</v>
+        <v>-0.8095098666666676</v>
       </c>
       <c r="O93">
-        <v>-0.1082805400000001</v>
+        <v>-0.1214264800000001</v>
       </c>
       <c r="P93">
-        <v>-0.6135897266666673</v>
+        <v>-0.6880833866666675</v>
       </c>
       <c r="Q93">
-        <v>1.626410273333333</v>
+        <v>1.551916613333333</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.473041129817089</v>
+        <v>1.651446271044225</v>
       </c>
       <c r="T93">
-        <v>8.728829080246925</v>
+        <v>9.819932715277794</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.136422849442991</v>
+        <v>0.1349399923838281</v>
       </c>
       <c r="W93">
-        <v>0.1267731257017689</v>
+        <v>0.126990809118054</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.9094856629532734</v>
+        <v>0.8995999492255204</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2489472460721477</v>
+        <v>0.2499572460721477</v>
       </c>
       <c r="C94">
-        <v>-4.981808882441371</v>
+        <v>-5.817322645560637</v>
       </c>
       <c r="D94">
-        <v>48.21219111755864</v>
+        <v>47.97367735443937</v>
       </c>
       <c r="E94">
-        <v>31.62400000000001</v>
+        <v>32.221</v>
       </c>
       <c r="F94">
-        <v>54.92400000000001</v>
+        <v>55.52100000000001</v>
       </c>
       <c r="G94">
         <v>1.73</v>
@@ -8995,37 +8995,37 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M94">
-        <v>8.062843200000001</v>
+        <v>8.150482800000002</v>
       </c>
       <c r="N94">
-        <v>-0.8095098666666676</v>
+        <v>-0.8971494666666686</v>
       </c>
       <c r="O94">
-        <v>-0.1214264800000001</v>
+        <v>-0.1345724200000003</v>
       </c>
       <c r="P94">
-        <v>-0.6880833866666675</v>
+        <v>-0.7625770466666684</v>
       </c>
       <c r="Q94">
-        <v>1.551916613333333</v>
+        <v>1.477422953333332</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.651446271044225</v>
+        <v>1.880824309764829</v>
       </c>
       <c r="T94">
-        <v>9.819932715277794</v>
+        <v>11.22278024603177</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1349399923838281</v>
+        <v>0.1334890247237869</v>
       </c>
       <c r="W94">
-        <v>0.126990809118054</v>
+        <v>0.1272038111705481</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8995999492255204</v>
+        <v>0.8899268314919125</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2499572460721477</v>
+        <v>0.2509672460721477</v>
       </c>
       <c r="C95">
-        <v>-5.817322645560637</v>
+        <v>-6.650488091340144</v>
       </c>
       <c r="D95">
-        <v>47.97367735443937</v>
+        <v>47.73751190865987</v>
       </c>
       <c r="E95">
-        <v>32.221</v>
+        <v>32.81800000000001</v>
       </c>
       <c r="F95">
-        <v>55.52100000000001</v>
+        <v>56.11800000000001</v>
       </c>
       <c r="G95">
         <v>1.73</v>
@@ -9077,37 +9077,37 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M95">
-        <v>8.150482800000002</v>
+        <v>8.238122400000002</v>
       </c>
       <c r="N95">
-        <v>-0.8971494666666686</v>
+        <v>-0.9847890666666679</v>
       </c>
       <c r="O95">
-        <v>-0.1345724200000003</v>
+        <v>-0.1477183600000002</v>
       </c>
       <c r="P95">
-        <v>-0.7625770466666684</v>
+        <v>-0.8370707066666677</v>
       </c>
       <c r="Q95">
-        <v>1.477422953333332</v>
+        <v>1.402929293333333</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.880824309764829</v>
+        <v>2.186661694725634</v>
       </c>
       <c r="T95">
-        <v>11.22278024603177</v>
+        <v>13.0932436203704</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1334890247237869</v>
+        <v>0.132068928716087</v>
       </c>
       <c r="W95">
-        <v>0.1272038111705481</v>
+        <v>0.1274122812644784</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8899268314919125</v>
+        <v>0.8804595247739135</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2509672460721477</v>
+        <v>0.2519772460721477</v>
       </c>
       <c r="C96">
-        <v>-6.650488091340144</v>
+        <v>-7.481339730870125</v>
       </c>
       <c r="D96">
-        <v>47.73751190865987</v>
+        <v>47.50366026912988</v>
       </c>
       <c r="E96">
-        <v>32.81800000000001</v>
+        <v>33.41500000000001</v>
       </c>
       <c r="F96">
-        <v>56.11800000000001</v>
+        <v>56.715</v>
       </c>
       <c r="G96">
         <v>1.73</v>
@@ -9159,37 +9159,37 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M96">
-        <v>8.238122400000002</v>
+        <v>8.325762000000001</v>
       </c>
       <c r="N96">
-        <v>-0.9847890666666679</v>
+        <v>-1.072428666666667</v>
       </c>
       <c r="O96">
-        <v>-0.1477183600000002</v>
+        <v>-0.1608643000000001</v>
       </c>
       <c r="P96">
-        <v>-0.8370707066666677</v>
+        <v>-0.9115643666666671</v>
       </c>
       <c r="Q96">
-        <v>1.402929293333333</v>
+        <v>1.328435633333333</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.186661694725634</v>
+        <v>2.614834033670763</v>
       </c>
       <c r="T96">
-        <v>13.0932436203704</v>
+        <v>15.71189234444449</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.132068928716087</v>
+        <v>0.130678729466444</v>
       </c>
       <c r="W96">
-        <v>0.1274122812644784</v>
+        <v>0.127616362514326</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8804595247739135</v>
+        <v>0.8711915297762935</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2519772460721477</v>
+        <v>0.2529872460721477</v>
       </c>
       <c r="C97">
-        <v>-7.481339730870125</v>
+        <v>-8.309911402299711</v>
       </c>
       <c r="D97">
-        <v>47.50366026912988</v>
+        <v>47.2720885977003</v>
       </c>
       <c r="E97">
-        <v>33.41500000000001</v>
+        <v>34.012</v>
       </c>
       <c r="F97">
-        <v>56.715</v>
+        <v>57.312</v>
       </c>
       <c r="G97">
         <v>1.73</v>
@@ -9241,37 +9241,37 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M97">
-        <v>8.325762000000001</v>
+        <v>8.413401600000002</v>
       </c>
       <c r="N97">
-        <v>-1.072428666666667</v>
+        <v>-1.160068266666668</v>
       </c>
       <c r="O97">
-        <v>-0.1608643000000001</v>
+        <v>-0.1740102400000002</v>
       </c>
       <c r="P97">
-        <v>-0.9115643666666671</v>
+        <v>-0.986058026666668</v>
       </c>
       <c r="Q97">
-        <v>1.328435633333333</v>
+        <v>1.253941973333332</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.614834033670763</v>
+        <v>3.257092542088454</v>
       </c>
       <c r="T97">
-        <v>15.71189234444449</v>
+        <v>19.63986543055561</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.130678729466444</v>
+        <v>0.1293174927011685</v>
       </c>
       <c r="W97">
-        <v>0.127616362514326</v>
+        <v>0.1278161920714685</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8711915297762935</v>
+        <v>0.8621166180077904</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2529872460721477</v>
+        <v>0.2539972460721477</v>
       </c>
       <c r="C98">
-        <v>-8.309911402299711</v>
+        <v>-9.136236287159761</v>
       </c>
       <c r="D98">
-        <v>47.27208859770029</v>
+        <v>47.04276371284024</v>
       </c>
       <c r="E98">
-        <v>34.012</v>
+        <v>34.60899999999999</v>
       </c>
       <c r="F98">
-        <v>57.312</v>
+        <v>57.909</v>
       </c>
       <c r="G98">
         <v>1.73</v>
@@ -9323,37 +9323,37 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M98">
-        <v>8.4134016</v>
+        <v>8.501041200000001</v>
       </c>
       <c r="N98">
-        <v>-1.160068266666666</v>
+        <v>-1.247707866666667</v>
       </c>
       <c r="O98">
-        <v>-0.17401024</v>
+        <v>-0.1871561800000001</v>
       </c>
       <c r="P98">
-        <v>-0.9860580266666664</v>
+        <v>-1.060551686666667</v>
       </c>
       <c r="Q98">
-        <v>1.253941973333334</v>
+        <v>1.179448313333333</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.257092542088446</v>
+        <v>4.327523389451262</v>
       </c>
       <c r="T98">
-        <v>19.63986543055556</v>
+        <v>26.18648724074075</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1293174927011686</v>
+        <v>0.1279843226733215</v>
       </c>
       <c r="W98">
-        <v>0.1278161920714685</v>
+        <v>0.1280119014315564</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8621166180077905</v>
+        <v>0.8532288178221431</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2539972460721477</v>
+        <v>0.2550072460721476</v>
       </c>
       <c r="C99">
-        <v>-9.136236287159761</v>
+        <v>-9.960346926212779</v>
       </c>
       <c r="D99">
-        <v>47.04276371284024</v>
+        <v>46.81565307378722</v>
       </c>
       <c r="E99">
-        <v>34.60899999999999</v>
+        <v>35.206</v>
       </c>
       <c r="F99">
-        <v>57.909</v>
+        <v>58.506</v>
       </c>
       <c r="G99">
         <v>1.73</v>
@@ -9405,37 +9405,37 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M99">
-        <v>8.501041200000001</v>
+        <v>8.588680800000001</v>
       </c>
       <c r="N99">
-        <v>-1.247707866666667</v>
+        <v>-1.335347466666667</v>
       </c>
       <c r="O99">
-        <v>-0.1871561800000001</v>
+        <v>-0.20030212</v>
       </c>
       <c r="P99">
-        <v>-1.060551686666667</v>
+        <v>-1.135045346666667</v>
       </c>
       <c r="Q99">
-        <v>1.179448313333333</v>
+        <v>1.104954653333333</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>4.327523389451262</v>
+        <v>6.468385084176892</v>
       </c>
       <c r="T99">
-        <v>26.18648724074075</v>
+        <v>39.27973086111112</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1279843226733215</v>
+        <v>0.1266783601970631</v>
       </c>
       <c r="W99">
-        <v>0.1280119014315564</v>
+        <v>0.1282036167230712</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8532288178221431</v>
+        <v>0.844522401313754</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2550072460721476</v>
+        <v>0.2560172460721477</v>
       </c>
       <c r="C100">
-        <v>-9.960346926212779</v>
+        <v>-10.78227523484594</v>
       </c>
       <c r="D100">
-        <v>46.81565307378722</v>
+        <v>46.59072476515406</v>
       </c>
       <c r="E100">
-        <v>35.206</v>
+        <v>35.803</v>
       </c>
       <c r="F100">
-        <v>58.506</v>
+        <v>59.103</v>
       </c>
       <c r="G100">
         <v>1.73</v>
@@ -9487,37 +9487,37 @@
         <v>7.253333333333334</v>
       </c>
       <c r="M100">
-        <v>8.588680800000001</v>
+        <v>8.676320400000002</v>
       </c>
       <c r="N100">
-        <v>-1.335347466666667</v>
+        <v>-1.422987066666668</v>
       </c>
       <c r="O100">
-        <v>-0.20030212</v>
+        <v>-0.2134480600000002</v>
       </c>
       <c r="P100">
-        <v>-1.135045346666667</v>
+        <v>-1.209539006666668</v>
       </c>
       <c r="Q100">
-        <v>1.104954653333333</v>
+        <v>1.030460993333333</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>6.468385084176892</v>
+        <v>12.89097016835378</v>
       </c>
       <c r="T100">
-        <v>39.27973086111112</v>
+        <v>78.55946172222224</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1266783601970631</v>
+        <v>0.1253987808011331</v>
       </c>
       <c r="W100">
-        <v>0.1282036167230712</v>
+        <v>0.1283914589783937</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.844522401313754</v>
+        <v>0.8359918720075543</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2560172460721477</v>
-      </c>
-      <c r="C101">
-        <v>-10.78227523484594</v>
-      </c>
-      <c r="D101">
-        <v>46.59072476515406</v>
-      </c>
-      <c r="E101">
-        <v>35.803</v>
-      </c>
-      <c r="F101">
-        <v>59.103</v>
-      </c>
-      <c r="G101">
-        <v>1.73</v>
-      </c>
-      <c r="H101">
-        <v>36.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>9.493333333333334</v>
-      </c>
-      <c r="K101">
-        <v>2.24</v>
-      </c>
-      <c r="L101">
-        <v>7.253333333333334</v>
-      </c>
-      <c r="M101">
-        <v>8.676320400000002</v>
-      </c>
-      <c r="N101">
-        <v>-1.422987066666668</v>
-      </c>
-      <c r="O101">
-        <v>-0.2134480600000002</v>
-      </c>
-      <c r="P101">
-        <v>-1.209539006666668</v>
-      </c>
-      <c r="Q101">
-        <v>1.030460993333333</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>12.89097016835378</v>
-      </c>
-      <c r="T101">
-        <v>78.55946172222224</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1253987808011331</v>
-      </c>
-      <c r="W101">
-        <v>0.1283914589783937</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8359918720075543</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
